--- a/PowerLogic_BESS_Model.xlsx
+++ b/PowerLogic_BESS_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jai_PC\Desktop\BessArbitrageApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A563252C-5AA6-4728-B2BF-EDFAE15382D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDE67D-0F40-4E30-A3AB-87D679DFE0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,15 @@
     <sheet name="01_Sizing" sheetId="2" r:id="rId2"/>
     <sheet name="02_Dispatch" sheetId="3" r:id="rId3"/>
     <sheet name="03_Revenue" sheetId="4" r:id="rId4"/>
-    <sheet name="Prices" sheetId="5" r:id="rId5"/>
+    <sheet name="04_Container" sheetId="5" r:id="rId5"/>
+    <sheet name="Prices" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="197">
   <si>
     <t>POWERLOGIC BESS · INDIAN POWER MARKET</t>
   </si>
@@ -77,6 +78,9 @@
     <t>Energy used by model (MWh)</t>
   </si>
   <si>
+    <t>Installed (container-rounded) energy when the switch is 1</t>
+  </si>
+  <si>
     <t>MSEDCL TARIFF — HT INDUSTRIAL (FY2026-27 ORDER)</t>
   </si>
   <si>
@@ -212,22 +216,40 @@
     <t>Max BESS output in the peak window, rounded up to 0.5 MW</t>
   </si>
   <si>
-    <t>Suggested energy — nameplate (MWh)</t>
+    <t>Energy needed — nameplate (MWh)</t>
   </si>
   <si>
     <t>Usable ÷ DoD ÷ (1 − EoL margin), rounded up to 1 MWh</t>
   </si>
   <si>
+    <t>Container rating (MWh)</t>
+  </si>
+  <si>
+    <t>5 MWh container from the container build-up sheet</t>
+  </si>
+  <si>
+    <t>Containers required</t>
+  </si>
+  <si>
+    <t>Whole 5 MWh containers to cover the energy needed</t>
+  </si>
+  <si>
+    <t>Installed energy (MWh)</t>
+  </si>
+  <si>
+    <t>Feeds dispatch &amp; revenue when the Inputs switch = 1</t>
+  </si>
+  <si>
     <t>Duration (h)</t>
   </si>
   <si>
-    <t>vs the 7-h MSEDCL peak window</t>
+    <t>installed, vs the 7-h MSEDCL peak window</t>
   </si>
   <si>
     <t>Indicative capex (₹ Cr)</t>
   </si>
   <si>
-    <t>+5% contingency</t>
+    <t>on installed energy, +5% contingency</t>
   </si>
   <si>
     <t>Feasibility check</t>
@@ -486,6 +508,102 @@
   </si>
   <si>
     <t>Fixed streams held flat; arbitrage degrades with the battery; O&amp;M escalates 5%/yr — same treatment as the app.</t>
+  </si>
+  <si>
+    <t>MODULE 00A · CONTAINER BUILD-UP</t>
+  </si>
+  <si>
+    <t>5 MWh BESS container — 314 Ah LFP cell electrical build-up</t>
+  </si>
+  <si>
+    <t>Source: user's "BESS 5 MWH Container Calculation.xlsx". Edit the blue cell specs / counts and the container rating flows into 01_Sizing.</t>
+  </si>
+  <si>
+    <t>Container nameplate (MWh)</t>
+  </si>
+  <si>
+    <t>Cells per container</t>
+  </si>
+  <si>
+    <t>Referenced by 01_Sizing to convert energy needed into whole containers.</t>
+  </si>
+  <si>
+    <t>DESIGN A — 52S1P (LV rack, 12 racks parallel)</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Series/Parallel</t>
+  </si>
+  <si>
+    <t>Nos</t>
+  </si>
+  <si>
+    <t>Of</t>
+  </si>
+  <si>
+    <t>Voltage (V)</t>
+  </si>
+  <si>
+    <t>Capacity (Ah)</t>
+  </si>
+  <si>
+    <t>Energy (Wh)</t>
+  </si>
+  <si>
+    <t>Energy (kWh)</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>3.2 V / 314 Ah LFP — blue inputs</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Series</t>
+  </si>
+  <si>
+    <t>Cells</t>
+  </si>
+  <si>
+    <t>Pack</t>
+  </si>
+  <si>
+    <t>Modules</t>
+  </si>
+  <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Packs</t>
+  </si>
+  <si>
+    <t>1,331 V DC rack, 418 kWh</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>Parallel</t>
+  </si>
+  <si>
+    <t>Racks</t>
+  </si>
+  <si>
+    <t>52S1P — voltage unchanged, Ah adds in parallel</t>
+  </si>
+  <si>
+    <t>DESIGN B — 104S1P (HV rack, 6 racks parallel) — alternate, same energy</t>
+  </si>
+  <si>
+    <t>2,662 V DC rack</t>
+  </si>
+  <si>
+    <t>104S1P — same 5,016 kWh as Design A</t>
   </si>
   <si>
     <t>Typical day (DAM)</t>
@@ -504,19 +622,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="12">
+  <numFmts count="20">
     <numFmt numFmtId="164" formatCode="#,##0.0&quot; MW&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; MWh&quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="&quot;₹&quot;0.00&quot; Cr&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="&quot;₹&quot;#,##0"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0&quot; MWh&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.0&quot; h&quot;"/>
-    <numFmt numFmtId="173" formatCode="&quot;₹&quot;#,##0.0&quot; Cr&quot;;\(&quot;₹&quot;#,##0.0&quot; Cr&quot;\)"/>
-    <numFmt numFmtId="174" formatCode="00"/>
-    <numFmt numFmtId="175" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0&quot; MWh&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;₹&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;₹&quot;0.00&quot; Cr&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000&quot; MWh&quot;"/>
+    <numFmt numFmtId="173" formatCode="0&quot; containers&quot;"/>
+    <numFmt numFmtId="174" formatCode="0.0&quot; h&quot;"/>
+    <numFmt numFmtId="175" formatCode="&quot;₹&quot;#,##0.0&quot; Cr&quot;;\(&quot;₹&quot;#,##0.0&quot; Cr&quot;\)"/>
+    <numFmt numFmtId="176" formatCode="00"/>
+    <numFmt numFmtId="177" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,##0&quot; cells&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0&quot; V&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0&quot; Ah&quot;"/>
+    <numFmt numFmtId="181" formatCode="#,##0.0"/>
+    <numFmt numFmtId="182" formatCode="#,##0.000"/>
+    <numFmt numFmtId="183" formatCode="#,##0.0&quot; V&quot;"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -620,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -634,29 +760,32 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -666,26 +795,41 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1105,13 +1249,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="13">
-        <f>IF('00_Inputs'!$B$11=1,'01_Sizing'!$C$10,'00_Inputs'!$B$10)</f>
-        <v>69</v>
+        <f>IF('00_Inputs'!$B$11=1,'01_Sizing'!$C$13,'00_Inputs'!$B$10)</f>
+        <v>70.223462400000017</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1119,18 +1266,18 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="14">
         <v>8.44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="15">
         <v>1.2</v>
@@ -1138,41 +1285,41 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="16">
         <v>0.85</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="14">
         <v>3.65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="17">
         <f>'00_Inputs'!$B$16*'00_Inputs'!$B$17</f>
         <v>10.127999999999998</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1180,7 +1327,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="18">
         <v>10</v>
@@ -1188,7 +1335,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="9">
         <v>5</v>
@@ -1196,7 +1343,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="9">
         <v>7</v>
@@ -1204,29 +1351,29 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="18">
         <v>9</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="11">
         <v>0.9</v>
@@ -1234,18 +1381,18 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="11">
         <v>0.1</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1253,7 +1400,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="19">
         <v>1.1000000000000001</v>
@@ -1261,7 +1408,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="20">
         <v>1.4999999999999999E-2</v>
@@ -1269,7 +1416,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="21">
         <v>330</v>
@@ -1277,7 +1424,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="20">
         <v>0.02</v>
@@ -1285,7 +1432,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="11">
         <v>0.12</v>
@@ -1293,7 +1440,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -1301,7 +1448,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="22">
         <v>5000</v>
@@ -1309,18 +1456,18 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="23">
         <v>450</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38" s="21">
         <v>100</v>
@@ -1328,7 +1475,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" s="14">
         <v>28</v>
@@ -1341,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1356,22 +1503,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1384,857 +1531,893 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="24">
-        <f>SUM($F$18:$F$41)</f>
+        <f>SUM($F$21:$F$44)</f>
         <v>63</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="24">
-        <f>SUM($H$18:$H$41)</f>
+        <f>SUM($H$21:$H$44)</f>
         <v>63</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="25">
         <f>MIN('00_Inputs'!$B$26,C7*'00_Inputs'!$B$12/C6)</f>
         <v>0.88</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="26">
-        <f>CEILING(MAX($F$18:$F$41)*C8,0.5)</f>
+        <f>CEILING(MAX($F$21:$F$44)*C8,0.5)</f>
         <v>8</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="27">
         <f>CEILING(C6*C8/'00_Inputs'!$B$27/(1-'00_Inputs'!$B$28),1)</f>
         <v>69</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="28">
-        <f>C10/C9</f>
-        <v>8.625</v>
+        <f>'04_Container'!$C$5</f>
+        <v>5.0159616000000007</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="29">
-        <f>C10*'00_Inputs'!$B$30*1.05</f>
-        <v>79.695000000000007</v>
+        <f>ROUNDUP(C10/C11,0)</f>
+        <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="30" t="str">
+        <v>69</v>
+      </c>
+      <c r="C13" s="30">
+        <f>C12*C11</f>
+        <v>70.223462400000017</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="31">
+        <f>C13/C9</f>
+        <v>8.7779328000000021</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="32">
+        <f>C13*'00_Inputs'!$B$30*1.05</f>
+        <v>81.10809907200003</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="33" t="str">
         <f>IF('00_Inputs'!$B$26&lt;=C8+0.0001,"OK — target coverage feasible","CHECK — max feasible coverage = "&amp;TEXT(C8,"0%")&amp;". Raise contract demand, shed day load, or add on-site solar.")</f>
         <v>CHECK — max feasible coverage = 88%. Raise contract demand, shed day load, or add on-site solar.</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="32" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="I19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H17" s="32" t="s">
+    </row>
+    <row r="20" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="B20" s="35" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="33">
-        <v>0</v>
-      </c>
-      <c r="B18" s="34" t="str">
-        <f t="shared" ref="B18:B41" si="0">IF(A18&gt;=17,"Peak",IF(A18&gt;=9,"Solar","Normal"))</f>
+      <c r="C20" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="36">
+        <v>0</v>
+      </c>
+      <c r="B21" s="37" t="str">
+        <f t="shared" ref="B21:B44" si="0">IF(A21&gt;=17,"Peak",IF(A21&gt;=9,"Solar","Normal"))</f>
         <v>Normal</v>
       </c>
-      <c r="C18" s="35">
-        <f>IF(A18&lt;6,'00_Inputs'!$B$23,IF(A18&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>5</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37">
-        <f t="shared" ref="E18:E41" si="1">IF(D18&lt;&gt;"",D18,C18)</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="37">
-        <f>IF(B18="Peak",MIN(E18,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="37">
-        <f t="shared" ref="G18:G41" si="2">F18*$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="37">
-        <f>IF(B18="Peak",0,MIN(MAX('00_Inputs'!$B$22-E18,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="33">
-        <v>1</v>
-      </c>
-      <c r="B19" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Normal</v>
-      </c>
-      <c r="C19" s="35">
-        <f>IF(A19&lt;6,'00_Inputs'!$B$23,IF(A19&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>5</v>
-      </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="F19" s="37">
-        <f>IF(B19="Peak",MIN(E19,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="37">
-        <f>IF(B19="Peak",0,MIN(MAX('00_Inputs'!$B$22-E19,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="33">
-        <v>2</v>
-      </c>
-      <c r="B20" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Normal</v>
-      </c>
-      <c r="C20" s="35">
-        <f>IF(A20&lt;6,'00_Inputs'!$B$23,IF(A20&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>5</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="F20" s="37">
-        <f>IF(B20="Peak",MIN(E20,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="37">
-        <f>IF(B20="Peak",0,MIN(MAX('00_Inputs'!$B$22-E20,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="33">
-        <v>3</v>
-      </c>
-      <c r="B21" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Normal</v>
-      </c>
-      <c r="C21" s="35">
+      <c r="C21" s="38">
         <f>IF(A21&lt;6,'00_Inputs'!$B$23,IF(A21&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37">
-        <f t="shared" si="1"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40">
+        <f t="shared" ref="E21:E44" si="1">IF(D21&lt;&gt;"",D21,C21)</f>
         <v>5</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="40">
         <f>IF(B21="Peak",MIN(E21,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="37">
-        <f>IF(B21="Peak",0,MIN(MAX('00_Inputs'!$B$22-E21,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G21" s="40">
+        <f t="shared" ref="G21:G44" si="2">F21*$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="40">
+        <f>IF(B21="Peak",0,MIN(MAX('00_Inputs'!$B$22-E21,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="33">
-        <v>4</v>
-      </c>
-      <c r="B22" s="34" t="str">
+      <c r="A22" s="36">
+        <v>1</v>
+      </c>
+      <c r="B22" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="38">
         <f>IF(A22&lt;6,'00_Inputs'!$B$23,IF(A22&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37">
+      <c r="D22" s="39"/>
+      <c r="E22" s="40">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="40">
         <f>IF(B22="Peak",MIN(E22,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="37">
-        <f>IF(B22="Peak",0,MIN(MAX('00_Inputs'!$B$22-E22,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G22" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="40">
+        <f>IF(B22="Peak",0,MIN(MAX('00_Inputs'!$B$22-E22,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="33">
-        <v>5</v>
-      </c>
-      <c r="B23" s="34" t="str">
+      <c r="A23" s="36">
+        <v>2</v>
+      </c>
+      <c r="B23" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="38">
         <f>IF(A23&lt;6,'00_Inputs'!$B$23,IF(A23&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37">
+      <c r="D23" s="39"/>
+      <c r="E23" s="40">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="40">
         <f>IF(B23="Peak",MIN(E23,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="37">
-        <f>IF(B23="Peak",0,MIN(MAX('00_Inputs'!$B$22-E23,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G23" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="40">
+        <f>IF(B23="Peak",0,MIN(MAX('00_Inputs'!$B$22-E23,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="33">
+      <c r="A24" s="36">
+        <v>3</v>
+      </c>
+      <c r="B24" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normal</v>
+      </c>
+      <c r="C24" s="38">
+        <f>IF(A24&lt;6,'00_Inputs'!$B$23,IF(A24&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>5</v>
+      </c>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F24" s="40">
+        <f>IF(B24="Peak",MIN(E24,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="40">
+        <f>IF(B24="Peak",0,MIN(MAX('00_Inputs'!$B$22-E24,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="36">
+        <v>4</v>
+      </c>
+      <c r="B25" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normal</v>
+      </c>
+      <c r="C25" s="38">
+        <f>IF(A25&lt;6,'00_Inputs'!$B$23,IF(A25&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>5</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F25" s="40">
+        <f>IF(B25="Peak",MIN(E25,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="40">
+        <f>IF(B25="Peak",0,MIN(MAX('00_Inputs'!$B$22-E25,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="36">
+        <v>5</v>
+      </c>
+      <c r="B26" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normal</v>
+      </c>
+      <c r="C26" s="38">
+        <f>IF(A26&lt;6,'00_Inputs'!$B$23,IF(A26&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>5</v>
+      </c>
+      <c r="D26" s="39"/>
+      <c r="E26" s="40">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F26" s="40">
+        <f>IF(B26="Peak",MIN(E26,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="40">
+        <f>IF(B26="Peak",0,MIN(MAX('00_Inputs'!$B$22-E26,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="36">
         <v>6</v>
       </c>
-      <c r="B24" s="34" t="str">
+      <c r="B27" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C24" s="35">
-        <f>IF(A24&lt;6,'00_Inputs'!$B$23,IF(A24&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>7</v>
-      </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="37">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F24" s="37">
-        <f>IF(B24="Peak",MIN(E24,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="37">
-        <f>IF(B24="Peak",0,MIN(MAX('00_Inputs'!$B$22-E24,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="33">
-        <v>7</v>
-      </c>
-      <c r="B25" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Normal</v>
-      </c>
-      <c r="C25" s="35">
-        <f>IF(A25&lt;6,'00_Inputs'!$B$23,IF(A25&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>7</v>
-      </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F25" s="37">
-        <f>IF(B25="Peak",MIN(E25,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="37">
-        <f>IF(B25="Peak",0,MIN(MAX('00_Inputs'!$B$22-E25,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="33">
-        <v>8</v>
-      </c>
-      <c r="B26" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Normal</v>
-      </c>
-      <c r="C26" s="35">
-        <f>IF(A26&lt;6,'00_Inputs'!$B$23,IF(A26&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>7</v>
-      </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="F26" s="37">
-        <f>IF(B26="Peak",MIN(E26,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="37">
-        <f>IF(B26="Peak",0,MIN(MAX('00_Inputs'!$B$22-E26,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="33">
-        <v>9</v>
-      </c>
-      <c r="B27" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Solar</v>
-      </c>
-      <c r="C27" s="35">
+      <c r="C27" s="38">
         <f>IF(A27&lt;6,'00_Inputs'!$B$23,IF(A27&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37">
+      <c r="D27" s="39"/>
+      <c r="E27" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="40">
         <f>IF(B27="Peak",MIN(E27,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="37">
-        <f>IF(B27="Peak",0,MIN(MAX('00_Inputs'!$B$22-E27,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G27" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="40">
+        <f>IF(B27="Peak",0,MIN(MAX('00_Inputs'!$B$22-E27,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="33">
-        <v>10</v>
-      </c>
-      <c r="B28" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Solar</v>
-      </c>
-      <c r="C28" s="35">
+      <c r="A28" s="36">
+        <v>7</v>
+      </c>
+      <c r="B28" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normal</v>
+      </c>
+      <c r="C28" s="38">
         <f>IF(A28&lt;6,'00_Inputs'!$B$23,IF(A28&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="37">
+      <c r="D28" s="39"/>
+      <c r="E28" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="40">
         <f>IF(B28="Peak",MIN(E28,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="37">
-        <f>IF(B28="Peak",0,MIN(MAX('00_Inputs'!$B$22-E28,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G28" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="40">
+        <f>IF(B28="Peak",0,MIN(MAX('00_Inputs'!$B$22-E28,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="33">
-        <v>11</v>
-      </c>
-      <c r="B29" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Solar</v>
-      </c>
-      <c r="C29" s="35">
+      <c r="A29" s="36">
+        <v>8</v>
+      </c>
+      <c r="B29" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Normal</v>
+      </c>
+      <c r="C29" s="38">
         <f>IF(A29&lt;6,'00_Inputs'!$B$23,IF(A29&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37">
+      <c r="D29" s="39"/>
+      <c r="E29" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="40">
         <f>IF(B29="Peak",MIN(E29,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="37">
-        <f>IF(B29="Peak",0,MIN(MAX('00_Inputs'!$B$22-E29,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="40">
+        <f>IF(B29="Peak",0,MIN(MAX('00_Inputs'!$B$22-E29,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="33">
-        <v>12</v>
-      </c>
-      <c r="B30" s="34" t="str">
+      <c r="A30" s="36">
+        <v>9</v>
+      </c>
+      <c r="B30" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="38">
         <f>IF(A30&lt;6,'00_Inputs'!$B$23,IF(A30&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37">
+      <c r="D30" s="39"/>
+      <c r="E30" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="40">
         <f>IF(B30="Peak",MIN(E30,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="37">
-        <f>IF(B30="Peak",0,MIN(MAX('00_Inputs'!$B$22-E30,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="40">
+        <f>IF(B30="Peak",0,MIN(MAX('00_Inputs'!$B$22-E30,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="33">
-        <v>13</v>
-      </c>
-      <c r="B31" s="34" t="str">
+      <c r="A31" s="36">
+        <v>10</v>
+      </c>
+      <c r="B31" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="38">
         <f>IF(A31&lt;6,'00_Inputs'!$B$23,IF(A31&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37">
+      <c r="D31" s="39"/>
+      <c r="E31" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="40">
         <f>IF(B31="Peak",MIN(E31,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="37">
-        <f>IF(B31="Peak",0,MIN(MAX('00_Inputs'!$B$22-E31,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="40">
+        <f>IF(B31="Peak",0,MIN(MAX('00_Inputs'!$B$22-E31,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="33">
-        <v>14</v>
-      </c>
-      <c r="B32" s="34" t="str">
+      <c r="A32" s="36">
+        <v>11</v>
+      </c>
+      <c r="B32" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="38">
         <f>IF(A32&lt;6,'00_Inputs'!$B$23,IF(A32&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="37">
+      <c r="D32" s="39"/>
+      <c r="E32" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="40">
         <f>IF(B32="Peak",MIN(E32,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="37">
-        <f>IF(B32="Peak",0,MIN(MAX('00_Inputs'!$B$22-E32,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="40">
+        <f>IF(B32="Peak",0,MIN(MAX('00_Inputs'!$B$22-E32,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="33">
-        <v>15</v>
-      </c>
-      <c r="B33" s="34" t="str">
+      <c r="A33" s="36">
+        <v>12</v>
+      </c>
+      <c r="B33" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="38">
         <f>IF(A33&lt;6,'00_Inputs'!$B$23,IF(A33&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37">
+      <c r="D33" s="39"/>
+      <c r="E33" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F33" s="37">
+      <c r="F33" s="40">
         <f>IF(B33="Peak",MIN(E33,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="37">
-        <f>IF(B33="Peak",0,MIN(MAX('00_Inputs'!$B$22-E33,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="40">
+        <f>IF(B33="Peak",0,MIN(MAX('00_Inputs'!$B$22-E33,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="33">
-        <v>16</v>
-      </c>
-      <c r="B34" s="34" t="str">
+      <c r="A34" s="36">
+        <v>13</v>
+      </c>
+      <c r="B34" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="38">
         <f>IF(A34&lt;6,'00_Inputs'!$B$23,IF(A34&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="37">
+      <c r="D34" s="39"/>
+      <c r="E34" s="40">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="40">
         <f>IF(B34="Peak",MIN(E34,'00_Inputs'!$B$22),0)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="37">
-        <f>IF(B34="Peak",0,MIN(MAX('00_Inputs'!$B$22-E34,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="G34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="40">
+        <f>IF(B34="Peak",0,MIN(MAX('00_Inputs'!$B$22-E34,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="33">
+      <c r="A35" s="36">
+        <v>14</v>
+      </c>
+      <c r="B35" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Solar</v>
+      </c>
+      <c r="C35" s="38">
+        <f>IF(A35&lt;6,'00_Inputs'!$B$23,IF(A35&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>7</v>
+      </c>
+      <c r="D35" s="39"/>
+      <c r="E35" s="40">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F35" s="40">
+        <f>IF(B35="Peak",MIN(E35,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="40">
+        <f>IF(B35="Peak",0,MIN(MAX('00_Inputs'!$B$22-E35,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="36">
+        <v>15</v>
+      </c>
+      <c r="B36" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Solar</v>
+      </c>
+      <c r="C36" s="38">
+        <f>IF(A36&lt;6,'00_Inputs'!$B$23,IF(A36&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>7</v>
+      </c>
+      <c r="D36" s="39"/>
+      <c r="E36" s="40">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F36" s="40">
+        <f>IF(B36="Peak",MIN(E36,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="40">
+        <f>IF(B36="Peak",0,MIN(MAX('00_Inputs'!$B$22-E36,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="36">
+        <v>16</v>
+      </c>
+      <c r="B37" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Solar</v>
+      </c>
+      <c r="C37" s="38">
+        <f>IF(A37&lt;6,'00_Inputs'!$B$23,IF(A37&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>7</v>
+      </c>
+      <c r="D37" s="39"/>
+      <c r="E37" s="40">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F37" s="40">
+        <f>IF(B37="Peak",MIN(E37,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="40">
+        <f>IF(B37="Peak",0,MIN(MAX('00_Inputs'!$B$22-E37,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="36">
         <v>17</v>
       </c>
-      <c r="B35" s="34" t="str">
+      <c r="B38" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C35" s="35">
-        <f>IF(A35&lt;6,'00_Inputs'!$B$23,IF(A35&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>9</v>
-      </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F35" s="37">
-        <f>IF(B35="Peak",MIN(E35,'00_Inputs'!$B$22),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G35" s="37">
-        <f t="shared" si="2"/>
-        <v>7.92</v>
-      </c>
-      <c r="H35" s="37">
-        <f>IF(B35="Peak",0,MIN(MAX('00_Inputs'!$B$22-E35,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="33">
-        <v>18</v>
-      </c>
-      <c r="B36" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Peak</v>
-      </c>
-      <c r="C36" s="35">
-        <f>IF(A36&lt;6,'00_Inputs'!$B$23,IF(A36&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>9</v>
-      </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="37">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F36" s="37">
-        <f>IF(B36="Peak",MIN(E36,'00_Inputs'!$B$22),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G36" s="37">
-        <f t="shared" si="2"/>
-        <v>7.92</v>
-      </c>
-      <c r="H36" s="37">
-        <f>IF(B36="Peak",0,MIN(MAX('00_Inputs'!$B$22-E36,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="33">
-        <v>19</v>
-      </c>
-      <c r="B37" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Peak</v>
-      </c>
-      <c r="C37" s="35">
-        <f>IF(A37&lt;6,'00_Inputs'!$B$23,IF(A37&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
-        <v>9</v>
-      </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="37">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="F37" s="37">
-        <f>IF(B37="Peak",MIN(E37,'00_Inputs'!$B$22),0)</f>
-        <v>9</v>
-      </c>
-      <c r="G37" s="37">
-        <f t="shared" si="2"/>
-        <v>7.92</v>
-      </c>
-      <c r="H37" s="37">
-        <f>IF(B37="Peak",0,MIN(MAX('00_Inputs'!$B$22-E37,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="33">
-        <v>20</v>
-      </c>
-      <c r="B38" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>Peak</v>
-      </c>
-      <c r="C38" s="35">
+      <c r="C38" s="38">
         <f>IF(A38&lt;6,'00_Inputs'!$B$23,IF(A38&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="37">
+      <c r="D38" s="39"/>
+      <c r="E38" s="40">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F38" s="37">
+      <c r="F38" s="40">
         <f>IF(B38="Peak",MIN(E38,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G38" s="37">
+      <c r="G38" s="40">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H38" s="37">
-        <f>IF(B38="Peak",0,MIN(MAX('00_Inputs'!$B$22-E38,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="H38" s="40">
+        <f>IF(B38="Peak",0,MIN(MAX('00_Inputs'!$B$22-E38,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="33">
-        <v>21</v>
-      </c>
-      <c r="B39" s="34" t="str">
+      <c r="A39" s="36">
+        <v>18</v>
+      </c>
+      <c r="B39" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="38">
         <f>IF(A39&lt;6,'00_Inputs'!$B$23,IF(A39&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37">
+      <c r="D39" s="39"/>
+      <c r="E39" s="40">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F39" s="37">
+      <c r="F39" s="40">
         <f>IF(B39="Peak",MIN(E39,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G39" s="37">
+      <c r="G39" s="40">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H39" s="37">
-        <f>IF(B39="Peak",0,MIN(MAX('00_Inputs'!$B$22-E39,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="H39" s="40">
+        <f>IF(B39="Peak",0,MIN(MAX('00_Inputs'!$B$22-E39,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="33">
-        <v>22</v>
-      </c>
-      <c r="B40" s="34" t="str">
+      <c r="A40" s="36">
+        <v>19</v>
+      </c>
+      <c r="B40" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="38">
         <f>IF(A40&lt;6,'00_Inputs'!$B$23,IF(A40&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="37">
+      <c r="D40" s="39"/>
+      <c r="E40" s="40">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F40" s="37">
+      <c r="F40" s="40">
         <f>IF(B40="Peak",MIN(E40,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G40" s="37">
+      <c r="G40" s="40">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H40" s="37">
-        <f>IF(B40="Peak",0,MIN(MAX('00_Inputs'!$B$22-E40,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="H40" s="40">
+        <f>IF(B40="Peak",0,MIN(MAX('00_Inputs'!$B$22-E40,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="33">
-        <v>23</v>
-      </c>
-      <c r="B41" s="34" t="str">
+      <c r="A41" s="36">
+        <v>20</v>
+      </c>
+      <c r="B41" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="38">
         <f>IF(A41&lt;6,'00_Inputs'!$B$23,IF(A41&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37">
+      <c r="D41" s="39"/>
+      <c r="E41" s="40">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F41" s="37">
+      <c r="F41" s="40">
         <f>IF(B41="Peak",MIN(E41,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G41" s="37">
+      <c r="G41" s="40">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H41" s="37">
-        <f>IF(B41="Peak",0,MIN(MAX('00_Inputs'!$B$22-E41,0),'00_Inputs'!$B$26*MAX($F$18:$F$41)))</f>
+      <c r="H41" s="40">
+        <f>IF(B41="Peak",0,MIN(MAX('00_Inputs'!$B$22-E41,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="36">
+        <v>21</v>
+      </c>
+      <c r="B42" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Peak</v>
+      </c>
+      <c r="C42" s="38">
+        <f>IF(A42&lt;6,'00_Inputs'!$B$23,IF(A42&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>9</v>
+      </c>
+      <c r="D42" s="39"/>
+      <c r="E42" s="40">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F42" s="40">
+        <f>IF(B42="Peak",MIN(E42,'00_Inputs'!$B$22),0)</f>
+        <v>9</v>
+      </c>
+      <c r="G42" s="40">
+        <f t="shared" si="2"/>
+        <v>7.92</v>
+      </c>
+      <c r="H42" s="40">
+        <f>IF(B42="Peak",0,MIN(MAX('00_Inputs'!$B$22-E42,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>80</v>
+      <c r="A43" s="36">
+        <v>22</v>
+      </c>
+      <c r="B43" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Peak</v>
+      </c>
+      <c r="C43" s="38">
+        <f>IF(A43&lt;6,'00_Inputs'!$B$23,IF(A43&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>9</v>
+      </c>
+      <c r="D43" s="39"/>
+      <c r="E43" s="40">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F43" s="40">
+        <f>IF(B43="Peak",MIN(E43,'00_Inputs'!$B$22),0)</f>
+        <v>9</v>
+      </c>
+      <c r="G43" s="40">
+        <f t="shared" si="2"/>
+        <v>7.92</v>
+      </c>
+      <c r="H43" s="40">
+        <f>IF(B43="Peak",0,MIN(MAX('00_Inputs'!$B$22-E43,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="36">
+        <v>23</v>
+      </c>
+      <c r="B44" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Peak</v>
+      </c>
+      <c r="C44" s="38">
+        <f>IF(A44&lt;6,'00_Inputs'!$B$23,IF(A44&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+        <v>9</v>
+      </c>
+      <c r="D44" s="39"/>
+      <c r="E44" s="40">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F44" s="40">
+        <f>IF(B44="Peak",MIN(E44,'00_Inputs'!$B$22),0)</f>
+        <v>9</v>
+      </c>
+      <c r="G44" s="40">
+        <f t="shared" si="2"/>
+        <v>7.92</v>
+      </c>
+      <c r="H44" s="40">
+        <f>IF(B44="Peak",0,MIN(MAX('00_Inputs'!$B$22-E44,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2261,22 +2444,22 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2285,28 +2468,28 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C6" s="24">
         <f>MIN('00_Inputs'!$B$14,'00_Inputs'!$B$13*7/'00_Inputs'!$B$12)</f>
         <v>63.636363636363633</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="38">
+        <v>94</v>
+      </c>
+      <c r="C7" s="41">
         <f>CEILING(C6/'00_Inputs'!$B$13,1)</f>
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C8" s="24">
         <f>SUM($H$21:$H$44)</f>
@@ -2315,7 +2498,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C9" s="24">
         <f>SUM($I$21:$I$44)</f>
@@ -2324,141 +2507,141 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="39">
+        <v>97</v>
+      </c>
+      <c r="C10" s="42">
         <f>SUM($L$21:$L$44)</f>
         <v>416745.45454545453</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="39">
+        <v>99</v>
+      </c>
+      <c r="C11" s="42">
         <f>SUM($M$21:$M$44)</f>
         <v>567167.99999999977</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="40">
+        <v>100</v>
+      </c>
+      <c r="C12" s="43">
         <f>(C11-C10)/100000</f>
         <v>1.5042254545454523</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="41">
+        <v>101</v>
+      </c>
+      <c r="C13" s="44">
         <f>C12*'00_Inputs'!$B$32/100</f>
         <v>4.9639439999999926</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="42">
+        <v>103</v>
+      </c>
+      <c r="C14" s="45">
         <f>IF(C8&gt;0,C10/C8/1000,0)</f>
         <v>6.5488571428571429</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="42">
+        <v>104</v>
+      </c>
+      <c r="C15" s="45">
         <f>IF(C9&gt;0,C11/C9/1000,0)</f>
         <v>10.127999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="42">
+        <v>105</v>
+      </c>
+      <c r="C16" s="45">
         <f>C15-C14/'00_Inputs'!$B$12</f>
         <v>2.6861168831168811</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="43">
+        <v>107</v>
+      </c>
+      <c r="C17" s="46">
         <f>$J$44/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" s="32" t="s">
+      <c r="A20" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="32" t="s">
+      <c r="D20" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="L20" s="32" t="s">
+      <c r="E20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="F20" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="N20" s="32" t="s">
+      <c r="G20" s="35" t="s">
         <v>113</v>
       </c>
+      <c r="H20" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="N20" s="35" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="33">
-        <v>0</v>
-      </c>
-      <c r="B21" s="34" t="str">
+      <c r="A21" s="36">
+        <v>0</v>
+      </c>
+      <c r="B21" s="37" t="str">
         <f t="shared" ref="B21:B44" si="0">IF(A21&gt;=17,"Peak",IF(A21&gt;=9,"Solar","Normal"))</f>
         <v>Normal</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A21+1,'00_Inputs'!$B$7)</f>
         <v>4.2</v>
       </c>
@@ -2470,52 +2653,52 @@
         <f>'00_Inputs'!$B$16*IF(B21="Peak",'00_Inputs'!$B$17,IF(B21="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="48">
         <f t="shared" ref="F21:F44" si="1">IF(B21="Peak","",SUMPRODUCT(($B$21:$B$44&lt;&gt;"Peak")*($D$21:$D$44&lt;D21))+1)</f>
         <v>14</v>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="48">
         <f>IF(B21="Peak",0,IF(AND(F21&lt;=$C$7,D21&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="40">
         <f>IF(G21=1,MIN('00_Inputs'!$B$13,$C$6),0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="40">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="40">
         <f>H21-I21/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K21" s="46">
+      <c r="K21" s="49">
         <f>J21/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L21" s="47">
+      <c r="L21" s="50">
         <f t="shared" ref="L21:L44" si="2">H21*1000*D21</f>
         <v>0</v>
       </c>
-      <c r="M21" s="47">
+      <c r="M21" s="50">
         <f t="shared" ref="M21:M44" si="3">I21*1000*E21</f>
         <v>0</v>
       </c>
-      <c r="N21" s="34" t="str">
+      <c r="N21" s="37" t="str">
         <f t="shared" ref="N21:N44" si="4">IF(H21&gt;0,"CHARGE",IF(I21&gt;0,"DISCHARGE","—"))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="33">
+      <c r="A22" s="36">
         <v>1</v>
       </c>
-      <c r="B22" s="34" t="str">
+      <c r="B22" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A22+1,'00_Inputs'!$B$7)</f>
         <v>3.9</v>
       </c>
@@ -2527,52 +2710,52 @@
         <f>'00_Inputs'!$B$16*IF(B22="Peak",'00_Inputs'!$B$17,IF(B22="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="48">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="48">
         <f>IF(B22="Peak",0,IF(AND(F22&lt;=$C$7,D22&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="40">
         <f>IF(G22=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H21))),0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="37">
+      <c r="I22" s="40">
         <f>IF(B22="Peak",MIN('00_Inputs'!$B$13,J21*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="40">
         <f>J21+H22-I22/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K22" s="46">
+      <c r="K22" s="49">
         <f>J22/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="47">
+      <c r="L22" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N22" s="34" t="str">
+      <c r="N22" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="33">
+      <c r="A23" s="36">
         <v>2</v>
       </c>
-      <c r="B23" s="34" t="str">
+      <c r="B23" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A23+1,'00_Inputs'!$B$7)</f>
         <v>3.7</v>
       </c>
@@ -2584,52 +2767,52 @@
         <f>'00_Inputs'!$B$16*IF(B23="Peak",'00_Inputs'!$B$17,IF(B23="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="48">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G23" s="45">
+      <c r="G23" s="48">
         <f>IF(B23="Peak",0,IF(AND(F23&lt;=$C$7,D23&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="37">
+      <c r="H23" s="40">
         <f>IF(G23=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H22))),0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="40">
         <f>IF(B23="Peak",MIN('00_Inputs'!$B$13,J22*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="40">
         <f>J22+H23-I23/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K23" s="46">
+      <c r="K23" s="49">
         <f>J23/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L23" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="47">
+      <c r="L23" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N23" s="34" t="str">
+      <c r="N23" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="33">
+      <c r="A24" s="36">
         <v>3</v>
       </c>
-      <c r="B24" s="34" t="str">
+      <c r="B24" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A24+1,'00_Inputs'!$B$7)</f>
         <v>3.6</v>
       </c>
@@ -2641,52 +2824,52 @@
         <f>'00_Inputs'!$B$16*IF(B24="Peak",'00_Inputs'!$B$17,IF(B24="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F24" s="45">
+      <c r="F24" s="48">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="48">
         <f>IF(B24="Peak",0,IF(AND(F24&lt;=$C$7,D24&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="40">
         <f>IF(G24=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H23))),0)</f>
         <v>8</v>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="40">
         <f>IF(B24="Peak",MIN('00_Inputs'!$B$13,J23*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="40">
         <f>J23+H24-I24/'00_Inputs'!$B$12</f>
         <v>8</v>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="49">
         <f>J24/'00_Inputs'!$B$14</f>
-        <v>0.11594202898550725</v>
-      </c>
-      <c r="L24" s="47">
+        <v>0.11392203868318515</v>
+      </c>
+      <c r="L24" s="50">
         <f t="shared" si="2"/>
         <v>58000</v>
       </c>
-      <c r="M24" s="47">
+      <c r="M24" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N24" s="34" t="str">
+      <c r="N24" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="33">
+      <c r="A25" s="36">
         <v>4</v>
       </c>
-      <c r="B25" s="34" t="str">
+      <c r="B25" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A25+1,'00_Inputs'!$B$7)</f>
         <v>3.5</v>
       </c>
@@ -2698,52 +2881,52 @@
         <f>'00_Inputs'!$B$16*IF(B25="Peak",'00_Inputs'!$B$17,IF(B25="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="48">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G25" s="45">
+      <c r="G25" s="48">
         <f>IF(B25="Peak",0,IF(AND(F25&lt;=$C$7,D25&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="40">
         <f>IF(G25=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H24))),0)</f>
         <v>8</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="40">
         <f>IF(B25="Peak",MIN('00_Inputs'!$B$13,J24*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="40">
         <f>J24+H25-I25/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="49">
         <f>J25/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L25" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L25" s="50">
         <f t="shared" si="2"/>
         <v>57200</v>
       </c>
-      <c r="M25" s="47">
+      <c r="M25" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N25" s="34" t="str">
+      <c r="N25" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="33">
+      <c r="A26" s="36">
         <v>5</v>
       </c>
-      <c r="B26" s="34" t="str">
+      <c r="B26" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A26+1,'00_Inputs'!$B$7)</f>
         <v>3.8</v>
       </c>
@@ -2755,52 +2938,52 @@
         <f>'00_Inputs'!$B$16*IF(B26="Peak",'00_Inputs'!$B$17,IF(B26="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F26" s="45">
+      <c r="F26" s="48">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G26" s="45">
+      <c r="G26" s="48">
         <f>IF(B26="Peak",0,IF(AND(F26&lt;=$C$7,D26&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="40">
         <f>IF(G26=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H25))),0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="40">
         <f>IF(B26="Peak",MIN('00_Inputs'!$B$13,J25*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="40">
         <f>J25+H26-I26/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K26" s="46">
+      <c r="K26" s="49">
         <f>J26/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L26" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L26" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N26" s="34" t="str">
+      <c r="N26" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="33">
+      <c r="A27" s="36">
         <v>6</v>
       </c>
-      <c r="B27" s="34" t="str">
+      <c r="B27" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A27+1,'00_Inputs'!$B$7)</f>
         <v>4.5999999999999996</v>
       </c>
@@ -2812,52 +2995,52 @@
         <f>'00_Inputs'!$B$16*IF(B27="Peak",'00_Inputs'!$B$17,IF(B27="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="48">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="48">
         <f>IF(B27="Peak",0,IF(AND(F27&lt;=$C$7,D27&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="37">
+      <c r="H27" s="40">
         <f>IF(G27=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H26))),0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="40">
         <f>IF(B27="Peak",MIN('00_Inputs'!$B$13,J26*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="40">
         <f>J26+H27-I27/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="49">
         <f>J27/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L27" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L27" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N27" s="34" t="str">
+      <c r="N27" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="33">
+      <c r="A28" s="36">
         <v>7</v>
       </c>
-      <c r="B28" s="34" t="str">
+      <c r="B28" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A28+1,'00_Inputs'!$B$7)</f>
         <v>5.4</v>
       </c>
@@ -2869,52 +3052,52 @@
         <f>'00_Inputs'!$B$16*IF(B28="Peak",'00_Inputs'!$B$17,IF(B28="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F28" s="45">
+      <c r="F28" s="48">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G28" s="45">
+      <c r="G28" s="48">
         <f>IF(B28="Peak",0,IF(AND(F28&lt;=$C$7,D28&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="40">
         <f>IF(G28=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H27))),0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="40">
         <f>IF(B28="Peak",MIN('00_Inputs'!$B$13,J27*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="40">
         <f>J27+H28-I28/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K28" s="46">
+      <c r="K28" s="49">
         <f>J28/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L28" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L28" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N28" s="34" t="str">
+      <c r="N28" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="33">
+      <c r="A29" s="36">
         <v>8</v>
       </c>
-      <c r="B29" s="34" t="str">
+      <c r="B29" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A29+1,'00_Inputs'!$B$7)</f>
         <v>5.2</v>
       </c>
@@ -2926,52 +3109,52 @@
         <f>'00_Inputs'!$B$16*IF(B29="Peak",'00_Inputs'!$B$17,IF(B29="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F29" s="45">
+      <c r="F29" s="48">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G29" s="45">
+      <c r="G29" s="48">
         <f>IF(B29="Peak",0,IF(AND(F29&lt;=$C$7,D29&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="37">
+      <c r="H29" s="40">
         <f>IF(G29=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H28))),0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="40">
         <f>IF(B29="Peak",MIN('00_Inputs'!$B$13,J28*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="40">
         <f>J28+H29-I29/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="49">
         <f>J29/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L29" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L29" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N29" s="34" t="str">
+      <c r="N29" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="33">
+      <c r="A30" s="36">
         <v>9</v>
       </c>
-      <c r="B30" s="34" t="str">
+      <c r="B30" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A30+1,'00_Inputs'!$B$7)</f>
         <v>4</v>
       </c>
@@ -2983,52 +3166,52 @@
         <f>'00_Inputs'!$B$16*IF(B30="Peak",'00_Inputs'!$B$17,IF(B30="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F30" s="45">
+      <c r="F30" s="48">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G30" s="45">
+      <c r="G30" s="48">
         <f>IF(B30="Peak",0,IF(AND(F30&lt;=$C$7,D30&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="40">
         <f>IF(G30=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H29))),0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="40">
         <f>IF(B30="Peak",MIN('00_Inputs'!$B$13,J29*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="40">
         <f>J29+H30-I30/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="49">
         <f>J30/'00_Inputs'!$B$14</f>
-        <v>0.2318840579710145</v>
-      </c>
-      <c r="L30" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="47">
+        <v>0.2278440773663703</v>
+      </c>
+      <c r="L30" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="34" t="str">
+      <c r="N30" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="33">
+      <c r="A31" s="36">
         <v>10</v>
       </c>
-      <c r="B31" s="34" t="str">
+      <c r="B31" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A31+1,'00_Inputs'!$B$7)</f>
         <v>3</v>
       </c>
@@ -3040,52 +3223,52 @@
         <f>'00_Inputs'!$B$16*IF(B31="Peak",'00_Inputs'!$B$17,IF(B31="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F31" s="45">
+      <c r="F31" s="48">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G31" s="45">
+      <c r="G31" s="48">
         <f>IF(B31="Peak",0,IF(AND(F31&lt;=$C$7,D31&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="40">
         <f>IF(G31=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H30))),0)</f>
         <v>8</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="40">
         <f>IF(B31="Peak",MIN('00_Inputs'!$B$13,J30*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="40">
         <f>J30+H31-I31/'00_Inputs'!$B$12</f>
         <v>24</v>
       </c>
-      <c r="K31" s="46">
+      <c r="K31" s="49">
         <f>J31/'00_Inputs'!$B$14</f>
-        <v>0.34782608695652173</v>
-      </c>
-      <c r="L31" s="47">
+        <v>0.34176611604955548</v>
+      </c>
+      <c r="L31" s="50">
         <f t="shared" si="2"/>
         <v>53200</v>
       </c>
-      <c r="M31" s="47">
+      <c r="M31" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N31" s="34" t="str">
+      <c r="N31" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="33">
+      <c r="A32" s="36">
         <v>11</v>
       </c>
-      <c r="B32" s="34" t="str">
+      <c r="B32" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A32+1,'00_Inputs'!$B$7)</f>
         <v>2.6</v>
       </c>
@@ -3097,52 +3280,52 @@
         <f>'00_Inputs'!$B$16*IF(B32="Peak",'00_Inputs'!$B$17,IF(B32="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F32" s="45">
+      <c r="F32" s="48">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G32" s="45">
+      <c r="G32" s="48">
         <f>IF(B32="Peak",0,IF(AND(F32&lt;=$C$7,D32&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H32" s="37">
+      <c r="H32" s="40">
         <f>IF(G32=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H31))),0)</f>
         <v>8</v>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="40">
         <f>IF(B32="Peak",MIN('00_Inputs'!$B$13,J31*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="37">
+      <c r="J32" s="40">
         <f>J31+H32-I32/'00_Inputs'!$B$12</f>
         <v>32</v>
       </c>
-      <c r="K32" s="46">
+      <c r="K32" s="49">
         <f>J32/'00_Inputs'!$B$14</f>
-        <v>0.46376811594202899</v>
-      </c>
-      <c r="L32" s="47">
+        <v>0.4556881547327406</v>
+      </c>
+      <c r="L32" s="50">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N32" s="34" t="str">
+      <c r="N32" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="33">
+      <c r="A33" s="36">
         <v>12</v>
       </c>
-      <c r="B33" s="34" t="str">
+      <c r="B33" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A33+1,'00_Inputs'!$B$7)</f>
         <v>2.4</v>
       </c>
@@ -3154,52 +3337,52 @@
         <f>'00_Inputs'!$B$16*IF(B33="Peak",'00_Inputs'!$B$17,IF(B33="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F33" s="45">
+      <c r="F33" s="48">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G33" s="45">
+      <c r="G33" s="48">
         <f>IF(B33="Peak",0,IF(AND(F33&lt;=$C$7,D33&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H33" s="37">
+      <c r="H33" s="40">
         <f>IF(G33=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H32))),0)</f>
         <v>8</v>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="40">
         <f>IF(B33="Peak",MIN('00_Inputs'!$B$13,J32*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="40">
         <f>J32+H33-I33/'00_Inputs'!$B$12</f>
         <v>40</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K33" s="49">
         <f>J33/'00_Inputs'!$B$14</f>
-        <v>0.57971014492753625</v>
-      </c>
-      <c r="L33" s="47">
+        <v>0.56961019341592578</v>
+      </c>
+      <c r="L33" s="50">
         <f t="shared" si="2"/>
         <v>48400</v>
       </c>
-      <c r="M33" s="47">
+      <c r="M33" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N33" s="34" t="str">
+      <c r="N33" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="33">
+      <c r="A34" s="36">
         <v>13</v>
       </c>
-      <c r="B34" s="34" t="str">
+      <c r="B34" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A34+1,'00_Inputs'!$B$7)</f>
         <v>2.4</v>
       </c>
@@ -3211,52 +3394,52 @@
         <f>'00_Inputs'!$B$16*IF(B34="Peak",'00_Inputs'!$B$17,IF(B34="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F34" s="45">
+      <c r="F34" s="48">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G34" s="45">
+      <c r="G34" s="48">
         <f>IF(B34="Peak",0,IF(AND(F34&lt;=$C$7,D34&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H34" s="37">
+      <c r="H34" s="40">
         <f>IF(G34=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H33))),0)</f>
         <v>8</v>
       </c>
-      <c r="I34" s="37">
+      <c r="I34" s="40">
         <f>IF(B34="Peak",MIN('00_Inputs'!$B$13,J33*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="40">
         <f>J33+H34-I34/'00_Inputs'!$B$12</f>
         <v>48</v>
       </c>
-      <c r="K34" s="46">
+      <c r="K34" s="49">
         <f>J34/'00_Inputs'!$B$14</f>
-        <v>0.69565217391304346</v>
-      </c>
-      <c r="L34" s="47">
+        <v>0.68353223209911096</v>
+      </c>
+      <c r="L34" s="50">
         <f t="shared" si="2"/>
         <v>48400</v>
       </c>
-      <c r="M34" s="47">
+      <c r="M34" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N34" s="34" t="str">
+      <c r="N34" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="33">
+      <c r="A35" s="36">
         <v>14</v>
       </c>
-      <c r="B35" s="34" t="str">
+      <c r="B35" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A35+1,'00_Inputs'!$B$7)</f>
         <v>2.6</v>
       </c>
@@ -3268,52 +3451,52 @@
         <f>'00_Inputs'!$B$16*IF(B35="Peak",'00_Inputs'!$B$17,IF(B35="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F35" s="45">
+      <c r="F35" s="48">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G35" s="45">
+      <c r="G35" s="48">
         <f>IF(B35="Peak",0,IF(AND(F35&lt;=$C$7,D35&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H35" s="37">
+      <c r="H35" s="40">
         <f>IF(G35=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H34))),0)</f>
         <v>8</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="40">
         <f>IF(B35="Peak",MIN('00_Inputs'!$B$13,J34*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="40">
         <f>J34+H35-I35/'00_Inputs'!$B$12</f>
         <v>56</v>
       </c>
-      <c r="K35" s="46">
+      <c r="K35" s="49">
         <f>J35/'00_Inputs'!$B$14</f>
-        <v>0.81159420289855078</v>
-      </c>
-      <c r="L35" s="47">
+        <v>0.79745427078229603</v>
+      </c>
+      <c r="L35" s="50">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M35" s="47">
+      <c r="M35" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="34" t="str">
+      <c r="N35" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="33">
+      <c r="A36" s="36">
         <v>15</v>
       </c>
-      <c r="B36" s="34" t="str">
+      <c r="B36" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A36+1,'00_Inputs'!$B$7)</f>
         <v>3.1</v>
       </c>
@@ -3325,52 +3508,52 @@
         <f>'00_Inputs'!$B$16*IF(B36="Peak",'00_Inputs'!$B$17,IF(B36="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F36" s="45">
+      <c r="F36" s="48">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="G36" s="45">
+      <c r="G36" s="48">
         <f>IF(B36="Peak",0,IF(AND(F36&lt;=$C$7,D36&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H36" s="37">
+      <c r="H36" s="40">
         <f>IF(G36=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H35))),0)</f>
         <v>7.6363636363636331</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="40">
         <f>IF(B36="Peak",MIN('00_Inputs'!$B$13,J35*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="37">
+      <c r="J36" s="40">
         <f>J35+H36-I36/'00_Inputs'!$B$12</f>
         <v>63.636363636363633</v>
       </c>
-      <c r="K36" s="46">
+      <c r="K36" s="49">
         <f>J36/'00_Inputs'!$B$14</f>
-        <v>0.92226613965744397</v>
-      </c>
-      <c r="L36" s="47">
+        <v>0.90619803497988183</v>
+      </c>
+      <c r="L36" s="50">
         <f t="shared" si="2"/>
         <v>51545.454545454522</v>
       </c>
-      <c r="M36" s="47">
+      <c r="M36" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N36" s="34" t="str">
+      <c r="N36" s="37" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="33">
+      <c r="A37" s="36">
         <v>16</v>
       </c>
-      <c r="B37" s="34" t="str">
+      <c r="B37" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A37+1,'00_Inputs'!$B$7)</f>
         <v>4</v>
       </c>
@@ -3382,52 +3565,52 @@
         <f>'00_Inputs'!$B$16*IF(B37="Peak",'00_Inputs'!$B$17,IF(B37="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F37" s="45">
+      <c r="F37" s="48">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G37" s="45">
+      <c r="G37" s="48">
         <f>IF(B37="Peak",0,IF(AND(F37&lt;=$C$7,D37&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H37" s="37">
+      <c r="H37" s="40">
         <f>IF(G37=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H36))),0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="37">
+      <c r="I37" s="40">
         <f>IF(B37="Peak",MIN('00_Inputs'!$B$13,J36*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="37">
+      <c r="J37" s="40">
         <f>J36+H37-I37/'00_Inputs'!$B$12</f>
         <v>63.636363636363633</v>
       </c>
-      <c r="K37" s="46">
+      <c r="K37" s="49">
         <f>J37/'00_Inputs'!$B$14</f>
-        <v>0.92226613965744397</v>
-      </c>
-      <c r="L37" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="47">
+        <v>0.90619803497988183</v>
+      </c>
+      <c r="L37" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N37" s="34" t="str">
+      <c r="N37" s="37" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="33">
+      <c r="A38" s="36">
         <v>17</v>
       </c>
-      <c r="B38" s="34" t="str">
+      <c r="B38" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A38+1,'00_Inputs'!$B$7)</f>
         <v>5.6</v>
       </c>
@@ -3439,52 +3622,52 @@
         <f>'00_Inputs'!$B$16*IF(B38="Peak",'00_Inputs'!$B$17,IF(B38="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F38" s="45" t="str">
+      <c r="F38" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="45">
+      <c r="G38" s="48">
         <f>IF(B38="Peak",0,IF(AND(F38&lt;=$C$7,D38&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="37">
+      <c r="H38" s="40">
         <f>IF(G38=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H37))),0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="37">
+      <c r="I38" s="40">
         <f>IF(B38="Peak",MIN('00_Inputs'!$B$13,J37*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J38" s="37">
+      <c r="J38" s="40">
         <f>J37+H38-I38/'00_Inputs'!$B$12</f>
         <v>54.54545454545454</v>
       </c>
-      <c r="K38" s="46">
+      <c r="K38" s="49">
         <f>J38/'00_Inputs'!$B$14</f>
-        <v>0.79051383399209474</v>
-      </c>
-      <c r="L38" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="47">
+        <v>0.77674117283989874</v>
+      </c>
+      <c r="L38" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N38" s="34" t="str">
+      <c r="N38" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="33">
+      <c r="A39" s="36">
         <v>18</v>
       </c>
-      <c r="B39" s="34" t="str">
+      <c r="B39" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A39+1,'00_Inputs'!$B$7)</f>
         <v>7.2</v>
       </c>
@@ -3496,52 +3679,52 @@
         <f>'00_Inputs'!$B$16*IF(B39="Peak",'00_Inputs'!$B$17,IF(B39="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F39" s="45" t="str">
+      <c r="F39" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="45">
+      <c r="G39" s="48">
         <f>IF(B39="Peak",0,IF(AND(F39&lt;=$C$7,D39&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="37">
+      <c r="H39" s="40">
         <f>IF(G39=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H38))),0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="37">
+      <c r="I39" s="40">
         <f>IF(B39="Peak",MIN('00_Inputs'!$B$13,J38*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J39" s="37">
+      <c r="J39" s="40">
         <f>J38+H39-I39/'00_Inputs'!$B$12</f>
         <v>45.454545454545446</v>
       </c>
-      <c r="K39" s="46">
+      <c r="K39" s="49">
         <f>J39/'00_Inputs'!$B$14</f>
-        <v>0.65876152832674562</v>
-      </c>
-      <c r="L39" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="47">
+        <v>0.64728431069991554</v>
+      </c>
+      <c r="L39" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N39" s="34" t="str">
+      <c r="N39" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="33">
+      <c r="A40" s="36">
         <v>19</v>
       </c>
-      <c r="B40" s="34" t="str">
+      <c r="B40" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A40+1,'00_Inputs'!$B$7)</f>
         <v>8.5</v>
       </c>
@@ -3553,52 +3736,52 @@
         <f>'00_Inputs'!$B$16*IF(B40="Peak",'00_Inputs'!$B$17,IF(B40="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F40" s="45" t="str">
+      <c r="F40" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="45">
+      <c r="G40" s="48">
         <f>IF(B40="Peak",0,IF(AND(F40&lt;=$C$7,D40&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H40" s="37">
+      <c r="H40" s="40">
         <f>IF(G40=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H39))),0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="37">
+      <c r="I40" s="40">
         <f>IF(B40="Peak",MIN('00_Inputs'!$B$13,J39*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J40" s="37">
+      <c r="J40" s="40">
         <f>J39+H40-I40/'00_Inputs'!$B$12</f>
         <v>36.363636363636353</v>
       </c>
-      <c r="K40" s="46">
+      <c r="K40" s="49">
         <f>J40/'00_Inputs'!$B$14</f>
-        <v>0.52700922266139638</v>
-      </c>
-      <c r="L40" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="47">
+        <v>0.51782744855993235</v>
+      </c>
+      <c r="L40" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N40" s="34" t="str">
+      <c r="N40" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="33">
+      <c r="A41" s="36">
         <v>20</v>
       </c>
-      <c r="B41" s="34" t="str">
+      <c r="B41" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C41" s="44">
+      <c r="C41" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A41+1,'00_Inputs'!$B$7)</f>
         <v>8.9</v>
       </c>
@@ -3610,52 +3793,52 @@
         <f>'00_Inputs'!$B$16*IF(B41="Peak",'00_Inputs'!$B$17,IF(B41="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F41" s="45" t="str">
+      <c r="F41" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="45">
+      <c r="G41" s="48">
         <f>IF(B41="Peak",0,IF(AND(F41&lt;=$C$7,D41&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H41" s="37">
+      <c r="H41" s="40">
         <f>IF(G41=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H40))),0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="37">
+      <c r="I41" s="40">
         <f>IF(B41="Peak",MIN('00_Inputs'!$B$13,J40*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J41" s="37">
+      <c r="J41" s="40">
         <f>J40+H41-I41/'00_Inputs'!$B$12</f>
         <v>27.272727272727259</v>
       </c>
-      <c r="K41" s="46">
+      <c r="K41" s="49">
         <f>J41/'00_Inputs'!$B$14</f>
-        <v>0.39525691699604726</v>
-      </c>
-      <c r="L41" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="47">
+        <v>0.3883705864199492</v>
+      </c>
+      <c r="L41" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N41" s="34" t="str">
+      <c r="N41" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="33">
+      <c r="A42" s="36">
         <v>21</v>
       </c>
-      <c r="B42" s="34" t="str">
+      <c r="B42" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C42" s="44">
+      <c r="C42" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A42+1,'00_Inputs'!$B$7)</f>
         <v>7.8</v>
       </c>
@@ -3667,52 +3850,52 @@
         <f>'00_Inputs'!$B$16*IF(B42="Peak",'00_Inputs'!$B$17,IF(B42="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F42" s="45" t="str">
+      <c r="F42" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="45">
+      <c r="G42" s="48">
         <f>IF(B42="Peak",0,IF(AND(F42&lt;=$C$7,D42&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H42" s="37">
+      <c r="H42" s="40">
         <f>IF(G42=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H41))),0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="40">
         <f>IF(B42="Peak",MIN('00_Inputs'!$B$13,J41*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J42" s="37">
+      <c r="J42" s="40">
         <f>J41+H42-I42/'00_Inputs'!$B$12</f>
         <v>18.181818181818166</v>
       </c>
-      <c r="K42" s="46">
+      <c r="K42" s="49">
         <f>J42/'00_Inputs'!$B$14</f>
-        <v>0.26350461133069808</v>
-      </c>
-      <c r="L42" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="47">
+        <v>0.25891372427996601</v>
+      </c>
+      <c r="L42" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N42" s="34" t="str">
+      <c r="N42" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="33">
+      <c r="A43" s="36">
         <v>22</v>
       </c>
-      <c r="B43" s="34" t="str">
+      <c r="B43" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A43+1,'00_Inputs'!$B$7)</f>
         <v>6.2</v>
       </c>
@@ -3724,52 +3907,52 @@
         <f>'00_Inputs'!$B$16*IF(B43="Peak",'00_Inputs'!$B$17,IF(B43="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F43" s="45" t="str">
+      <c r="F43" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="45">
+      <c r="G43" s="48">
         <f>IF(B43="Peak",0,IF(AND(F43&lt;=$C$7,D43&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H43" s="37">
+      <c r="H43" s="40">
         <f>IF(G43=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H42))),0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="37">
+      <c r="I43" s="40">
         <f>IF(B43="Peak",MIN('00_Inputs'!$B$13,J42*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J43" s="37">
+      <c r="J43" s="40">
         <f>J42+H43-I43/'00_Inputs'!$B$12</f>
         <v>9.090909090909074</v>
       </c>
-      <c r="K43" s="46">
+      <c r="K43" s="49">
         <f>J43/'00_Inputs'!$B$14</f>
-        <v>0.1317523056653489</v>
-      </c>
-      <c r="L43" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="47">
+        <v>0.12945686213998289</v>
+      </c>
+      <c r="L43" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N43" s="34" t="str">
+      <c r="N43" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="33">
+      <c r="A44" s="36">
         <v>23</v>
       </c>
-      <c r="B44" s="34" t="str">
+      <c r="B44" s="37" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="47">
         <f>INDEX(Prices!$B$2:$D$25,A44+1,'00_Inputs'!$B$7)</f>
         <v>5</v>
       </c>
@@ -3781,46 +3964,46 @@
         <f>'00_Inputs'!$B$16*IF(B44="Peak",'00_Inputs'!$B$17,IF(B44="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F44" s="45" t="str">
+      <c r="F44" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="45">
+      <c r="G44" s="48">
         <f>IF(B44="Peak",0,IF(AND(F44&lt;=$C$7,D44&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H44" s="37">
+      <c r="H44" s="40">
         <f>IF(G44=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H43))),0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="40">
         <f>IF(B44="Peak",MIN('00_Inputs'!$B$13,J43*'00_Inputs'!$B$12),0)</f>
         <v>7.9999999999999849</v>
       </c>
-      <c r="J44" s="37">
+      <c r="J44" s="40">
         <f>J43+H44-I44/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K44" s="46">
+      <c r="K44" s="49">
         <f>J44/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L44" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="47">
+      <c r="L44" s="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="50">
         <f t="shared" si="3"/>
         <v>81023.999999999825</v>
       </c>
-      <c r="N44" s="34" t="str">
+      <c r="N44" s="37" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3840,17 +4023,17 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -3858,55 +4041,55 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="41">
+        <v>125</v>
+      </c>
+      <c r="B5" s="44">
         <f>C24</f>
-        <v>8.0333189999999917</v>
+        <v>8.0121225139199908</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="29">
+        <v>126</v>
+      </c>
+      <c r="B6" s="32">
         <f>'00_Inputs'!$B$14*'00_Inputs'!$B$30*1.05</f>
-        <v>79.695000000000007</v>
+        <v>81.10809907200003</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="31" t="str">
+        <v>128</v>
+      </c>
+      <c r="B7" s="34" t="str">
         <f>IF(N25&gt;=0,"Y"&amp;(COUNTIF($C$25:$N$25,"&lt;0")+1),"&gt;12 yrs")</f>
         <v>Y12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="48">
+        <v>129</v>
+      </c>
+      <c r="B8" s="51">
         <f>IFERROR(IRR(B24:N24),"n/a")</f>
-        <v>1.1651251084825232E-2</v>
+        <v>8.0952091901571599E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="29">
+        <v>130</v>
+      </c>
+      <c r="B9" s="32">
         <f>B24+NPV('00_Inputs'!$B$34,C24:N24)</f>
-        <v>-34.167688392964187</v>
+        <v>-35.744015066846572</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -3914,67 +4097,67 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="49">
+        <v>132</v>
+      </c>
+      <c r="B12" s="52">
         <f>'02_Dispatch'!$C$13</f>
         <v>4.9639439999999926</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="29">
+        <v>133</v>
+      </c>
+      <c r="B13" s="32">
         <f>'00_Inputs'!$B$36*'00_Inputs'!$B$37*12/10000000</f>
         <v>2.7</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="29">
+        <v>135</v>
+      </c>
+      <c r="B14" s="32">
         <f>'00_Inputs'!$B$38*'00_Inputs'!$B$13*1000*('00_Inputs'!$B$39-'00_Inputs'!$B$16)/10000000</f>
         <v>1.5648000000000002</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="50">
+      <c r="A15" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="53">
         <f>SUM(B12:B14)</f>
         <v>9.2287439999999936</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="29">
+        <v>138</v>
+      </c>
+      <c r="B16" s="32">
         <f>-B6*'00_Inputs'!$B$31</f>
-        <v>-1.195425</v>
+        <v>-1.2166214860800004</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="50">
+      <c r="A17" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="53">
         <f>B15+B16</f>
-        <v>8.0333189999999934</v>
+        <v>8.0121225139199925</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -3992,325 +4175,325 @@
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="H20" s="32" t="s">
+      <c r="A20" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="B20" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="C20" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K20" s="32" t="s">
+      <c r="D20" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="L20" s="32" t="s">
+      <c r="E20" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="F20" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="N20" s="32" t="s">
+      <c r="G20" s="35" t="s">
         <v>147</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="M20" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="N20" s="35" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" s="51">
+        <v>155</v>
+      </c>
+      <c r="C21" s="54">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(1-1)</f>
         <v>4.9639439999999926</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(2-1)</f>
         <v>4.8646651199999926</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(3-1)</f>
         <v>4.7673718175999928</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(4-1)</f>
         <v>4.6720243812479927</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(5-1)</f>
         <v>4.5785838936230325</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(6-1)</f>
         <v>4.4870122157505712</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(7-1)</f>
         <v>4.3972719714355604</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(8-1)</f>
         <v>4.3093265320068488</v>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(9-1)</f>
         <v>4.223140001366712</v>
       </c>
-      <c r="L21" s="52">
+      <c r="L21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(10-1)</f>
         <v>4.1386772013393776</v>
       </c>
-      <c r="M21" s="52">
+      <c r="M21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(11-1)</f>
         <v>4.0559036573125891</v>
       </c>
-      <c r="N21" s="52">
+      <c r="N21" s="55">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(12-1)</f>
         <v>3.9747855841663378</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="52">
+        <v>156</v>
+      </c>
+      <c r="C22" s="55">
         <f t="shared" ref="C22:N22" si="0">$B$13+$B$14</f>
         <v>4.2648000000000001</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="I22" s="52">
+      <c r="I22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="J22" s="52">
+      <c r="J22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="K22" s="52">
+      <c r="K22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="L22" s="52">
+      <c r="L22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="M22" s="52">
+      <c r="M22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="N22" s="52">
+      <c r="N22" s="55">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" s="52">
+        <v>157</v>
+      </c>
+      <c r="C23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(1-1)</f>
-        <v>-1.195425</v>
-      </c>
-      <c r="D23" s="52">
+        <v>-1.2166214860800004</v>
+      </c>
+      <c r="D23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(2-1)</f>
-        <v>-1.25519625</v>
-      </c>
-      <c r="E23" s="52">
+        <v>-1.2774525603840006</v>
+      </c>
+      <c r="E23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(3-1)</f>
-        <v>-1.3179560625</v>
-      </c>
-      <c r="F23" s="52">
+        <v>-1.3413251884032005</v>
+      </c>
+      <c r="F23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(4-1)</f>
-        <v>-1.3838538656250001</v>
-      </c>
-      <c r="G23" s="52">
+        <v>-1.4083914478233606</v>
+      </c>
+      <c r="G23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(5-1)</f>
-        <v>-1.45304655890625</v>
-      </c>
-      <c r="H23" s="52">
+        <v>-1.4788110202145286</v>
+      </c>
+      <c r="H23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(6-1)</f>
-        <v>-1.5256988868515626</v>
-      </c>
-      <c r="I23" s="52">
+        <v>-1.5527515712252551</v>
+      </c>
+      <c r="I23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(7-1)</f>
-        <v>-1.6019838311941406</v>
-      </c>
-      <c r="J23" s="52">
+        <v>-1.6303891497865177</v>
+      </c>
+      <c r="J23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(8-1)</f>
-        <v>-1.6820830227538479</v>
-      </c>
-      <c r="K23" s="52">
+        <v>-1.7119086072758438</v>
+      </c>
+      <c r="K23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(9-1)</f>
-        <v>-1.76618717389154</v>
-      </c>
-      <c r="L23" s="52">
+        <v>-1.7975040376396358</v>
+      </c>
+      <c r="L23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(10-1)</f>
-        <v>-1.8544965325861171</v>
-      </c>
-      <c r="M23" s="52">
+        <v>-1.8873792395216178</v>
+      </c>
+      <c r="M23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(11-1)</f>
-        <v>-1.9472213592154231</v>
-      </c>
-      <c r="N23" s="52">
+        <v>-1.9817482014976986</v>
+      </c>
+      <c r="N23" s="55">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(12-1)</f>
-        <v>-2.0445824271761945</v>
+        <v>-2.0808356115725837</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="52">
+      <c r="A24" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="55">
         <f>-B6</f>
-        <v>-79.695000000000007</v>
-      </c>
-      <c r="C24" s="53">
+        <v>-81.10809907200003</v>
+      </c>
+      <c r="C24" s="56">
         <f t="shared" ref="C24:N24" si="1">C21+C22+C23</f>
-        <v>8.0333189999999917</v>
-      </c>
-      <c r="D24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.8742688699999919</v>
-      </c>
-      <c r="E24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.7142157550999926</v>
-      </c>
-      <c r="F24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.5529705156229925</v>
-      </c>
-      <c r="G24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.3903373347167829</v>
-      </c>
-      <c r="H24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.2261133288990091</v>
-      </c>
-      <c r="I24" s="53">
-        <f t="shared" si="1"/>
-        <v>7.0600881402414197</v>
-      </c>
-      <c r="J24" s="53">
-        <f t="shared" si="1"/>
-        <v>6.8920435092530008</v>
-      </c>
-      <c r="K24" s="53">
-        <f t="shared" si="1"/>
-        <v>6.7217528274751732</v>
-      </c>
-      <c r="L24" s="53">
-        <f t="shared" si="1"/>
-        <v>6.548980668753261</v>
-      </c>
-      <c r="M24" s="53">
-        <f t="shared" si="1"/>
-        <v>6.3734822980971657</v>
-      </c>
-      <c r="N24" s="53">
-        <f t="shared" si="1"/>
-        <v>6.1950031569901434</v>
+        <v>8.0121225139199908</v>
+      </c>
+      <c r="D24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.8520125596159911</v>
+      </c>
+      <c r="E24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.690846629196793</v>
+      </c>
+      <c r="F24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.5284329334246323</v>
+      </c>
+      <c r="G24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.3645728734085036</v>
+      </c>
+      <c r="H24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.1990606445253169</v>
+      </c>
+      <c r="I24" s="56">
+        <f t="shared" si="1"/>
+        <v>7.031682821649043</v>
+      </c>
+      <c r="J24" s="56">
+        <f t="shared" si="1"/>
+        <v>6.8622179247310049</v>
+      </c>
+      <c r="K24" s="56">
+        <f t="shared" si="1"/>
+        <v>6.6904359637270776</v>
+      </c>
+      <c r="L24" s="56">
+        <f t="shared" si="1"/>
+        <v>6.5160979618177599</v>
+      </c>
+      <c r="M24" s="56">
+        <f t="shared" si="1"/>
+        <v>6.3389554558148902</v>
+      </c>
+      <c r="N24" s="56">
+        <f t="shared" si="1"/>
+        <v>6.1587499725937551</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="52">
+      <c r="A25" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="55">
         <f>B24</f>
-        <v>-79.695000000000007</v>
-      </c>
-      <c r="C25" s="53">
+        <v>-81.10809907200003</v>
+      </c>
+      <c r="C25" s="56">
         <f t="shared" ref="C25:N25" si="2">B25+C24</f>
-        <v>-71.661681000000016</v>
-      </c>
-      <c r="D25" s="53">
-        <f t="shared" si="2"/>
-        <v>-63.787412130000021</v>
-      </c>
-      <c r="E25" s="53">
-        <f t="shared" si="2"/>
-        <v>-56.073196374900029</v>
-      </c>
-      <c r="F25" s="53">
-        <f t="shared" si="2"/>
-        <v>-48.520225859277033</v>
-      </c>
-      <c r="G25" s="53">
-        <f t="shared" si="2"/>
-        <v>-41.129888524560251</v>
-      </c>
-      <c r="H25" s="53">
-        <f t="shared" si="2"/>
-        <v>-33.90377519566124</v>
-      </c>
-      <c r="I25" s="53">
-        <f t="shared" si="2"/>
-        <v>-26.843687055419821</v>
-      </c>
-      <c r="J25" s="53">
-        <f t="shared" si="2"/>
-        <v>-19.951643546166821</v>
-      </c>
-      <c r="K25" s="53">
-        <f t="shared" si="2"/>
-        <v>-13.229890718691648</v>
-      </c>
-      <c r="L25" s="53">
-        <f t="shared" si="2"/>
-        <v>-6.6809100499383867</v>
-      </c>
-      <c r="M25" s="53">
-        <f t="shared" si="2"/>
-        <v>-0.30742775184122095</v>
-      </c>
-      <c r="N25" s="53">
-        <f t="shared" si="2"/>
-        <v>5.8875754051489224</v>
+        <v>-73.095976558080039</v>
+      </c>
+      <c r="D25" s="56">
+        <f t="shared" si="2"/>
+        <v>-65.243963998464054</v>
+      </c>
+      <c r="E25" s="56">
+        <f t="shared" si="2"/>
+        <v>-57.553117369267262</v>
+      </c>
+      <c r="F25" s="56">
+        <f t="shared" si="2"/>
+        <v>-50.02468443584263</v>
+      </c>
+      <c r="G25" s="56">
+        <f t="shared" si="2"/>
+        <v>-42.660111562434125</v>
+      </c>
+      <c r="H25" s="56">
+        <f t="shared" si="2"/>
+        <v>-35.461050917908807</v>
+      </c>
+      <c r="I25" s="56">
+        <f t="shared" si="2"/>
+        <v>-28.429368096259765</v>
+      </c>
+      <c r="J25" s="56">
+        <f t="shared" si="2"/>
+        <v>-21.567150171528759</v>
+      </c>
+      <c r="K25" s="56">
+        <f t="shared" si="2"/>
+        <v>-14.876714207801681</v>
+      </c>
+      <c r="L25" s="56">
+        <f t="shared" si="2"/>
+        <v>-8.3606162459839215</v>
+      </c>
+      <c r="M25" s="56">
+        <f t="shared" si="2"/>
+        <v>-2.0216607901690313</v>
+      </c>
+      <c r="N25" s="56">
+        <f t="shared" si="2"/>
+        <v>4.1370891824247238</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4320,6 +4503,417 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="57">
+        <f>H13/1000</f>
+        <v>5.0159616000000007</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="58">
+        <f>C10*C11*C12*C13</f>
+        <v>4992</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="60">
+        <v>3.2</v>
+      </c>
+      <c r="F9" s="61">
+        <v>314</v>
+      </c>
+      <c r="G9" s="62">
+        <f>E9*F9</f>
+        <v>1004.8000000000001</v>
+      </c>
+      <c r="H9" s="63">
+        <f>G9/1000</f>
+        <v>1.0048000000000001</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="64">
+        <v>13</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="65">
+        <f>C10*E9</f>
+        <v>41.6</v>
+      </c>
+      <c r="F10" s="66">
+        <f>F9</f>
+        <v>314</v>
+      </c>
+      <c r="G10" s="62">
+        <f>G9*C10</f>
+        <v>13062.400000000001</v>
+      </c>
+      <c r="H10" s="40">
+        <f>G10/1000</f>
+        <v>13.062400000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="64">
+        <v>4</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="65">
+        <f>C11*E10</f>
+        <v>166.4</v>
+      </c>
+      <c r="F11" s="66">
+        <f>F10</f>
+        <v>314</v>
+      </c>
+      <c r="G11" s="62">
+        <f>G10*C11</f>
+        <v>52249.600000000006</v>
+      </c>
+      <c r="H11" s="40">
+        <f>G11/1000</f>
+        <v>52.249600000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="64">
+        <v>8</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="65">
+        <f>C12*E11</f>
+        <v>1331.2</v>
+      </c>
+      <c r="F12" s="66">
+        <f>F11</f>
+        <v>314</v>
+      </c>
+      <c r="G12" s="62">
+        <f>G11*C12</f>
+        <v>417996.80000000005</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12/1000</f>
+        <v>417.99680000000006</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="64">
+        <v>12</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="65">
+        <f>E12</f>
+        <v>1331.2</v>
+      </c>
+      <c r="F13" s="66">
+        <f>F12*C13</f>
+        <v>3768</v>
+      </c>
+      <c r="G13" s="68">
+        <f>G12*C13</f>
+        <v>5015961.6000000006</v>
+      </c>
+      <c r="H13" s="69">
+        <f>G13/1000</f>
+        <v>5015.9616000000005</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="64">
+        <v>13</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="65">
+        <f>C18*$E$9</f>
+        <v>41.6</v>
+      </c>
+      <c r="F18" s="66">
+        <f>$F$9</f>
+        <v>314</v>
+      </c>
+      <c r="G18" s="62">
+        <f>$G$9*C18</f>
+        <v>13062.400000000001</v>
+      </c>
+      <c r="H18" s="40">
+        <f>G18/1000</f>
+        <v>13.062400000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="64">
+        <v>8</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="65">
+        <f>C19*E18</f>
+        <v>332.8</v>
+      </c>
+      <c r="F19" s="66">
+        <f>F18</f>
+        <v>314</v>
+      </c>
+      <c r="G19" s="62">
+        <f>G18*C19</f>
+        <v>104499.20000000001</v>
+      </c>
+      <c r="H19" s="40">
+        <f>G19/1000</f>
+        <v>104.49920000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="64">
+        <v>8</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" s="65">
+        <f>C20*E19</f>
+        <v>2662.4</v>
+      </c>
+      <c r="F20" s="66">
+        <f>F19</f>
+        <v>314</v>
+      </c>
+      <c r="G20" s="62">
+        <f>G19*C20</f>
+        <v>835993.60000000009</v>
+      </c>
+      <c r="H20" s="40">
+        <f>G20/1000</f>
+        <v>835.99360000000013</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="64">
+        <v>6</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="65">
+        <f>E20</f>
+        <v>2662.4</v>
+      </c>
+      <c r="F21" s="66">
+        <f>F20*C21</f>
+        <v>1884</v>
+      </c>
+      <c r="G21" s="68">
+        <f>G20*C21</f>
+        <v>5015961.6000000006</v>
+      </c>
+      <c r="H21" s="69">
+        <f>G21/1000</f>
+        <v>5015.9616000000005</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4328,358 +4922,358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>156</v>
+      <c r="A1" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="33">
-        <v>0</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="A2" s="36">
+        <v>0</v>
+      </c>
+      <c r="B2" s="70">
         <v>4.2</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="70">
         <v>5</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="70">
         <v>3.8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="33">
+      <c r="A3" s="36">
         <v>1</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="70">
         <v>3.9</v>
       </c>
-      <c r="C3" s="54">
+      <c r="C3" s="70">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="70">
         <v>3.6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="33">
+      <c r="A4" s="36">
         <v>2</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="70">
         <v>3.7</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="70">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="70">
         <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="33">
+      <c r="A5" s="36">
         <v>3</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B5" s="70">
         <v>3.6</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="70">
         <v>4.3</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="70">
         <v>3.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="33">
+      <c r="A6" s="36">
         <v>4</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="70">
         <v>3.5</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="70">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="70">
         <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="33">
+      <c r="A7" s="36">
         <v>5</v>
       </c>
-      <c r="B7" s="54">
+      <c r="B7" s="70">
         <v>3.8</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="70">
         <v>4.8</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="70">
         <v>3.6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="33">
+      <c r="A8" s="36">
         <v>6</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="70">
         <v>4.5999999999999996</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="70">
         <v>5.8</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="70">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="33">
+      <c r="A9" s="36">
         <v>7</v>
       </c>
-      <c r="B9" s="54">
+      <c r="B9" s="70">
         <v>5.4</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="70">
         <v>6.8</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="70">
         <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="33">
+      <c r="A10" s="36">
         <v>8</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="70">
         <v>5.2</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="70">
         <v>6.2</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="70">
         <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="33">
+      <c r="A11" s="36">
         <v>9</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="70">
         <v>4</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="70">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="70">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="36">
         <v>10</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="70">
         <v>3</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="70">
         <v>3.2</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="70">
         <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="33">
+      <c r="A13" s="36">
         <v>11</v>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="70">
         <v>2.6</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="70">
         <v>2.6</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="70">
         <v>3.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="33">
+      <c r="A14" s="36">
         <v>12</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="70">
         <v>2.4</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="70">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="70">
         <v>3.4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="33">
+      <c r="A15" s="36">
         <v>13</v>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="70">
         <v>2.4</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="70">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="70">
         <v>3.4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="33">
+      <c r="A16" s="36">
         <v>14</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="70">
         <v>2.6</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="70">
         <v>2.5</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="70">
         <v>3.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="33">
+      <c r="A17" s="36">
         <v>15</v>
       </c>
-      <c r="B17" s="54">
+      <c r="B17" s="70">
         <v>3.1</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="70">
         <v>3.4</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="70">
         <v>3.7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="33">
+      <c r="A18" s="36">
         <v>16</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="70">
         <v>4</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="70">
         <v>5.2</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="70">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="33">
+      <c r="A19" s="36">
         <v>17</v>
       </c>
-      <c r="B19" s="54">
+      <c r="B19" s="70">
         <v>5.6</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="70">
         <v>7.4</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="70">
         <v>4.7</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="33">
+      <c r="A20" s="36">
         <v>18</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="70">
         <v>7.2</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="70">
         <v>9.6</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="70">
         <v>5.4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="33">
+      <c r="A21" s="36">
         <v>19</v>
       </c>
-      <c r="B21" s="54">
+      <c r="B21" s="70">
         <v>8.5</v>
       </c>
-      <c r="C21" s="54">
+      <c r="C21" s="70">
         <v>10</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="70">
         <v>5.8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="33">
+      <c r="A22" s="36">
         <v>20</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="70">
         <v>8.9</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="70">
         <v>10</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="70">
         <v>5.7</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="33">
+      <c r="A23" s="36">
         <v>21</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="70">
         <v>7.8</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="70">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="70">
         <v>5.2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="33">
+      <c r="A24" s="36">
         <v>22</v>
       </c>
-      <c r="B24" s="54">
+      <c r="B24" s="70">
         <v>6.2</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="70">
         <v>7.4</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="70">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="33">
+      <c r="A25" s="36">
         <v>23</v>
       </c>
-      <c r="B25" s="54">
+      <c r="B25" s="70">
         <v>5</v>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="70">
         <v>6</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="70">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/PowerLogic_BESS_Model.xlsx
+++ b/PowerLogic_BESS_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jai_PC\Desktop\BessArbitrageApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDE67D-0F40-4E30-A3AB-87D679DFE0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42293E2-87CB-4DEB-897A-64A7447D84BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="215">
   <si>
     <t>POWERLOGIC BESS · INDIAN POWER MARKET</t>
   </si>
@@ -253,6 +253,60 @@
   </si>
   <si>
     <t>Feasibility check</t>
+  </si>
+  <si>
+    <t>PCS CONFIGURATION — MARKET-AVAILABLE UNITS (1500 V DC CLASS)</t>
+  </si>
+  <si>
+    <t>PCS unit rating (MW)</t>
+  </si>
+  <si>
+    <t>Market blocks: 0.25 (string) · 1.25 · 2.5 (standard pair for a 5 MWh 0.5C container) · 3.45 · 5.0 MW skids</t>
+  </si>
+  <si>
+    <t>Redundant units (N+1 → enter 1)</t>
+  </si>
+  <si>
+    <t>PCS units required</t>
+  </si>
+  <si>
+    <t>PCS installed (MW)</t>
+  </si>
+  <si>
+    <t>System C-rate (PCS ÷ installed energy)</t>
+  </si>
+  <si>
+    <t>314 Ah / 5 MWh containers are 0.5C continuous products</t>
+  </si>
+  <si>
+    <t>CHARGING-CYCLE VALIDATION — INDIAN (MSEDCL) OPERATING DAY</t>
+  </si>
+  <si>
+    <t>Usable energy per cycle (MWh)</t>
+  </si>
+  <si>
+    <t>Installed × DoD</t>
+  </si>
+  <si>
+    <t>Peak-window demand to serve (MWh/day)</t>
+  </si>
+  <si>
+    <t>Cycles per day implied</t>
+  </si>
+  <si>
+    <t>LFP warranty ≈ 6,000–8,000 cycles: 1/day ≈ 18+ yrs, 2/day ≈ 9–10 yrs</t>
+  </si>
+  <si>
+    <t>Recharge need (MWh/day) vs solar-window capability</t>
+  </si>
+  <si>
+    <t>Cycle verdict</t>
+  </si>
+  <si>
+    <t>Containers if 2 cycles/day were usable</t>
+  </si>
+  <si>
+    <t>Needs a second premium window (dual-peak ToD states like UP/UK, or RTM stacking) — not available under MSEDCL's single 17–24 peak; second-cycle margin vs normal tariff ≈ ₹0.5–1.5/kWh only</t>
   </si>
   <si>
     <t>24-HOUR LOAD PROFILE</t>
@@ -622,7 +676,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="20">
+  <numFmts count="23">
     <numFmt numFmtId="164" formatCode="#,##0.0&quot; MW&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; MWh&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0&quot; MWh&quot;"/>
@@ -635,14 +689,17 @@
     <numFmt numFmtId="173" formatCode="0&quot; containers&quot;"/>
     <numFmt numFmtId="174" formatCode="0.0&quot; h&quot;"/>
     <numFmt numFmtId="175" formatCode="&quot;₹&quot;#,##0.0&quot; Cr&quot;;\(&quot;₹&quot;#,##0.0&quot; Cr&quot;\)"/>
-    <numFmt numFmtId="176" formatCode="00"/>
-    <numFmt numFmtId="177" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0&quot; cells&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0&quot; V&quot;"/>
-    <numFmt numFmtId="180" formatCode="#,##0&quot; Ah&quot;"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0"/>
-    <numFmt numFmtId="182" formatCode="#,##0.000"/>
-    <numFmt numFmtId="183" formatCode="#,##0.0&quot; V&quot;"/>
+    <numFmt numFmtId="176" formatCode="0&quot; units&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.00&quot;C&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.00&quot; /day&quot;"/>
+    <numFmt numFmtId="179" formatCode="00"/>
+    <numFmt numFmtId="180" formatCode="&quot;₹&quot;#,##0.00&quot; L&quot;"/>
+    <numFmt numFmtId="181" formatCode="#,##0&quot; cells&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.0&quot; V&quot;"/>
+    <numFmt numFmtId="183" formatCode="#,##0&quot; Ah&quot;"/>
+    <numFmt numFmtId="184" formatCode="#,##0.0"/>
+    <numFmt numFmtId="185" formatCode="#,##0.000"/>
+    <numFmt numFmtId="186" formatCode="#,##0.0&quot; V&quot;"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -746,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -781,11 +838,16 @@
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -796,7 +858,7 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -815,17 +877,17 @@
     <xf numFmtId="175" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="175" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="183" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1488,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1534,7 +1596,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="24">
-        <f>SUM($F$21:$F$44)</f>
+        <f>SUM($F$35:$F$58)</f>
         <v>63</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -1546,7 +1608,7 @@
         <v>57</v>
       </c>
       <c r="C7" s="24">
-        <f>SUM($H$21:$H$44)</f>
+        <f>SUM($H$35:$H$58)</f>
         <v>63</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -1570,7 +1632,7 @@
         <v>61</v>
       </c>
       <c r="C9" s="26">
-        <f>CEILING(MAX($F$21:$F$44)*C8,0.5)</f>
+        <f>CEILING(MAX($F$35:$F$58)*C8,0.5)</f>
         <v>8</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -1658,766 +1720,912 @@
         <v>CHECK — max feasible coverage = 88%. Raise contract demand, shed day load, or add on-site solar.</v>
       </c>
     </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="34" t="s">
-        <v>76</v>
+      <c r="A19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="18">
+        <v>2.5</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="35" t="s">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="C21" s="34">
+        <f>ROUNDUP(C9/C19,0)+C20</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="C22" s="35">
+        <f>C21*C19</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="C23" s="36">
+        <f>C22/C13</f>
+        <v>0.14240254835398145</v>
+      </c>
+      <c r="D23" s="6" t="str">
+        <f>IF(C23&lt;=0.5,"OK — within 0.5C container rating","CHECK — above the 0.5C rating of the 314 Ah container: add containers or smaller PCS")</f>
+        <v>OK — within 0.5C container rating</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="35" t="s">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="C26" s="24">
+        <f>C13*'00_Inputs'!$B$27</f>
+        <v>63.201116160000019</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="36">
-        <v>0</v>
-      </c>
-      <c r="B21" s="37" t="str">
-        <f t="shared" ref="B21:B44" si="0">IF(A21&gt;=17,"Peak",IF(A21&gt;=9,"Solar","Normal"))</f>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="24">
+        <f>C6*C8</f>
+        <v>55.44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="37">
+        <f>C27/C26</f>
+        <v>0.87719969786052554</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="24">
+        <f>C27/'00_Inputs'!$B$12</f>
+        <v>63</v>
+      </c>
+      <c r="D29" s="6" t="str">
+        <f>"solar window (09–17) can deliver "&amp;TEXT(SUMPRODUCT(($B$35:$B$58="Solar")*($H$35:$H$58)),"0")&amp;" MWh at contract headroom"</f>
+        <v>solar window (09–17) can deliver 24 MWh at contract headroom</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="33" t="str">
+        <f>IF(C28&lt;=1,"ONE daily cycle sufficient — charge solar hours (IEX floor), discharge 17–24 peak. Standard Indian BTM pattern.",IF(C28&lt;=2,"TWO cycles needed — MSEDCL has a single evening peak, so add "&amp;(ROUNDUP(C27/'00_Inputs'!$B$27/C11,0)-C12)&amp;" containers for one-cycle operation, or run cycle 2 as thin-margin morning arbitrage (dual-peak states like UP/UK support true 2-cycle).","UNDERSIZED — more than 2 cycles/day implied against a single 7-h peak: add containers or cut the coverage target."))</f>
+        <v>ONE daily cycle sufficient — charge solar hours (IEX floor), discharge 17–24 peak. Standard Indian BTM pattern.</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="38">
+        <f>ROUNDUP(C27/2/'00_Inputs'!$B$27/C11,0)</f>
+        <v>7</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="I34" s="40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="41">
+        <v>0</v>
+      </c>
+      <c r="B35" s="42" t="str">
+        <f t="shared" ref="B35:B58" si="0">IF(A35&gt;=17,"Peak",IF(A35&gt;=9,"Solar","Normal"))</f>
         <v>Normal</v>
       </c>
-      <c r="C21" s="38">
-        <f>IF(A21&lt;6,'00_Inputs'!$B$23,IF(A21&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C35" s="43">
+        <f>IF(A35&lt;6,'00_Inputs'!$B$23,IF(A35&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40">
-        <f t="shared" ref="E21:E44" si="1">IF(D21&lt;&gt;"",D21,C21)</f>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45">
+        <f t="shared" ref="E35:E58" si="1">IF(D35&lt;&gt;"",D35,C35)</f>
         <v>5</v>
       </c>
-      <c r="F21" s="40">
-        <f>IF(B21="Peak",MIN(E21,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="40">
-        <f t="shared" ref="G21:G44" si="2">F21*$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="40">
-        <f>IF(B21="Peak",0,MIN(MAX('00_Inputs'!$B$22-E21,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F35" s="45">
+        <f>IF(B35="Peak",MIN(E35,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="45">
+        <f t="shared" ref="G35:G58" si="2">F35*$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="45">
+        <f>IF(B35="Peak",0,MIN(MAX('00_Inputs'!$B$22-E35,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="36">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="41">
         <v>1</v>
       </c>
-      <c r="B22" s="37" t="str">
+      <c r="B36" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C22" s="38">
-        <f>IF(A22&lt;6,'00_Inputs'!$B$23,IF(A22&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C36" s="43">
+        <f>IF(A36&lt;6,'00_Inputs'!$B$23,IF(A36&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40">
+      <c r="D36" s="44"/>
+      <c r="E36" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F22" s="40">
-        <f>IF(B22="Peak",MIN(E22,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="40">
-        <f>IF(B22="Peak",0,MIN(MAX('00_Inputs'!$B$22-E22,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F36" s="45">
+        <f>IF(B36="Peak",MIN(E36,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="45">
+        <f>IF(B36="Peak",0,MIN(MAX('00_Inputs'!$B$22-E36,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="36">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="41">
         <v>2</v>
       </c>
-      <c r="B23" s="37" t="str">
+      <c r="B37" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C23" s="38">
-        <f>IF(A23&lt;6,'00_Inputs'!$B$23,IF(A23&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C37" s="43">
+        <f>IF(A37&lt;6,'00_Inputs'!$B$23,IF(A37&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40">
+      <c r="D37" s="44"/>
+      <c r="E37" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F23" s="40">
-        <f>IF(B23="Peak",MIN(E23,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="40">
-        <f>IF(B23="Peak",0,MIN(MAX('00_Inputs'!$B$22-E23,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F37" s="45">
+        <f>IF(B37="Peak",MIN(E37,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="45">
+        <f>IF(B37="Peak",0,MIN(MAX('00_Inputs'!$B$22-E37,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="36">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="41">
         <v>3</v>
       </c>
-      <c r="B24" s="37" t="str">
+      <c r="B38" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C24" s="38">
-        <f>IF(A24&lt;6,'00_Inputs'!$B$23,IF(A24&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C38" s="43">
+        <f>IF(A38&lt;6,'00_Inputs'!$B$23,IF(A38&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40">
+      <c r="D38" s="44"/>
+      <c r="E38" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F24" s="40">
-        <f>IF(B24="Peak",MIN(E24,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="40">
-        <f>IF(B24="Peak",0,MIN(MAX('00_Inputs'!$B$22-E24,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F38" s="45">
+        <f>IF(B38="Peak",MIN(E38,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="45">
+        <f>IF(B38="Peak",0,MIN(MAX('00_Inputs'!$B$22-E38,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="36">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="41">
         <v>4</v>
       </c>
-      <c r="B25" s="37" t="str">
+      <c r="B39" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C25" s="38">
-        <f>IF(A25&lt;6,'00_Inputs'!$B$23,IF(A25&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C39" s="43">
+        <f>IF(A39&lt;6,'00_Inputs'!$B$23,IF(A39&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40">
+      <c r="D39" s="44"/>
+      <c r="E39" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F25" s="40">
-        <f>IF(B25="Peak",MIN(E25,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="40">
-        <f>IF(B25="Peak",0,MIN(MAX('00_Inputs'!$B$22-E25,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F39" s="45">
+        <f>IF(B39="Peak",MIN(E39,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="45">
+        <f>IF(B39="Peak",0,MIN(MAX('00_Inputs'!$B$22-E39,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="36">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="41">
         <v>5</v>
       </c>
-      <c r="B26" s="37" t="str">
+      <c r="B40" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C26" s="38">
-        <f>IF(A26&lt;6,'00_Inputs'!$B$23,IF(A26&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C40" s="43">
+        <f>IF(A40&lt;6,'00_Inputs'!$B$23,IF(A40&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>5</v>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40">
+      <c r="D40" s="44"/>
+      <c r="E40" s="45">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F26" s="40">
-        <f>IF(B26="Peak",MIN(E26,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="40">
-        <f>IF(B26="Peak",0,MIN(MAX('00_Inputs'!$B$22-E26,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F40" s="45">
+        <f>IF(B40="Peak",MIN(E40,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="45">
+        <f>IF(B40="Peak",0,MIN(MAX('00_Inputs'!$B$22-E40,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="36">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="41">
         <v>6</v>
       </c>
-      <c r="B27" s="37" t="str">
+      <c r="B41" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C27" s="38">
-        <f>IF(A27&lt;6,'00_Inputs'!$B$23,IF(A27&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C41" s="43">
+        <f>IF(A41&lt;6,'00_Inputs'!$B$23,IF(A41&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D27" s="39"/>
-      <c r="E27" s="40">
+      <c r="D41" s="44"/>
+      <c r="E41" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F27" s="40">
-        <f>IF(B27="Peak",MIN(E27,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="40">
-        <f>IF(B27="Peak",0,MIN(MAX('00_Inputs'!$B$22-E27,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F41" s="45">
+        <f>IF(B41="Peak",MIN(E41,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="45">
+        <f>IF(B41="Peak",0,MIN(MAX('00_Inputs'!$B$22-E41,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="36">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="41">
         <v>7</v>
       </c>
-      <c r="B28" s="37" t="str">
+      <c r="B42" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C28" s="38">
-        <f>IF(A28&lt;6,'00_Inputs'!$B$23,IF(A28&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C42" s="43">
+        <f>IF(A42&lt;6,'00_Inputs'!$B$23,IF(A42&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40">
+      <c r="D42" s="44"/>
+      <c r="E42" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F28" s="40">
-        <f>IF(B28="Peak",MIN(E28,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="40">
-        <f>IF(B28="Peak",0,MIN(MAX('00_Inputs'!$B$22-E28,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F42" s="45">
+        <f>IF(B42="Peak",MIN(E42,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="45">
+        <f>IF(B42="Peak",0,MIN(MAX('00_Inputs'!$B$22-E42,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="36">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="41">
         <v>8</v>
       </c>
-      <c r="B29" s="37" t="str">
+      <c r="B43" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C29" s="38">
-        <f>IF(A29&lt;6,'00_Inputs'!$B$23,IF(A29&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C43" s="43">
+        <f>IF(A43&lt;6,'00_Inputs'!$B$23,IF(A43&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40">
+      <c r="D43" s="44"/>
+      <c r="E43" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F29" s="40">
-        <f>IF(B29="Peak",MIN(E29,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="40">
-        <f>IF(B29="Peak",0,MIN(MAX('00_Inputs'!$B$22-E29,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F43" s="45">
+        <f>IF(B43="Peak",MIN(E43,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="45">
+        <f>IF(B43="Peak",0,MIN(MAX('00_Inputs'!$B$22-E43,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="36">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="41">
         <v>9</v>
       </c>
-      <c r="B30" s="37" t="str">
+      <c r="B44" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C30" s="38">
-        <f>IF(A30&lt;6,'00_Inputs'!$B$23,IF(A30&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C44" s="43">
+        <f>IF(A44&lt;6,'00_Inputs'!$B$23,IF(A44&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40">
+      <c r="D44" s="44"/>
+      <c r="E44" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F30" s="40">
-        <f>IF(B30="Peak",MIN(E30,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="40">
-        <f>IF(B30="Peak",0,MIN(MAX('00_Inputs'!$B$22-E30,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F44" s="45">
+        <f>IF(B44="Peak",MIN(E44,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="45">
+        <f>IF(B44="Peak",0,MIN(MAX('00_Inputs'!$B$22-E44,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="36">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="41">
         <v>10</v>
       </c>
-      <c r="B31" s="37" t="str">
+      <c r="B45" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C31" s="38">
-        <f>IF(A31&lt;6,'00_Inputs'!$B$23,IF(A31&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C45" s="43">
+        <f>IF(A45&lt;6,'00_Inputs'!$B$23,IF(A45&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="40">
+      <c r="D45" s="44"/>
+      <c r="E45" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F31" s="40">
-        <f>IF(B31="Peak",MIN(E31,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="40">
-        <f>IF(B31="Peak",0,MIN(MAX('00_Inputs'!$B$22-E31,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F45" s="45">
+        <f>IF(B45="Peak",MIN(E45,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="45">
+        <f>IF(B45="Peak",0,MIN(MAX('00_Inputs'!$B$22-E45,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="36">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="41">
         <v>11</v>
       </c>
-      <c r="B32" s="37" t="str">
+      <c r="B46" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C32" s="38">
-        <f>IF(A32&lt;6,'00_Inputs'!$B$23,IF(A32&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C46" s="43">
+        <f>IF(A46&lt;6,'00_Inputs'!$B$23,IF(A46&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="40">
+      <c r="D46" s="44"/>
+      <c r="E46" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F32" s="40">
-        <f>IF(B32="Peak",MIN(E32,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="40">
-        <f>IF(B32="Peak",0,MIN(MAX('00_Inputs'!$B$22-E32,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F46" s="45">
+        <f>IF(B46="Peak",MIN(E46,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="45">
+        <f>IF(B46="Peak",0,MIN(MAX('00_Inputs'!$B$22-E46,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="36">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="41">
         <v>12</v>
       </c>
-      <c r="B33" s="37" t="str">
+      <c r="B47" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C33" s="38">
-        <f>IF(A33&lt;6,'00_Inputs'!$B$23,IF(A33&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C47" s="43">
+        <f>IF(A47&lt;6,'00_Inputs'!$B$23,IF(A47&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="40">
+      <c r="D47" s="44"/>
+      <c r="E47" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F33" s="40">
-        <f>IF(B33="Peak",MIN(E33,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="40">
-        <f>IF(B33="Peak",0,MIN(MAX('00_Inputs'!$B$22-E33,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F47" s="45">
+        <f>IF(B47="Peak",MIN(E47,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="45">
+        <f>IF(B47="Peak",0,MIN(MAX('00_Inputs'!$B$22-E47,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="36">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="41">
         <v>13</v>
       </c>
-      <c r="B34" s="37" t="str">
+      <c r="B48" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C34" s="38">
-        <f>IF(A34&lt;6,'00_Inputs'!$B$23,IF(A34&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C48" s="43">
+        <f>IF(A48&lt;6,'00_Inputs'!$B$23,IF(A48&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="40">
+      <c r="D48" s="44"/>
+      <c r="E48" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F34" s="40">
-        <f>IF(B34="Peak",MIN(E34,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="40">
-        <f>IF(B34="Peak",0,MIN(MAX('00_Inputs'!$B$22-E34,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F48" s="45">
+        <f>IF(B48="Peak",MIN(E48,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="45">
+        <f>IF(B48="Peak",0,MIN(MAX('00_Inputs'!$B$22-E48,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="36">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" s="41">
         <v>14</v>
       </c>
-      <c r="B35" s="37" t="str">
+      <c r="B49" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C35" s="38">
-        <f>IF(A35&lt;6,'00_Inputs'!$B$23,IF(A35&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C49" s="43">
+        <f>IF(A49&lt;6,'00_Inputs'!$B$23,IF(A49&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="40">
+      <c r="D49" s="44"/>
+      <c r="E49" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F35" s="40">
-        <f>IF(B35="Peak",MIN(E35,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="40">
-        <f>IF(B35="Peak",0,MIN(MAX('00_Inputs'!$B$22-E35,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F49" s="45">
+        <f>IF(B49="Peak",MIN(E49,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="45">
+        <f>IF(B49="Peak",0,MIN(MAX('00_Inputs'!$B$22-E49,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="36">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" s="41">
         <v>15</v>
       </c>
-      <c r="B36" s="37" t="str">
+      <c r="B50" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C36" s="38">
-        <f>IF(A36&lt;6,'00_Inputs'!$B$23,IF(A36&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C50" s="43">
+        <f>IF(A50&lt;6,'00_Inputs'!$B$23,IF(A50&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="40">
+      <c r="D50" s="44"/>
+      <c r="E50" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F36" s="40">
-        <f>IF(B36="Peak",MIN(E36,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="40">
-        <f>IF(B36="Peak",0,MIN(MAX('00_Inputs'!$B$22-E36,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F50" s="45">
+        <f>IF(B50="Peak",MIN(E50,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="45">
+        <f>IF(B50="Peak",0,MIN(MAX('00_Inputs'!$B$22-E50,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="36">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" s="41">
         <v>16</v>
       </c>
-      <c r="B37" s="37" t="str">
+      <c r="B51" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C37" s="38">
-        <f>IF(A37&lt;6,'00_Inputs'!$B$23,IF(A37&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C51" s="43">
+        <f>IF(A51&lt;6,'00_Inputs'!$B$23,IF(A51&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>7</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40">
+      <c r="D51" s="44"/>
+      <c r="E51" s="45">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F37" s="40">
-        <f>IF(B37="Peak",MIN(E37,'00_Inputs'!$B$22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="40">
-        <f>IF(B37="Peak",0,MIN(MAX('00_Inputs'!$B$22-E37,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
+      <c r="F51" s="45">
+        <f>IF(B51="Peak",MIN(E51,'00_Inputs'!$B$22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="45">
+        <f>IF(B51="Peak",0,MIN(MAX('00_Inputs'!$B$22-E51,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="36">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="41">
         <v>17</v>
       </c>
-      <c r="B38" s="37" t="str">
+      <c r="B52" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C38" s="38">
-        <f>IF(A38&lt;6,'00_Inputs'!$B$23,IF(A38&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C52" s="43">
+        <f>IF(A52&lt;6,'00_Inputs'!$B$23,IF(A52&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D38" s="39"/>
-      <c r="E38" s="40">
+      <c r="D52" s="44"/>
+      <c r="E52" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F38" s="40">
-        <f>IF(B38="Peak",MIN(E38,'00_Inputs'!$B$22),0)</f>
+      <c r="F52" s="45">
+        <f>IF(B52="Peak",MIN(E52,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G38" s="40">
+      <c r="G52" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H38" s="40">
-        <f>IF(B38="Peak",0,MIN(MAX('00_Inputs'!$B$22-E38,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="36">
+      <c r="H52" s="45">
+        <f>IF(B52="Peak",0,MIN(MAX('00_Inputs'!$B$22-E52,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A53" s="41">
         <v>18</v>
       </c>
-      <c r="B39" s="37" t="str">
+      <c r="B53" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C39" s="38">
-        <f>IF(A39&lt;6,'00_Inputs'!$B$23,IF(A39&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C53" s="43">
+        <f>IF(A53&lt;6,'00_Inputs'!$B$23,IF(A53&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40">
+      <c r="D53" s="44"/>
+      <c r="E53" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F39" s="40">
-        <f>IF(B39="Peak",MIN(E39,'00_Inputs'!$B$22),0)</f>
+      <c r="F53" s="45">
+        <f>IF(B53="Peak",MIN(E53,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G39" s="40">
+      <c r="G53" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H39" s="40">
-        <f>IF(B39="Peak",0,MIN(MAX('00_Inputs'!$B$22-E39,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="36">
+      <c r="H53" s="45">
+        <f>IF(B53="Peak",0,MIN(MAX('00_Inputs'!$B$22-E53,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A54" s="41">
         <v>19</v>
       </c>
-      <c r="B40" s="37" t="str">
+      <c r="B54" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C40" s="38">
-        <f>IF(A40&lt;6,'00_Inputs'!$B$23,IF(A40&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C54" s="43">
+        <f>IF(A54&lt;6,'00_Inputs'!$B$23,IF(A54&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40">
+      <c r="D54" s="44"/>
+      <c r="E54" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F40" s="40">
-        <f>IF(B40="Peak",MIN(E40,'00_Inputs'!$B$22),0)</f>
+      <c r="F54" s="45">
+        <f>IF(B54="Peak",MIN(E54,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G40" s="40">
+      <c r="G54" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H40" s="40">
-        <f>IF(B40="Peak",0,MIN(MAX('00_Inputs'!$B$22-E40,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="36">
+      <c r="H54" s="45">
+        <f>IF(B54="Peak",0,MIN(MAX('00_Inputs'!$B$22-E54,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="41">
         <v>20</v>
       </c>
-      <c r="B41" s="37" t="str">
+      <c r="B55" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C41" s="38">
-        <f>IF(A41&lt;6,'00_Inputs'!$B$23,IF(A41&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C55" s="43">
+        <f>IF(A55&lt;6,'00_Inputs'!$B$23,IF(A55&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D41" s="39"/>
-      <c r="E41" s="40">
+      <c r="D55" s="44"/>
+      <c r="E55" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F41" s="40">
-        <f>IF(B41="Peak",MIN(E41,'00_Inputs'!$B$22),0)</f>
+      <c r="F55" s="45">
+        <f>IF(B55="Peak",MIN(E55,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G41" s="40">
+      <c r="G55" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H41" s="40">
-        <f>IF(B41="Peak",0,MIN(MAX('00_Inputs'!$B$22-E41,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="36">
+      <c r="H55" s="45">
+        <f>IF(B55="Peak",0,MIN(MAX('00_Inputs'!$B$22-E55,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="41">
         <v>21</v>
       </c>
-      <c r="B42" s="37" t="str">
+      <c r="B56" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C42" s="38">
-        <f>IF(A42&lt;6,'00_Inputs'!$B$23,IF(A42&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C56" s="43">
+        <f>IF(A56&lt;6,'00_Inputs'!$B$23,IF(A56&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D42" s="39"/>
-      <c r="E42" s="40">
+      <c r="D56" s="44"/>
+      <c r="E56" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F42" s="40">
-        <f>IF(B42="Peak",MIN(E42,'00_Inputs'!$B$22),0)</f>
+      <c r="F56" s="45">
+        <f>IF(B56="Peak",MIN(E56,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G42" s="40">
+      <c r="G56" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H42" s="40">
-        <f>IF(B42="Peak",0,MIN(MAX('00_Inputs'!$B$22-E42,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="36">
+      <c r="H56" s="45">
+        <f>IF(B56="Peak",0,MIN(MAX('00_Inputs'!$B$22-E56,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="41">
         <v>22</v>
       </c>
-      <c r="B43" s="37" t="str">
+      <c r="B57" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C43" s="38">
-        <f>IF(A43&lt;6,'00_Inputs'!$B$23,IF(A43&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C57" s="43">
+        <f>IF(A57&lt;6,'00_Inputs'!$B$23,IF(A57&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="40">
+      <c r="D57" s="44"/>
+      <c r="E57" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F43" s="40">
-        <f>IF(B43="Peak",MIN(E43,'00_Inputs'!$B$22),0)</f>
+      <c r="F57" s="45">
+        <f>IF(B57="Peak",MIN(E57,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G43" s="40">
+      <c r="G57" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H43" s="40">
-        <f>IF(B43="Peak",0,MIN(MAX('00_Inputs'!$B$22-E43,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="36">
+      <c r="H57" s="45">
+        <f>IF(B57="Peak",0,MIN(MAX('00_Inputs'!$B$22-E57,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="41">
         <v>23</v>
       </c>
-      <c r="B44" s="37" t="str">
+      <c r="B58" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C44" s="38">
-        <f>IF(A44&lt;6,'00_Inputs'!$B$23,IF(A44&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
+      <c r="C58" s="43">
+        <f>IF(A58&lt;6,'00_Inputs'!$B$23,IF(A58&lt;17,'00_Inputs'!$B$24,'00_Inputs'!$B$25))</f>
         <v>9</v>
       </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="40">
+      <c r="D58" s="44"/>
+      <c r="E58" s="45">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="F44" s="40">
-        <f>IF(B44="Peak",MIN(E44,'00_Inputs'!$B$22),0)</f>
+      <c r="F58" s="45">
+        <f>IF(B58="Peak",MIN(E58,'00_Inputs'!$B$22),0)</f>
         <v>9</v>
       </c>
-      <c r="G44" s="40">
+      <c r="G58" s="45">
         <f t="shared" si="2"/>
         <v>7.92</v>
       </c>
-      <c r="H44" s="40">
-        <f>IF(B44="Peak",0,MIN(MAX('00_Inputs'!$B$22-E44,0),'00_Inputs'!$B$26*MAX($F$21:$F$44)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>87</v>
+      <c r="H58" s="45">
+        <f>IF(B58="Peak",0,MIN(MAX('00_Inputs'!$B$22-E58,0),'00_Inputs'!$B$26*MAX($F$35:$F$58)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2444,22 +2652,22 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2468,28 +2676,28 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C6" s="24">
         <f>MIN('00_Inputs'!$B$14,'00_Inputs'!$B$13*7/'00_Inputs'!$B$12)</f>
         <v>63.636363636363633</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="41">
+        <v>112</v>
+      </c>
+      <c r="C7" s="46">
         <f>CEILING(C6/'00_Inputs'!$B$13,1)</f>
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C8" s="24">
         <f>SUM($H$21:$H$44)</f>
@@ -2498,7 +2706,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C9" s="24">
         <f>SUM($I$21:$I$44)</f>
@@ -2507,141 +2715,141 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="42">
+        <v>115</v>
+      </c>
+      <c r="C10" s="47">
         <f>SUM($L$21:$L$44)</f>
         <v>416745.45454545453</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="42">
+        <v>117</v>
+      </c>
+      <c r="C11" s="47">
         <f>SUM($M$21:$M$44)</f>
         <v>567167.99999999977</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="43">
+        <v>118</v>
+      </c>
+      <c r="C12" s="48">
         <f>(C11-C10)/100000</f>
         <v>1.5042254545454523</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="44">
+        <v>119</v>
+      </c>
+      <c r="C13" s="49">
         <f>C12*'00_Inputs'!$B$32/100</f>
         <v>4.9639439999999926</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="45">
+        <v>121</v>
+      </c>
+      <c r="C14" s="50">
         <f>IF(C8&gt;0,C10/C8/1000,0)</f>
         <v>6.5488571428571429</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="45">
+        <v>122</v>
+      </c>
+      <c r="C15" s="50">
         <f>IF(C9&gt;0,C11/C9/1000,0)</f>
         <v>10.127999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="45">
+        <v>123</v>
+      </c>
+      <c r="C16" s="50">
         <f>C15-C14/'00_Inputs'!$B$12</f>
         <v>2.6861168831168811</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="46">
+        <v>125</v>
+      </c>
+      <c r="C17" s="51">
         <f>$J$44/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="L20" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="M20" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="N20" s="35" t="s">
-        <v>120</v>
+      <c r="A20" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="M20" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="N20" s="40" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="36">
-        <v>0</v>
-      </c>
-      <c r="B21" s="37" t="str">
+      <c r="A21" s="41">
+        <v>0</v>
+      </c>
+      <c r="B21" s="42" t="str">
         <f t="shared" ref="B21:B44" si="0">IF(A21&gt;=17,"Peak",IF(A21&gt;=9,"Solar","Normal"))</f>
         <v>Normal</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A21+1,'00_Inputs'!$B$7)</f>
         <v>4.2</v>
       </c>
@@ -2653,52 +2861,52 @@
         <f>'00_Inputs'!$B$16*IF(B21="Peak",'00_Inputs'!$B$17,IF(B21="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="53">
         <f t="shared" ref="F21:F44" si="1">IF(B21="Peak","",SUMPRODUCT(($B$21:$B$44&lt;&gt;"Peak")*($D$21:$D$44&lt;D21))+1)</f>
         <v>14</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="53">
         <f>IF(B21="Peak",0,IF(AND(F21&lt;=$C$7,D21&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="45">
         <f>IF(G21=1,MIN('00_Inputs'!$B$13,$C$6),0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="40">
+      <c r="I21" s="45">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="45">
         <f>H21-I21/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K21" s="49">
+      <c r="K21" s="54">
         <f>J21/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L21" s="55">
         <f t="shared" ref="L21:L44" si="2">H21*1000*D21</f>
         <v>0</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="55">
         <f t="shared" ref="M21:M44" si="3">I21*1000*E21</f>
         <v>0</v>
       </c>
-      <c r="N21" s="37" t="str">
+      <c r="N21" s="42" t="str">
         <f t="shared" ref="N21:N44" si="4">IF(H21&gt;0,"CHARGE",IF(I21&gt;0,"DISCHARGE","—"))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="36">
+      <c r="A22" s="41">
         <v>1</v>
       </c>
-      <c r="B22" s="37" t="str">
+      <c r="B22" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A22+1,'00_Inputs'!$B$7)</f>
         <v>3.9</v>
       </c>
@@ -2710,52 +2918,52 @@
         <f>'00_Inputs'!$B$16*IF(B22="Peak",'00_Inputs'!$B$17,IF(B22="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="53">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="53">
         <f>IF(B22="Peak",0,IF(AND(F22&lt;=$C$7,D22&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="45">
         <f>IF(G22=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H21))),0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="45">
         <f>IF(B22="Peak",MIN('00_Inputs'!$B$13,J21*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="45">
         <f>J21+H22-I22/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K22" s="49">
+      <c r="K22" s="54">
         <f>J22/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L22" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="50">
+      <c r="L22" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N22" s="37" t="str">
+      <c r="N22" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="36">
+      <c r="A23" s="41">
         <v>2</v>
       </c>
-      <c r="B23" s="37" t="str">
+      <c r="B23" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A23+1,'00_Inputs'!$B$7)</f>
         <v>3.7</v>
       </c>
@@ -2767,52 +2975,52 @@
         <f>'00_Inputs'!$B$16*IF(B23="Peak",'00_Inputs'!$B$17,IF(B23="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="53">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="53">
         <f>IF(B23="Peak",0,IF(AND(F23&lt;=$C$7,D23&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H23" s="40">
+      <c r="H23" s="45">
         <f>IF(G23=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H22))),0)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="45">
         <f>IF(B23="Peak",MIN('00_Inputs'!$B$13,J22*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="45">
         <f>J22+H23-I23/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K23" s="49">
+      <c r="K23" s="54">
         <f>J23/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L23" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="50">
+      <c r="L23" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N23" s="37" t="str">
+      <c r="N23" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="36">
+      <c r="A24" s="41">
         <v>3</v>
       </c>
-      <c r="B24" s="37" t="str">
+      <c r="B24" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A24+1,'00_Inputs'!$B$7)</f>
         <v>3.6</v>
       </c>
@@ -2824,52 +3032,52 @@
         <f>'00_Inputs'!$B$16*IF(B24="Peak",'00_Inputs'!$B$17,IF(B24="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="53">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="53">
         <f>IF(B24="Peak",0,IF(AND(F24&lt;=$C$7,D24&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="45">
         <f>IF(G24=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H23))),0)</f>
         <v>8</v>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="45">
         <f>IF(B24="Peak",MIN('00_Inputs'!$B$13,J23*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="45">
         <f>J23+H24-I24/'00_Inputs'!$B$12</f>
         <v>8</v>
       </c>
-      <c r="K24" s="49">
+      <c r="K24" s="54">
         <f>J24/'00_Inputs'!$B$14</f>
         <v>0.11392203868318515</v>
       </c>
-      <c r="L24" s="50">
+      <c r="L24" s="55">
         <f t="shared" si="2"/>
         <v>58000</v>
       </c>
-      <c r="M24" s="50">
+      <c r="M24" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N24" s="37" t="str">
+      <c r="N24" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="36">
+      <c r="A25" s="41">
         <v>4</v>
       </c>
-      <c r="B25" s="37" t="str">
+      <c r="B25" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A25+1,'00_Inputs'!$B$7)</f>
         <v>3.5</v>
       </c>
@@ -2881,52 +3089,52 @@
         <f>'00_Inputs'!$B$16*IF(B25="Peak",'00_Inputs'!$B$17,IF(B25="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F25" s="48">
+      <c r="F25" s="53">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G25" s="48">
+      <c r="G25" s="53">
         <f>IF(B25="Peak",0,IF(AND(F25&lt;=$C$7,D25&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H25" s="40">
+      <c r="H25" s="45">
         <f>IF(G25=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H24))),0)</f>
         <v>8</v>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="45">
         <f>IF(B25="Peak",MIN('00_Inputs'!$B$13,J24*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="40">
+      <c r="J25" s="45">
         <f>J24+H25-I25/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K25" s="49">
+      <c r="K25" s="54">
         <f>J25/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L25" s="50">
+      <c r="L25" s="55">
         <f t="shared" si="2"/>
         <v>57200</v>
       </c>
-      <c r="M25" s="50">
+      <c r="M25" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N25" s="37" t="str">
+      <c r="N25" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="36">
+      <c r="A26" s="41">
         <v>5</v>
       </c>
-      <c r="B26" s="37" t="str">
+      <c r="B26" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A26+1,'00_Inputs'!$B$7)</f>
         <v>3.8</v>
       </c>
@@ -2938,52 +3146,52 @@
         <f>'00_Inputs'!$B$16*IF(B26="Peak",'00_Inputs'!$B$17,IF(B26="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F26" s="48">
+      <c r="F26" s="53">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G26" s="48">
+      <c r="G26" s="53">
         <f>IF(B26="Peak",0,IF(AND(F26&lt;=$C$7,D26&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="45">
         <f>IF(G26=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H25))),0)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="45">
         <f>IF(B26="Peak",MIN('00_Inputs'!$B$13,J25*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="45">
         <f>J25+H26-I26/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K26" s="49">
+      <c r="K26" s="54">
         <f>J26/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L26" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="50">
+      <c r="L26" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N26" s="37" t="str">
+      <c r="N26" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="36">
+      <c r="A27" s="41">
         <v>6</v>
       </c>
-      <c r="B27" s="37" t="str">
+      <c r="B27" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A27+1,'00_Inputs'!$B$7)</f>
         <v>4.5999999999999996</v>
       </c>
@@ -2995,52 +3203,52 @@
         <f>'00_Inputs'!$B$16*IF(B27="Peak",'00_Inputs'!$B$17,IF(B27="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="53">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="53">
         <f>IF(B27="Peak",0,IF(AND(F27&lt;=$C$7,D27&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="45">
         <f>IF(G27=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H26))),0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="45">
         <f>IF(B27="Peak",MIN('00_Inputs'!$B$13,J26*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="45">
         <f>J26+H27-I27/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K27" s="49">
+      <c r="K27" s="54">
         <f>J27/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L27" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="50">
+      <c r="L27" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N27" s="37" t="str">
+      <c r="N27" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="36">
+      <c r="A28" s="41">
         <v>7</v>
       </c>
-      <c r="B28" s="37" t="str">
+      <c r="B28" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A28+1,'00_Inputs'!$B$7)</f>
         <v>5.4</v>
       </c>
@@ -3052,52 +3260,52 @@
         <f>'00_Inputs'!$B$16*IF(B28="Peak",'00_Inputs'!$B$17,IF(B28="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="53">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="53">
         <f>IF(B28="Peak",0,IF(AND(F28&lt;=$C$7,D28&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="45">
         <f>IF(G28=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H27))),0)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="45">
         <f>IF(B28="Peak",MIN('00_Inputs'!$B$13,J27*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="45">
         <f>J27+H28-I28/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K28" s="49">
+      <c r="K28" s="54">
         <f>J28/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L28" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="50">
+      <c r="L28" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N28" s="37" t="str">
+      <c r="N28" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="36">
+      <c r="A29" s="41">
         <v>8</v>
       </c>
-      <c r="B29" s="37" t="str">
+      <c r="B29" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Normal</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A29+1,'00_Inputs'!$B$7)</f>
         <v>5.2</v>
       </c>
@@ -3109,52 +3317,52 @@
         <f>'00_Inputs'!$B$16*IF(B29="Peak",'00_Inputs'!$B$17,IF(B29="Solar",'00_Inputs'!$B$18,1))</f>
         <v>8.44</v>
       </c>
-      <c r="F29" s="48">
+      <c r="F29" s="53">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="G29" s="48">
+      <c r="G29" s="53">
         <f>IF(B29="Peak",0,IF(AND(F29&lt;=$C$7,D29&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="45">
         <f>IF(G29=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H28))),0)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="45">
         <f>IF(B29="Peak",MIN('00_Inputs'!$B$13,J28*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="45">
         <f>J28+H29-I29/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K29" s="49">
+      <c r="K29" s="54">
         <f>J29/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L29" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="50">
+      <c r="L29" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N29" s="37" t="str">
+      <c r="N29" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="36">
+      <c r="A30" s="41">
         <v>9</v>
       </c>
-      <c r="B30" s="37" t="str">
+      <c r="B30" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A30+1,'00_Inputs'!$B$7)</f>
         <v>4</v>
       </c>
@@ -3166,52 +3374,52 @@
         <f>'00_Inputs'!$B$16*IF(B30="Peak",'00_Inputs'!$B$17,IF(B30="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="53">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="53">
         <f>IF(B30="Peak",0,IF(AND(F30&lt;=$C$7,D30&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="45">
         <f>IF(G30=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H29))),0)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="45">
         <f>IF(B30="Peak",MIN('00_Inputs'!$B$13,J29*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="45">
         <f>J29+H30-I30/'00_Inputs'!$B$12</f>
         <v>16</v>
       </c>
-      <c r="K30" s="49">
+      <c r="K30" s="54">
         <f>J30/'00_Inputs'!$B$14</f>
         <v>0.2278440773663703</v>
       </c>
-      <c r="L30" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="50">
+      <c r="L30" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="37" t="str">
+      <c r="N30" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="36">
+      <c r="A31" s="41">
         <v>10</v>
       </c>
-      <c r="B31" s="37" t="str">
+      <c r="B31" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A31+1,'00_Inputs'!$B$7)</f>
         <v>3</v>
       </c>
@@ -3223,52 +3431,52 @@
         <f>'00_Inputs'!$B$16*IF(B31="Peak",'00_Inputs'!$B$17,IF(B31="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F31" s="48">
+      <c r="F31" s="53">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G31" s="48">
+      <c r="G31" s="53">
         <f>IF(B31="Peak",0,IF(AND(F31&lt;=$C$7,D31&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="45">
         <f>IF(G31=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H30))),0)</f>
         <v>8</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="45">
         <f>IF(B31="Peak",MIN('00_Inputs'!$B$13,J30*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="45">
         <f>J30+H31-I31/'00_Inputs'!$B$12</f>
         <v>24</v>
       </c>
-      <c r="K31" s="49">
+      <c r="K31" s="54">
         <f>J31/'00_Inputs'!$B$14</f>
         <v>0.34176611604955548</v>
       </c>
-      <c r="L31" s="50">
+      <c r="L31" s="55">
         <f t="shared" si="2"/>
         <v>53200</v>
       </c>
-      <c r="M31" s="50">
+      <c r="M31" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N31" s="37" t="str">
+      <c r="N31" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="36">
+      <c r="A32" s="41">
         <v>11</v>
       </c>
-      <c r="B32" s="37" t="str">
+      <c r="B32" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A32+1,'00_Inputs'!$B$7)</f>
         <v>2.6</v>
       </c>
@@ -3280,52 +3488,52 @@
         <f>'00_Inputs'!$B$16*IF(B32="Peak",'00_Inputs'!$B$17,IF(B32="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F32" s="48">
+      <c r="F32" s="53">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G32" s="48">
+      <c r="G32" s="53">
         <f>IF(B32="Peak",0,IF(AND(F32&lt;=$C$7,D32&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="45">
         <f>IF(G32=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H31))),0)</f>
         <v>8</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="45">
         <f>IF(B32="Peak",MIN('00_Inputs'!$B$13,J31*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="45">
         <f>J31+H32-I32/'00_Inputs'!$B$12</f>
         <v>32</v>
       </c>
-      <c r="K32" s="49">
+      <c r="K32" s="54">
         <f>J32/'00_Inputs'!$B$14</f>
         <v>0.4556881547327406</v>
       </c>
-      <c r="L32" s="50">
+      <c r="L32" s="55">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M32" s="50">
+      <c r="M32" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N32" s="37" t="str">
+      <c r="N32" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="36">
+      <c r="A33" s="41">
         <v>12</v>
       </c>
-      <c r="B33" s="37" t="str">
+      <c r="B33" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A33+1,'00_Inputs'!$B$7)</f>
         <v>2.4</v>
       </c>
@@ -3337,52 +3545,52 @@
         <f>'00_Inputs'!$B$16*IF(B33="Peak",'00_Inputs'!$B$17,IF(B33="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F33" s="48">
+      <c r="F33" s="53">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="53">
         <f>IF(B33="Peak",0,IF(AND(F33&lt;=$C$7,D33&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="45">
         <f>IF(G33=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H32))),0)</f>
         <v>8</v>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="45">
         <f>IF(B33="Peak",MIN('00_Inputs'!$B$13,J32*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="40">
+      <c r="J33" s="45">
         <f>J32+H33-I33/'00_Inputs'!$B$12</f>
         <v>40</v>
       </c>
-      <c r="K33" s="49">
+      <c r="K33" s="54">
         <f>J33/'00_Inputs'!$B$14</f>
         <v>0.56961019341592578</v>
       </c>
-      <c r="L33" s="50">
+      <c r="L33" s="55">
         <f t="shared" si="2"/>
         <v>48400</v>
       </c>
-      <c r="M33" s="50">
+      <c r="M33" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N33" s="37" t="str">
+      <c r="N33" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="36">
+      <c r="A34" s="41">
         <v>13</v>
       </c>
-      <c r="B34" s="37" t="str">
+      <c r="B34" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A34+1,'00_Inputs'!$B$7)</f>
         <v>2.4</v>
       </c>
@@ -3394,52 +3602,52 @@
         <f>'00_Inputs'!$B$16*IF(B34="Peak",'00_Inputs'!$B$17,IF(B34="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="53">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="53">
         <f>IF(B34="Peak",0,IF(AND(F34&lt;=$C$7,D34&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H34" s="40">
+      <c r="H34" s="45">
         <f>IF(G34=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H33))),0)</f>
         <v>8</v>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="45">
         <f>IF(B34="Peak",MIN('00_Inputs'!$B$13,J33*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="40">
+      <c r="J34" s="45">
         <f>J33+H34-I34/'00_Inputs'!$B$12</f>
         <v>48</v>
       </c>
-      <c r="K34" s="49">
+      <c r="K34" s="54">
         <f>J34/'00_Inputs'!$B$14</f>
         <v>0.68353223209911096</v>
       </c>
-      <c r="L34" s="50">
+      <c r="L34" s="55">
         <f t="shared" si="2"/>
         <v>48400</v>
       </c>
-      <c r="M34" s="50">
+      <c r="M34" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N34" s="37" t="str">
+      <c r="N34" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="36">
+      <c r="A35" s="41">
         <v>14</v>
       </c>
-      <c r="B35" s="37" t="str">
+      <c r="B35" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A35+1,'00_Inputs'!$B$7)</f>
         <v>2.6</v>
       </c>
@@ -3451,52 +3659,52 @@
         <f>'00_Inputs'!$B$16*IF(B35="Peak",'00_Inputs'!$B$17,IF(B35="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F35" s="48">
+      <c r="F35" s="53">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G35" s="48">
+      <c r="G35" s="53">
         <f>IF(B35="Peak",0,IF(AND(F35&lt;=$C$7,D35&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H35" s="40">
+      <c r="H35" s="45">
         <f>IF(G35=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H34))),0)</f>
         <v>8</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="45">
         <f>IF(B35="Peak",MIN('00_Inputs'!$B$13,J34*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="45">
         <f>J34+H35-I35/'00_Inputs'!$B$12</f>
         <v>56</v>
       </c>
-      <c r="K35" s="49">
+      <c r="K35" s="54">
         <f>J35/'00_Inputs'!$B$14</f>
         <v>0.79745427078229603</v>
       </c>
-      <c r="L35" s="50">
+      <c r="L35" s="55">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M35" s="50">
+      <c r="M35" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N35" s="37" t="str">
+      <c r="N35" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="36">
+      <c r="A36" s="41">
         <v>15</v>
       </c>
-      <c r="B36" s="37" t="str">
+      <c r="B36" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A36+1,'00_Inputs'!$B$7)</f>
         <v>3.1</v>
       </c>
@@ -3508,52 +3716,52 @@
         <f>'00_Inputs'!$B$16*IF(B36="Peak",'00_Inputs'!$B$17,IF(B36="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="53">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="G36" s="48">
+      <c r="G36" s="53">
         <f>IF(B36="Peak",0,IF(AND(F36&lt;=$C$7,D36&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>1</v>
       </c>
-      <c r="H36" s="40">
+      <c r="H36" s="45">
         <f>IF(G36=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H35))),0)</f>
         <v>7.6363636363636331</v>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="45">
         <f>IF(B36="Peak",MIN('00_Inputs'!$B$13,J35*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="40">
+      <c r="J36" s="45">
         <f>J35+H36-I36/'00_Inputs'!$B$12</f>
         <v>63.636363636363633</v>
       </c>
-      <c r="K36" s="49">
+      <c r="K36" s="54">
         <f>J36/'00_Inputs'!$B$14</f>
         <v>0.90619803497988183</v>
       </c>
-      <c r="L36" s="50">
+      <c r="L36" s="55">
         <f t="shared" si="2"/>
         <v>51545.454545454522</v>
       </c>
-      <c r="M36" s="50">
+      <c r="M36" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N36" s="37" t="str">
+      <c r="N36" s="42" t="str">
         <f t="shared" si="4"/>
         <v>CHARGE</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="36">
+      <c r="A37" s="41">
         <v>16</v>
       </c>
-      <c r="B37" s="37" t="str">
+      <c r="B37" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Solar</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A37+1,'00_Inputs'!$B$7)</f>
         <v>4</v>
       </c>
@@ -3565,52 +3773,52 @@
         <f>'00_Inputs'!$B$16*IF(B37="Peak",'00_Inputs'!$B$17,IF(B37="Solar",'00_Inputs'!$B$18,1))</f>
         <v>7.1739999999999995</v>
       </c>
-      <c r="F37" s="48">
+      <c r="F37" s="53">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G37" s="48">
+      <c r="G37" s="53">
         <f>IF(B37="Peak",0,IF(AND(F37&lt;=$C$7,D37&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H37" s="40">
+      <c r="H37" s="45">
         <f>IF(G37=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H36))),0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="45">
         <f>IF(B37="Peak",MIN('00_Inputs'!$B$13,J36*'00_Inputs'!$B$12),0)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="40">
+      <c r="J37" s="45">
         <f>J36+H37-I37/'00_Inputs'!$B$12</f>
         <v>63.636363636363633</v>
       </c>
-      <c r="K37" s="49">
+      <c r="K37" s="54">
         <f>J37/'00_Inputs'!$B$14</f>
         <v>0.90619803497988183</v>
       </c>
-      <c r="L37" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="50">
+      <c r="L37" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N37" s="37" t="str">
+      <c r="N37" s="42" t="str">
         <f t="shared" si="4"/>
         <v>—</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="36">
+      <c r="A38" s="41">
         <v>17</v>
       </c>
-      <c r="B38" s="37" t="str">
+      <c r="B38" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A38+1,'00_Inputs'!$B$7)</f>
         <v>5.6</v>
       </c>
@@ -3622,52 +3830,52 @@
         <f>'00_Inputs'!$B$16*IF(B38="Peak",'00_Inputs'!$B$17,IF(B38="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F38" s="48" t="str">
+      <c r="F38" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="53">
         <f>IF(B38="Peak",0,IF(AND(F38&lt;=$C$7,D38&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H38" s="40">
+      <c r="H38" s="45">
         <f>IF(G38=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H37))),0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="45">
         <f>IF(B38="Peak",MIN('00_Inputs'!$B$13,J37*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="45">
         <f>J37+H38-I38/'00_Inputs'!$B$12</f>
         <v>54.54545454545454</v>
       </c>
-      <c r="K38" s="49">
+      <c r="K38" s="54">
         <f>J38/'00_Inputs'!$B$14</f>
         <v>0.77674117283989874</v>
       </c>
-      <c r="L38" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="50">
+      <c r="L38" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N38" s="37" t="str">
+      <c r="N38" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="36">
+      <c r="A39" s="41">
         <v>18</v>
       </c>
-      <c r="B39" s="37" t="str">
+      <c r="B39" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A39+1,'00_Inputs'!$B$7)</f>
         <v>7.2</v>
       </c>
@@ -3679,52 +3887,52 @@
         <f>'00_Inputs'!$B$16*IF(B39="Peak",'00_Inputs'!$B$17,IF(B39="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F39" s="48" t="str">
+      <c r="F39" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="53">
         <f>IF(B39="Peak",0,IF(AND(F39&lt;=$C$7,D39&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H39" s="40">
+      <c r="H39" s="45">
         <f>IF(G39=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H38))),0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="45">
         <f>IF(B39="Peak",MIN('00_Inputs'!$B$13,J38*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="45">
         <f>J38+H39-I39/'00_Inputs'!$B$12</f>
         <v>45.454545454545446</v>
       </c>
-      <c r="K39" s="49">
+      <c r="K39" s="54">
         <f>J39/'00_Inputs'!$B$14</f>
         <v>0.64728431069991554</v>
       </c>
-      <c r="L39" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="50">
+      <c r="L39" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N39" s="37" t="str">
+      <c r="N39" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="36">
+      <c r="A40" s="41">
         <v>19</v>
       </c>
-      <c r="B40" s="37" t="str">
+      <c r="B40" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A40+1,'00_Inputs'!$B$7)</f>
         <v>8.5</v>
       </c>
@@ -3736,52 +3944,52 @@
         <f>'00_Inputs'!$B$16*IF(B40="Peak",'00_Inputs'!$B$17,IF(B40="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F40" s="48" t="str">
+      <c r="F40" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G40" s="48">
+      <c r="G40" s="53">
         <f>IF(B40="Peak",0,IF(AND(F40&lt;=$C$7,D40&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H40" s="40">
+      <c r="H40" s="45">
         <f>IF(G40=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H39))),0)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="45">
         <f>IF(B40="Peak",MIN('00_Inputs'!$B$13,J39*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J40" s="40">
+      <c r="J40" s="45">
         <f>J39+H40-I40/'00_Inputs'!$B$12</f>
         <v>36.363636363636353</v>
       </c>
-      <c r="K40" s="49">
+      <c r="K40" s="54">
         <f>J40/'00_Inputs'!$B$14</f>
         <v>0.51782744855993235</v>
       </c>
-      <c r="L40" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="50">
+      <c r="L40" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N40" s="37" t="str">
+      <c r="N40" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="36">
+      <c r="A41" s="41">
         <v>20</v>
       </c>
-      <c r="B41" s="37" t="str">
+      <c r="B41" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A41+1,'00_Inputs'!$B$7)</f>
         <v>8.9</v>
       </c>
@@ -3793,52 +4001,52 @@
         <f>'00_Inputs'!$B$16*IF(B41="Peak",'00_Inputs'!$B$17,IF(B41="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F41" s="48" t="str">
+      <c r="F41" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="53">
         <f>IF(B41="Peak",0,IF(AND(F41&lt;=$C$7,D41&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H41" s="40">
+      <c r="H41" s="45">
         <f>IF(G41=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H40))),0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="45">
         <f>IF(B41="Peak",MIN('00_Inputs'!$B$13,J40*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J41" s="40">
+      <c r="J41" s="45">
         <f>J40+H41-I41/'00_Inputs'!$B$12</f>
         <v>27.272727272727259</v>
       </c>
-      <c r="K41" s="49">
+      <c r="K41" s="54">
         <f>J41/'00_Inputs'!$B$14</f>
         <v>0.3883705864199492</v>
       </c>
-      <c r="L41" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="50">
+      <c r="L41" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N41" s="37" t="str">
+      <c r="N41" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="36">
+      <c r="A42" s="41">
         <v>21</v>
       </c>
-      <c r="B42" s="37" t="str">
+      <c r="B42" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A42+1,'00_Inputs'!$B$7)</f>
         <v>7.8</v>
       </c>
@@ -3850,52 +4058,52 @@
         <f>'00_Inputs'!$B$16*IF(B42="Peak",'00_Inputs'!$B$17,IF(B42="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F42" s="48" t="str">
+      <c r="F42" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G42" s="48">
+      <c r="G42" s="53">
         <f>IF(B42="Peak",0,IF(AND(F42&lt;=$C$7,D42&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="45">
         <f>IF(G42=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H41))),0)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="45">
         <f>IF(B42="Peak",MIN('00_Inputs'!$B$13,J41*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J42" s="40">
+      <c r="J42" s="45">
         <f>J41+H42-I42/'00_Inputs'!$B$12</f>
         <v>18.181818181818166</v>
       </c>
-      <c r="K42" s="49">
+      <c r="K42" s="54">
         <f>J42/'00_Inputs'!$B$14</f>
         <v>0.25891372427996601</v>
       </c>
-      <c r="L42" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="50">
+      <c r="L42" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N42" s="37" t="str">
+      <c r="N42" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="36">
+      <c r="A43" s="41">
         <v>22</v>
       </c>
-      <c r="B43" s="37" t="str">
+      <c r="B43" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A43+1,'00_Inputs'!$B$7)</f>
         <v>6.2</v>
       </c>
@@ -3907,52 +4115,52 @@
         <f>'00_Inputs'!$B$16*IF(B43="Peak",'00_Inputs'!$B$17,IF(B43="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F43" s="48" t="str">
+      <c r="F43" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G43" s="48">
+      <c r="G43" s="53">
         <f>IF(B43="Peak",0,IF(AND(F43&lt;=$C$7,D43&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="45">
         <f>IF(G43=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H42))),0)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="45">
         <f>IF(B43="Peak",MIN('00_Inputs'!$B$13,J42*'00_Inputs'!$B$12),0)</f>
         <v>8</v>
       </c>
-      <c r="J43" s="40">
+      <c r="J43" s="45">
         <f>J42+H43-I43/'00_Inputs'!$B$12</f>
         <v>9.090909090909074</v>
       </c>
-      <c r="K43" s="49">
+      <c r="K43" s="54">
         <f>J43/'00_Inputs'!$B$14</f>
         <v>0.12945686213998289</v>
       </c>
-      <c r="L43" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="50">
+      <c r="L43" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999985</v>
       </c>
-      <c r="N43" s="37" t="str">
+      <c r="N43" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="36">
+      <c r="A44" s="41">
         <v>23</v>
       </c>
-      <c r="B44" s="37" t="str">
+      <c r="B44" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Peak</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="52">
         <f>INDEX(Prices!$B$2:$D$25,A44+1,'00_Inputs'!$B$7)</f>
         <v>5</v>
       </c>
@@ -3964,46 +4172,46 @@
         <f>'00_Inputs'!$B$16*IF(B44="Peak",'00_Inputs'!$B$17,IF(B44="Solar",'00_Inputs'!$B$18,1))</f>
         <v>10.127999999999998</v>
       </c>
-      <c r="F44" s="48" t="str">
+      <c r="F44" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G44" s="48">
+      <c r="G44" s="53">
         <f>IF(B44="Peak",0,IF(AND(F44&lt;=$C$7,D44&lt;'00_Inputs'!$B$12*'00_Inputs'!$B$20),1,0))</f>
         <v>0</v>
       </c>
-      <c r="H44" s="40">
+      <c r="H44" s="45">
         <f>IF(G44=1,MIN('00_Inputs'!$B$13,MAX(0,$C$6-SUM($H$21:H43))),0)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="40">
+      <c r="I44" s="45">
         <f>IF(B44="Peak",MIN('00_Inputs'!$B$13,J43*'00_Inputs'!$B$12),0)</f>
         <v>7.9999999999999849</v>
       </c>
-      <c r="J44" s="40">
+      <c r="J44" s="45">
         <f>J43+H44-I44/'00_Inputs'!$B$12</f>
         <v>0</v>
       </c>
-      <c r="K44" s="49">
+      <c r="K44" s="54">
         <f>J44/'00_Inputs'!$B$14</f>
         <v>0</v>
       </c>
-      <c r="L44" s="50">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="50">
+      <c r="L44" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="55">
         <f t="shared" si="3"/>
         <v>81023.999999999825</v>
       </c>
-      <c r="N44" s="37" t="str">
+      <c r="N44" s="42" t="str">
         <f t="shared" si="4"/>
         <v>DISCHARGE</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4023,17 +4231,17 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -4041,46 +4249,46 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="44">
+        <v>143</v>
+      </c>
+      <c r="B5" s="49">
         <f>C24</f>
         <v>8.0121225139199908</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B6" s="32">
         <f>'00_Inputs'!$B$14*'00_Inputs'!$B$30*1.05</f>
         <v>81.10809907200003</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" s="34" t="str">
+        <v>146</v>
+      </c>
+      <c r="B7" s="39" t="str">
         <f>IF(N25&gt;=0,"Y"&amp;(COUNTIF($C$25:$N$25,"&lt;0")+1),"&gt;12 yrs")</f>
         <v>Y12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="51">
+        <v>147</v>
+      </c>
+      <c r="B8" s="56">
         <f>IFERROR(IRR(B24:N24),"n/a")</f>
         <v>8.0952091901571599E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B9" s="32">
         <f>B24+NPV('00_Inputs'!$B$34,C24:N24)</f>
@@ -4089,7 +4297,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -4097,49 +4305,49 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="52">
+        <v>150</v>
+      </c>
+      <c r="B12" s="57">
         <f>'02_Dispatch'!$C$13</f>
         <v>4.9639439999999926</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B13" s="32">
         <f>'00_Inputs'!$B$36*'00_Inputs'!$B$37*12/10000000</f>
         <v>2.7</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B14" s="32">
         <f>'00_Inputs'!$B$38*'00_Inputs'!$B$13*1000*('00_Inputs'!$B$39-'00_Inputs'!$B$16)/10000000</f>
         <v>1.5648000000000002</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="53">
+      <c r="A15" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="58">
         <f>SUM(B12:B14)</f>
         <v>9.2287439999999936</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B16" s="32">
         <f>-B6*'00_Inputs'!$B$31</f>
@@ -4147,17 +4355,17 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="53">
+      <c r="A17" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="58">
         <f>B15+B16</f>
         <v>8.0121225139199925</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4175,325 +4383,325 @@
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="L20" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="M20" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="N20" s="35" t="s">
-        <v>154</v>
+      <c r="A20" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="L20" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="M20" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="N20" s="40" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="54">
+        <v>173</v>
+      </c>
+      <c r="C21" s="59">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(1-1)</f>
         <v>4.9639439999999926</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(2-1)</f>
         <v>4.8646651199999926</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(3-1)</f>
         <v>4.7673718175999928</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(4-1)</f>
         <v>4.6720243812479927</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(5-1)</f>
         <v>4.5785838936230325</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(6-1)</f>
         <v>4.4870122157505712</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(7-1)</f>
         <v>4.3972719714355604</v>
       </c>
-      <c r="J21" s="55">
+      <c r="J21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(8-1)</f>
         <v>4.3093265320068488</v>
       </c>
-      <c r="K21" s="55">
+      <c r="K21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(9-1)</f>
         <v>4.223140001366712</v>
       </c>
-      <c r="L21" s="55">
+      <c r="L21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(10-1)</f>
         <v>4.1386772013393776</v>
       </c>
-      <c r="M21" s="55">
+      <c r="M21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(11-1)</f>
         <v>4.0559036573125891</v>
       </c>
-      <c r="N21" s="55">
+      <c r="N21" s="60">
         <f>'02_Dispatch'!$C$13*(1-'00_Inputs'!$B$33)^(12-1)</f>
         <v>3.9747855841663378</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="55">
+        <v>174</v>
+      </c>
+      <c r="C22" s="60">
         <f t="shared" ref="C22:N22" si="0">$B$13+$B$14</f>
         <v>4.2648000000000001</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="J22" s="55">
+      <c r="J22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="K22" s="55">
+      <c r="K22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="L22" s="55">
+      <c r="L22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="M22" s="55">
+      <c r="M22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
-      <c r="N22" s="55">
+      <c r="N22" s="60">
         <f t="shared" si="0"/>
         <v>4.2648000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="55">
+        <v>175</v>
+      </c>
+      <c r="C23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(1-1)</f>
         <v>-1.2166214860800004</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(2-1)</f>
         <v>-1.2774525603840006</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(3-1)</f>
         <v>-1.3413251884032005</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(4-1)</f>
         <v>-1.4083914478233606</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(5-1)</f>
         <v>-1.4788110202145286</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(6-1)</f>
         <v>-1.5527515712252551</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(7-1)</f>
         <v>-1.6303891497865177</v>
       </c>
-      <c r="J23" s="55">
+      <c r="J23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(8-1)</f>
         <v>-1.7119086072758438</v>
       </c>
-      <c r="K23" s="55">
+      <c r="K23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(9-1)</f>
         <v>-1.7975040376396358</v>
       </c>
-      <c r="L23" s="55">
+      <c r="L23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(10-1)</f>
         <v>-1.8873792395216178</v>
       </c>
-      <c r="M23" s="55">
+      <c r="M23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(11-1)</f>
         <v>-1.9817482014976986</v>
       </c>
-      <c r="N23" s="55">
+      <c r="N23" s="60">
         <f>-$B$6*'00_Inputs'!$B$31*1.05^(12-1)</f>
         <v>-2.0808356115725837</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="B24" s="55">
+      <c r="A24" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="60">
         <f>-B6</f>
         <v>-81.10809907200003</v>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="61">
         <f t="shared" ref="C24:N24" si="1">C21+C22+C23</f>
         <v>8.0121225139199908</v>
       </c>
-      <c r="D24" s="56">
+      <c r="D24" s="61">
         <f t="shared" si="1"/>
         <v>7.8520125596159911</v>
       </c>
-      <c r="E24" s="56">
+      <c r="E24" s="61">
         <f t="shared" si="1"/>
         <v>7.690846629196793</v>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="61">
         <f t="shared" si="1"/>
         <v>7.5284329334246323</v>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="61">
         <f t="shared" si="1"/>
         <v>7.3645728734085036</v>
       </c>
-      <c r="H24" s="56">
+      <c r="H24" s="61">
         <f t="shared" si="1"/>
         <v>7.1990606445253169</v>
       </c>
-      <c r="I24" s="56">
+      <c r="I24" s="61">
         <f t="shared" si="1"/>
         <v>7.031682821649043</v>
       </c>
-      <c r="J24" s="56">
+      <c r="J24" s="61">
         <f t="shared" si="1"/>
         <v>6.8622179247310049</v>
       </c>
-      <c r="K24" s="56">
+      <c r="K24" s="61">
         <f t="shared" si="1"/>
         <v>6.6904359637270776</v>
       </c>
-      <c r="L24" s="56">
+      <c r="L24" s="61">
         <f t="shared" si="1"/>
         <v>6.5160979618177599</v>
       </c>
-      <c r="M24" s="56">
+      <c r="M24" s="61">
         <f t="shared" si="1"/>
         <v>6.3389554558148902</v>
       </c>
-      <c r="N24" s="56">
+      <c r="N24" s="61">
         <f t="shared" si="1"/>
         <v>6.1587499725937551</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="B25" s="55">
+      <c r="A25" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="60">
         <f>B24</f>
         <v>-81.10809907200003</v>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="61">
         <f t="shared" ref="C25:N25" si="2">B25+C24</f>
         <v>-73.095976558080039</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="61">
         <f t="shared" si="2"/>
         <v>-65.243963998464054</v>
       </c>
-      <c r="E25" s="56">
+      <c r="E25" s="61">
         <f t="shared" si="2"/>
         <v>-57.553117369267262</v>
       </c>
-      <c r="F25" s="56">
+      <c r="F25" s="61">
         <f t="shared" si="2"/>
         <v>-50.02468443584263</v>
       </c>
-      <c r="G25" s="56">
+      <c r="G25" s="61">
         <f t="shared" si="2"/>
         <v>-42.660111562434125</v>
       </c>
-      <c r="H25" s="56">
+      <c r="H25" s="61">
         <f t="shared" si="2"/>
         <v>-35.461050917908807</v>
       </c>
-      <c r="I25" s="56">
+      <c r="I25" s="61">
         <f t="shared" si="2"/>
         <v>-28.429368096259765</v>
       </c>
-      <c r="J25" s="56">
+      <c r="J25" s="61">
         <f t="shared" si="2"/>
         <v>-21.567150171528759</v>
       </c>
-      <c r="K25" s="56">
+      <c r="K25" s="61">
         <f t="shared" si="2"/>
         <v>-14.876714207801681</v>
       </c>
-      <c r="L25" s="56">
+      <c r="L25" s="61">
         <f t="shared" si="2"/>
         <v>-8.3606162459839215</v>
       </c>
-      <c r="M25" s="56">
+      <c r="M25" s="61">
         <f t="shared" si="2"/>
         <v>-2.0216607901690313</v>
       </c>
-      <c r="N25" s="56">
+      <c r="N25" s="61">
         <f t="shared" si="2"/>
         <v>4.1370891824247238</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4517,41 +4725,41 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="57">
+        <v>182</v>
+      </c>
+      <c r="C5" s="62">
         <f>H13/1000</f>
         <v>5.0159616000000007</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="58">
+        <v>183</v>
+      </c>
+      <c r="G5" s="63">
         <f>C10*C11*C12*C13</f>
         <v>4992</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -4563,185 +4771,185 @@
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>86</v>
+      <c r="A8" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="60">
+      <c r="A9" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="65">
         <v>3.2</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="66">
         <v>314</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="67">
         <f>E9*F9</f>
         <v>1004.8000000000001</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="68">
         <f>G9/1000</f>
         <v>1.0048000000000001</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="64">
+      <c r="A10" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="69">
         <v>13</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="E10" s="65">
+      <c r="D10" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="70">
         <f>C10*E9</f>
         <v>41.6</v>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="71">
         <f>F9</f>
         <v>314</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="67">
         <f>G9*C10</f>
         <v>13062.400000000001</v>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="45">
         <f>G10/1000</f>
         <v>13.062400000000002</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="64">
+      <c r="A11" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="69">
         <v>4</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E11" s="65">
+      <c r="D11" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="E11" s="70">
         <f>C11*E10</f>
         <v>166.4</v>
       </c>
-      <c r="F11" s="66">
+      <c r="F11" s="71">
         <f>F10</f>
         <v>314</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="67">
         <f>G10*C11</f>
         <v>52249.600000000006</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="45">
         <f>G11/1000</f>
         <v>52.249600000000008</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="64">
+      <c r="A12" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="69">
         <v>8</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="65">
+      <c r="D12" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="70">
         <f>C12*E11</f>
         <v>1331.2</v>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="71">
         <f>F11</f>
         <v>314</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="67">
         <f>G11*C12</f>
         <v>417996.80000000005</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="45">
         <f>G12/1000</f>
         <v>417.99680000000006</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="64">
+      <c r="A13" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="69">
         <v>12</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="65">
+      <c r="D13" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="70">
         <f>E12</f>
         <v>1331.2</v>
       </c>
-      <c r="F13" s="66">
+      <c r="F13" s="71">
         <f>F12*C13</f>
         <v>3768</v>
       </c>
-      <c r="G13" s="68">
+      <c r="G13" s="73">
         <f>G12*C13</f>
         <v>5015961.6000000006</v>
       </c>
-      <c r="H13" s="69">
+      <c r="H13" s="74">
         <f>G13/1000</f>
         <v>5015.9616000000005</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -4753,158 +4961,158 @@
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" ht="26.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>86</v>
+      <c r="A17" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="64">
+      <c r="A18" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="69">
         <v>13</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="E18" s="65">
+      <c r="D18" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="70">
         <f>C18*$E$9</f>
         <v>41.6</v>
       </c>
-      <c r="F18" s="66">
+      <c r="F18" s="71">
         <f>$F$9</f>
         <v>314</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G18" s="67">
         <f>$G$9*C18</f>
         <v>13062.400000000001</v>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="45">
         <f>G18/1000</f>
         <v>13.062400000000002</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="64">
+      <c r="A19" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" s="69">
         <v>8</v>
       </c>
-      <c r="D19" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E19" s="65">
+      <c r="D19" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="70">
         <f>C19*E18</f>
         <v>332.8</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F19" s="71">
         <f>F18</f>
         <v>314</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="67">
         <f>G18*C19</f>
         <v>104499.20000000001</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="45">
         <f>G19/1000</f>
         <v>104.49920000000002</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="64">
+      <c r="A20" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="69">
         <v>8</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="E20" s="65">
+      <c r="D20" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="70">
         <f>C20*E19</f>
         <v>2662.4</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="71">
         <f>F19</f>
         <v>314</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="67">
         <f>G19*C20</f>
         <v>835993.60000000009</v>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="45">
         <f>G20/1000</f>
         <v>835.99360000000013</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="64">
+      <c r="A21" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="69">
         <v>6</v>
       </c>
-      <c r="D21" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="E21" s="65">
+      <c r="D21" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="70">
         <f>E20</f>
         <v>2662.4</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="71">
         <f>F20*C21</f>
         <v>1884</v>
       </c>
-      <c r="G21" s="68">
+      <c r="G21" s="73">
         <f>G20*C21</f>
         <v>5015961.6000000006</v>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="74">
         <f>G21/1000</f>
         <v>5015.9616000000005</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4922,358 +5130,358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>195</v>
+      <c r="A1" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="36">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70">
+      <c r="A2" s="41">
+        <v>0</v>
+      </c>
+      <c r="B2" s="75">
         <v>4.2</v>
       </c>
-      <c r="C2" s="70">
+      <c r="C2" s="75">
         <v>5</v>
       </c>
-      <c r="D2" s="70">
+      <c r="D2" s="75">
         <v>3.8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="36">
+      <c r="A3" s="41">
         <v>1</v>
       </c>
-      <c r="B3" s="70">
+      <c r="B3" s="75">
         <v>3.9</v>
       </c>
-      <c r="C3" s="70">
+      <c r="C3" s="75">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D3" s="70">
+      <c r="D3" s="75">
         <v>3.6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="36">
+      <c r="A4" s="41">
         <v>2</v>
       </c>
-      <c r="B4" s="70">
+      <c r="B4" s="75">
         <v>3.7</v>
       </c>
-      <c r="C4" s="70">
+      <c r="C4" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="75">
         <v>3.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="36">
+      <c r="A5" s="41">
         <v>3</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="75">
         <v>3.6</v>
       </c>
-      <c r="C5" s="70">
+      <c r="C5" s="75">
         <v>4.3</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="75">
         <v>3.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="36">
+      <c r="A6" s="41">
         <v>4</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="75">
         <v>3.5</v>
       </c>
-      <c r="C6" s="70">
+      <c r="C6" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="75">
         <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="36">
+      <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="75">
         <v>3.8</v>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="75">
         <v>4.8</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="75">
         <v>3.6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="36">
+      <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="75">
         <v>4.5999999999999996</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="75">
         <v>5.8</v>
       </c>
-      <c r="D8" s="70">
+      <c r="D8" s="75">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="36">
+      <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B9" s="75">
         <v>5.4</v>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="75">
         <v>6.8</v>
       </c>
-      <c r="D9" s="70">
+      <c r="D9" s="75">
         <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="36">
+      <c r="A10" s="41">
         <v>8</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="75">
         <v>5.2</v>
       </c>
-      <c r="C10" s="70">
+      <c r="C10" s="75">
         <v>6.2</v>
       </c>
-      <c r="D10" s="70">
+      <c r="D10" s="75">
         <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="36">
+      <c r="A11" s="41">
         <v>9</v>
       </c>
-      <c r="B11" s="70">
+      <c r="B11" s="75">
         <v>4</v>
       </c>
-      <c r="C11" s="70">
+      <c r="C11" s="75">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="75">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="36">
+      <c r="A12" s="41">
         <v>10</v>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="75">
         <v>3</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="75">
         <v>3.2</v>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="75">
         <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="36">
+      <c r="A13" s="41">
         <v>11</v>
       </c>
-      <c r="B13" s="70">
+      <c r="B13" s="75">
         <v>2.6</v>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="75">
         <v>2.6</v>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="75">
         <v>3.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="36">
+      <c r="A14" s="41">
         <v>12</v>
       </c>
-      <c r="B14" s="70">
+      <c r="B14" s="75">
         <v>2.4</v>
       </c>
-      <c r="C14" s="70">
+      <c r="C14" s="75">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="75">
         <v>3.4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="36">
+      <c r="A15" s="41">
         <v>13</v>
       </c>
-      <c r="B15" s="70">
+      <c r="B15" s="75">
         <v>2.4</v>
       </c>
-      <c r="C15" s="70">
+      <c r="C15" s="75">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="75">
         <v>3.4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="36">
+      <c r="A16" s="41">
         <v>14</v>
       </c>
-      <c r="B16" s="70">
+      <c r="B16" s="75">
         <v>2.6</v>
       </c>
-      <c r="C16" s="70">
+      <c r="C16" s="75">
         <v>2.5</v>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="75">
         <v>3.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="36">
+      <c r="A17" s="41">
         <v>15</v>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="75">
         <v>3.1</v>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="75">
         <v>3.4</v>
       </c>
-      <c r="D17" s="70">
+      <c r="D17" s="75">
         <v>3.7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="36">
+      <c r="A18" s="41">
         <v>16</v>
       </c>
-      <c r="B18" s="70">
+      <c r="B18" s="75">
         <v>4</v>
       </c>
-      <c r="C18" s="70">
+      <c r="C18" s="75">
         <v>5.2</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="75">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="36">
+      <c r="A19" s="41">
         <v>17</v>
       </c>
-      <c r="B19" s="70">
+      <c r="B19" s="75">
         <v>5.6</v>
       </c>
-      <c r="C19" s="70">
+      <c r="C19" s="75">
         <v>7.4</v>
       </c>
-      <c r="D19" s="70">
+      <c r="D19" s="75">
         <v>4.7</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="36">
+      <c r="A20" s="41">
         <v>18</v>
       </c>
-      <c r="B20" s="70">
+      <c r="B20" s="75">
         <v>7.2</v>
       </c>
-      <c r="C20" s="70">
+      <c r="C20" s="75">
         <v>9.6</v>
       </c>
-      <c r="D20" s="70">
+      <c r="D20" s="75">
         <v>5.4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="36">
+      <c r="A21" s="41">
         <v>19</v>
       </c>
-      <c r="B21" s="70">
+      <c r="B21" s="75">
         <v>8.5</v>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="75">
         <v>10</v>
       </c>
-      <c r="D21" s="70">
+      <c r="D21" s="75">
         <v>5.8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="36">
+      <c r="A22" s="41">
         <v>20</v>
       </c>
-      <c r="B22" s="70">
+      <c r="B22" s="75">
         <v>8.9</v>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="75">
         <v>10</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D22" s="75">
         <v>5.7</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="36">
+      <c r="A23" s="41">
         <v>21</v>
       </c>
-      <c r="B23" s="70">
+      <c r="B23" s="75">
         <v>7.8</v>
       </c>
-      <c r="C23" s="70">
+      <c r="C23" s="75">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D23" s="75">
         <v>5.2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="36">
+      <c r="A24" s="41">
         <v>22</v>
       </c>
-      <c r="B24" s="70">
+      <c r="B24" s="75">
         <v>6.2</v>
       </c>
-      <c r="C24" s="70">
+      <c r="C24" s="75">
         <v>7.4</v>
       </c>
-      <c r="D24" s="70">
+      <c r="D24" s="75">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="36">
+      <c r="A25" s="41">
         <v>23</v>
       </c>
-      <c r="B25" s="70">
+      <c r="B25" s="75">
         <v>5</v>
       </c>
-      <c r="C25" s="70">
+      <c r="C25" s="75">
         <v>6</v>
       </c>
-      <c r="D25" s="70">
+      <c r="D25" s="75">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/PowerLogic_BESS_Model.xlsx
+++ b/PowerLogic_BESS_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jai_PC\Desktop\BessArbitrageApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42293E2-87CB-4DEB-897A-64A7447D84BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B08311-4451-4D50-BA2B-5D501EC3763D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,15 @@
     <sheet name="02_Dispatch" sheetId="3" r:id="rId3"/>
     <sheet name="03_Revenue" sheetId="4" r:id="rId4"/>
     <sheet name="04_Container" sheetId="5" r:id="rId5"/>
-    <sheet name="Prices" sheetId="6" r:id="rId6"/>
+    <sheet name="05_Schedule96" sheetId="6" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="226">
   <si>
     <t>POWERLOGIC BESS · INDIAN POWER MARKET</t>
   </si>
@@ -658,6 +659,39 @@
   </si>
   <si>
     <t>104S1P — same 5,016 kWh as Design A</t>
+  </si>
+  <si>
+    <t>MODULE 01A · 96-BLOCK SCHEDULE</t>
+  </si>
+  <si>
+    <t>Dispatch converted to 15-minute time blocks — RLDC / SLDC / REMC format</t>
+  </si>
+  <si>
+    <t>Block 1 = 00:00–00:15 … block 96 = 23:45–24:00. Drawal (charging) positive; behind-the-meter discharge is not an injection schedule. Copy into your REMC portal template.</t>
+  </si>
+  <si>
+    <t>Block No</t>
+  </si>
+  <si>
+    <t>Time From</t>
+  </si>
+  <si>
+    <t>Time To</t>
+  </si>
+  <si>
+    <t>Charge / exchange drawal (MW)</t>
+  </si>
+  <si>
+    <t>BTM discharge (MW)</t>
+  </si>
+  <si>
+    <t>Net BESS schedule (MW)</t>
+  </si>
+  <si>
+    <t>SoC end of block (%)</t>
+  </si>
+  <si>
+    <t>SoC is interpolated linearly inside each hour. MW values repeat across the four blocks of an hour — the dispatch plan is hourly; refine block-wise in RTM if needed.</t>
   </si>
   <si>
     <t>Typical day (DAM)</t>
@@ -676,7 +710,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="23">
+  <numFmts count="24">
     <numFmt numFmtId="164" formatCode="#,##0.0&quot; MW&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; MWh&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0&quot; MWh&quot;"/>
@@ -700,6 +734,7 @@
     <numFmt numFmtId="184" formatCode="#,##0.0"/>
     <numFmt numFmtId="185" formatCode="#,##0.000"/>
     <numFmt numFmtId="186" formatCode="#,##0.0&quot; V&quot;"/>
+    <numFmt numFmtId="187" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -803,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -891,6 +926,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5122,6 +5160,3627 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I103"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="H5" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="53">
+        <v>1</v>
+      </c>
+      <c r="B6" s="42" t="str">
+        <f t="shared" ref="B6:B37" si="0">TEXT(TIME(INT((A6-1)*15/60),MOD((A6-1)*15,60),0),"hh:mm")</f>
+        <v>00:00</v>
+      </c>
+      <c r="C6" s="42" t="str">
+        <f t="shared" ref="C6:C37" si="1">IF(A6=96,"24:00",TEXT(TIME(INT(A6*15/60),MOD(A6*15,60),0),"hh:mm"))</f>
+        <v>00:15</v>
+      </c>
+      <c r="D6" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A6-1)/4)+1)</f>
+        <v>4.2</v>
+      </c>
+      <c r="E6" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A6-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A6-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="45">
+        <f t="shared" ref="G6:G37" si="2">E6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="75">
+        <f>100*(IF(INT((A6-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A6-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A6-1)/4)+1)-IF(INT((A6-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A6-1)/4))))*(MOD(A6-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="42" t="str">
+        <f t="shared" ref="I6:I37" si="3">IF(E6&gt;0,"CHARGE",IF(F6&gt;0,"DISCHARGE","—"))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="53">
+        <v>2</v>
+      </c>
+      <c r="B7" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>00:15</v>
+      </c>
+      <c r="C7" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>00:30</v>
+      </c>
+      <c r="D7" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A7-1)/4)+1)</f>
+        <v>4.2</v>
+      </c>
+      <c r="E7" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A7-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A7-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="75">
+        <f>100*(IF(INT((A7-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A7-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A7-1)/4)+1)-IF(INT((A7-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A7-1)/4))))*(MOD(A7-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="53">
+        <v>3</v>
+      </c>
+      <c r="B8" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>00:30</v>
+      </c>
+      <c r="C8" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>00:45</v>
+      </c>
+      <c r="D8" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A8-1)/4)+1)</f>
+        <v>4.2</v>
+      </c>
+      <c r="E8" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A8-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A8-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="75">
+        <f>100*(IF(INT((A8-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A8-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A8-1)/4)+1)-IF(INT((A8-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A8-1)/4))))*(MOD(A8-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="53">
+        <v>4</v>
+      </c>
+      <c r="B9" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>00:45</v>
+      </c>
+      <c r="C9" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>01:00</v>
+      </c>
+      <c r="D9" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A9-1)/4)+1)</f>
+        <v>4.2</v>
+      </c>
+      <c r="E9" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A9-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A9-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="75">
+        <f>100*(IF(INT((A9-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A9-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A9-1)/4)+1)-IF(INT((A9-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A9-1)/4))))*(MOD(A9-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="53">
+        <v>5</v>
+      </c>
+      <c r="B10" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>01:00</v>
+      </c>
+      <c r="C10" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>01:15</v>
+      </c>
+      <c r="D10" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A10-1)/4)+1)</f>
+        <v>3.9</v>
+      </c>
+      <c r="E10" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A10-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A10-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="75">
+        <f>100*(IF(INT((A10-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A10-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A10-1)/4)+1)-IF(INT((A10-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A10-1)/4))))*(MOD(A10-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="53">
+        <v>6</v>
+      </c>
+      <c r="B11" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>01:15</v>
+      </c>
+      <c r="C11" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>01:30</v>
+      </c>
+      <c r="D11" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A11-1)/4)+1)</f>
+        <v>3.9</v>
+      </c>
+      <c r="E11" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A11-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A11-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="75">
+        <f>100*(IF(INT((A11-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A11-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A11-1)/4)+1)-IF(INT((A11-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A11-1)/4))))*(MOD(A11-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="53">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>01:30</v>
+      </c>
+      <c r="C12" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>01:45</v>
+      </c>
+      <c r="D12" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A12-1)/4)+1)</f>
+        <v>3.9</v>
+      </c>
+      <c r="E12" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A12-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A12-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="75">
+        <f>100*(IF(INT((A12-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A12-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A12-1)/4)+1)-IF(INT((A12-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A12-1)/4))))*(MOD(A12-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="53">
+        <v>8</v>
+      </c>
+      <c r="B13" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>01:45</v>
+      </c>
+      <c r="C13" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>02:00</v>
+      </c>
+      <c r="D13" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A13-1)/4)+1)</f>
+        <v>3.9</v>
+      </c>
+      <c r="E13" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A13-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A13-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="75">
+        <f>100*(IF(INT((A13-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A13-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A13-1)/4)+1)-IF(INT((A13-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A13-1)/4))))*(MOD(A13-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="53">
+        <v>9</v>
+      </c>
+      <c r="B14" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>02:00</v>
+      </c>
+      <c r="C14" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>02:15</v>
+      </c>
+      <c r="D14" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A14-1)/4)+1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="E14" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A14-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A14-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="75">
+        <f>100*(IF(INT((A14-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A14-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A14-1)/4)+1)-IF(INT((A14-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A14-1)/4))))*(MOD(A14-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="53">
+        <v>10</v>
+      </c>
+      <c r="B15" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>02:15</v>
+      </c>
+      <c r="C15" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>02:30</v>
+      </c>
+      <c r="D15" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A15-1)/4)+1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="E15" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A15-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A15-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="75">
+        <f>100*(IF(INT((A15-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A15-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A15-1)/4)+1)-IF(INT((A15-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A15-1)/4))))*(MOD(A15-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="53">
+        <v>11</v>
+      </c>
+      <c r="B16" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>02:30</v>
+      </c>
+      <c r="C16" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>02:45</v>
+      </c>
+      <c r="D16" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A16-1)/4)+1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="E16" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A16-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A16-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="75">
+        <f>100*(IF(INT((A16-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A16-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A16-1)/4)+1)-IF(INT((A16-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A16-1)/4))))*(MOD(A16-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="53">
+        <v>12</v>
+      </c>
+      <c r="B17" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>02:45</v>
+      </c>
+      <c r="C17" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>03:00</v>
+      </c>
+      <c r="D17" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A17-1)/4)+1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="E17" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A17-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A17-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="75">
+        <f>100*(IF(INT((A17-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A17-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A17-1)/4)+1)-IF(INT((A17-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A17-1)/4))))*(MOD(A17-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="53">
+        <v>13</v>
+      </c>
+      <c r="B18" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>03:00</v>
+      </c>
+      <c r="C18" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>03:15</v>
+      </c>
+      <c r="D18" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A18-1)/4)+1)</f>
+        <v>3.6</v>
+      </c>
+      <c r="E18" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A18-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F18" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A18-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H18" s="75">
+        <f>100*(IF(INT((A18-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A18-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A18-1)/4)+1)-IF(INT((A18-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A18-1)/4))))*(MOD(A18-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>2.848050967079629</v>
+      </c>
+      <c r="I18" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="53">
+        <v>14</v>
+      </c>
+      <c r="B19" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>03:15</v>
+      </c>
+      <c r="C19" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>03:30</v>
+      </c>
+      <c r="D19" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A19-1)/4)+1)</f>
+        <v>3.6</v>
+      </c>
+      <c r="E19" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A19-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F19" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A19-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H19" s="75">
+        <f>100*(IF(INT((A19-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A19-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A19-1)/4)+1)-IF(INT((A19-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A19-1)/4))))*(MOD(A19-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>5.696101934159258</v>
+      </c>
+      <c r="I19" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="53">
+        <v>15</v>
+      </c>
+      <c r="B20" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>03:30</v>
+      </c>
+      <c r="C20" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>03:45</v>
+      </c>
+      <c r="D20" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A20-1)/4)+1)</f>
+        <v>3.6</v>
+      </c>
+      <c r="E20" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A20-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F20" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A20-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H20" s="75">
+        <f>100*(IF(INT((A20-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A20-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A20-1)/4)+1)-IF(INT((A20-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A20-1)/4))))*(MOD(A20-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>8.5441529012388866</v>
+      </c>
+      <c r="I20" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="53">
+        <v>16</v>
+      </c>
+      <c r="B21" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>03:45</v>
+      </c>
+      <c r="C21" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>04:00</v>
+      </c>
+      <c r="D21" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A21-1)/4)+1)</f>
+        <v>3.6</v>
+      </c>
+      <c r="E21" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A21-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F21" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A21-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H21" s="75">
+        <f>100*(IF(INT((A21-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A21-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A21-1)/4)+1)-IF(INT((A21-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A21-1)/4))))*(MOD(A21-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>11.392203868318516</v>
+      </c>
+      <c r="I21" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="53">
+        <v>17</v>
+      </c>
+      <c r="B22" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>04:00</v>
+      </c>
+      <c r="C22" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>04:15</v>
+      </c>
+      <c r="D22" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A22-1)/4)+1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E22" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A22-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F22" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A22-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H22" s="75">
+        <f>100*(IF(INT((A22-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A22-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A22-1)/4)+1)-IF(INT((A22-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A22-1)/4))))*(MOD(A22-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>14.240254835398144</v>
+      </c>
+      <c r="I22" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="53">
+        <v>18</v>
+      </c>
+      <c r="B23" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>04:15</v>
+      </c>
+      <c r="C23" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>04:30</v>
+      </c>
+      <c r="D23" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A23-1)/4)+1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E23" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A23-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F23" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A23-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H23" s="75">
+        <f>100*(IF(INT((A23-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A23-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A23-1)/4)+1)-IF(INT((A23-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A23-1)/4))))*(MOD(A23-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>17.088305802477773</v>
+      </c>
+      <c r="I23" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="53">
+        <v>19</v>
+      </c>
+      <c r="B24" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>04:30</v>
+      </c>
+      <c r="C24" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>04:45</v>
+      </c>
+      <c r="D24" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A24-1)/4)+1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E24" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A24-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F24" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A24-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H24" s="75">
+        <f>100*(IF(INT((A24-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A24-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A24-1)/4)+1)-IF(INT((A24-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A24-1)/4))))*(MOD(A24-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>19.936356769557403</v>
+      </c>
+      <c r="I24" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="53">
+        <v>20</v>
+      </c>
+      <c r="B25" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>04:45</v>
+      </c>
+      <c r="C25" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>05:00</v>
+      </c>
+      <c r="D25" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A25-1)/4)+1)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E25" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A25-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F25" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A25-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="45">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H25" s="75">
+        <f>100*(IF(INT((A25-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A25-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A25-1)/4)+1)-IF(INT((A25-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A25-1)/4))))*(MOD(A25-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I25" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="53">
+        <v>21</v>
+      </c>
+      <c r="B26" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>05:00</v>
+      </c>
+      <c r="C26" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>05:15</v>
+      </c>
+      <c r="D26" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A26-1)/4)+1)</f>
+        <v>3.8</v>
+      </c>
+      <c r="E26" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A26-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A26-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="75">
+        <f>100*(IF(INT((A26-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A26-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A26-1)/4)+1)-IF(INT((A26-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A26-1)/4))))*(MOD(A26-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I26" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="53">
+        <v>22</v>
+      </c>
+      <c r="B27" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>05:15</v>
+      </c>
+      <c r="C27" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>05:30</v>
+      </c>
+      <c r="D27" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A27-1)/4)+1)</f>
+        <v>3.8</v>
+      </c>
+      <c r="E27" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A27-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A27-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="75">
+        <f>100*(IF(INT((A27-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A27-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A27-1)/4)+1)-IF(INT((A27-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A27-1)/4))))*(MOD(A27-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I27" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="53">
+        <v>23</v>
+      </c>
+      <c r="B28" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>05:30</v>
+      </c>
+      <c r="C28" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>05:45</v>
+      </c>
+      <c r="D28" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A28-1)/4)+1)</f>
+        <v>3.8</v>
+      </c>
+      <c r="E28" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A28-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A28-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="75">
+        <f>100*(IF(INT((A28-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A28-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A28-1)/4)+1)-IF(INT((A28-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A28-1)/4))))*(MOD(A28-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I28" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="53">
+        <v>24</v>
+      </c>
+      <c r="B29" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>05:45</v>
+      </c>
+      <c r="C29" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>06:00</v>
+      </c>
+      <c r="D29" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A29-1)/4)+1)</f>
+        <v>3.8</v>
+      </c>
+      <c r="E29" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A29-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A29-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="75">
+        <f>100*(IF(INT((A29-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A29-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A29-1)/4)+1)-IF(INT((A29-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A29-1)/4))))*(MOD(A29-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I29" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="53">
+        <v>25</v>
+      </c>
+      <c r="B30" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>06:00</v>
+      </c>
+      <c r="C30" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>06:15</v>
+      </c>
+      <c r="D30" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A30-1)/4)+1)</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E30" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A30-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A30-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="75">
+        <f>100*(IF(INT((A30-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A30-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A30-1)/4)+1)-IF(INT((A30-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A30-1)/4))))*(MOD(A30-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I30" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="53">
+        <v>26</v>
+      </c>
+      <c r="B31" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>06:15</v>
+      </c>
+      <c r="C31" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>06:30</v>
+      </c>
+      <c r="D31" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A31-1)/4)+1)</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E31" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A31-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A31-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="75">
+        <f>100*(IF(INT((A31-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A31-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A31-1)/4)+1)-IF(INT((A31-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A31-1)/4))))*(MOD(A31-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I31" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="53">
+        <v>27</v>
+      </c>
+      <c r="B32" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>06:30</v>
+      </c>
+      <c r="C32" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>06:45</v>
+      </c>
+      <c r="D32" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A32-1)/4)+1)</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E32" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A32-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A32-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="75">
+        <f>100*(IF(INT((A32-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A32-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A32-1)/4)+1)-IF(INT((A32-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A32-1)/4))))*(MOD(A32-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I32" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="53">
+        <v>28</v>
+      </c>
+      <c r="B33" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>06:45</v>
+      </c>
+      <c r="C33" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+      <c r="D33" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A33-1)/4)+1)</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E33" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A33-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A33-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="75">
+        <f>100*(IF(INT((A33-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A33-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A33-1)/4)+1)-IF(INT((A33-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A33-1)/4))))*(MOD(A33-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I33" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="53">
+        <v>29</v>
+      </c>
+      <c r="B34" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>07:00</v>
+      </c>
+      <c r="C34" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>07:15</v>
+      </c>
+      <c r="D34" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A34-1)/4)+1)</f>
+        <v>5.4</v>
+      </c>
+      <c r="E34" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A34-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A34-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="75">
+        <f>100*(IF(INT((A34-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A34-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A34-1)/4)+1)-IF(INT((A34-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A34-1)/4))))*(MOD(A34-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I34" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="53">
+        <v>30</v>
+      </c>
+      <c r="B35" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>07:15</v>
+      </c>
+      <c r="C35" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>07:30</v>
+      </c>
+      <c r="D35" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A35-1)/4)+1)</f>
+        <v>5.4</v>
+      </c>
+      <c r="E35" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A35-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A35-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="75">
+        <f>100*(IF(INT((A35-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A35-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A35-1)/4)+1)-IF(INT((A35-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A35-1)/4))))*(MOD(A35-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I35" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="53">
+        <v>31</v>
+      </c>
+      <c r="B36" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>07:30</v>
+      </c>
+      <c r="C36" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>07:45</v>
+      </c>
+      <c r="D36" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A36-1)/4)+1)</f>
+        <v>5.4</v>
+      </c>
+      <c r="E36" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A36-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A36-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="75">
+        <f>100*(IF(INT((A36-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A36-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A36-1)/4)+1)-IF(INT((A36-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A36-1)/4))))*(MOD(A36-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I36" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="53">
+        <v>32</v>
+      </c>
+      <c r="B37" s="42" t="str">
+        <f t="shared" si="0"/>
+        <v>07:45</v>
+      </c>
+      <c r="C37" s="42" t="str">
+        <f t="shared" si="1"/>
+        <v>08:00</v>
+      </c>
+      <c r="D37" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A37-1)/4)+1)</f>
+        <v>5.4</v>
+      </c>
+      <c r="E37" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A37-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A37-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="75">
+        <f>100*(IF(INT((A37-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A37-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A37-1)/4)+1)-IF(INT((A37-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A37-1)/4))))*(MOD(A37-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I37" s="42" t="str">
+        <f t="shared" si="3"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="53">
+        <v>33</v>
+      </c>
+      <c r="B38" s="42" t="str">
+        <f t="shared" ref="B38:B69" si="4">TEXT(TIME(INT((A38-1)*15/60),MOD((A38-1)*15,60),0),"hh:mm")</f>
+        <v>08:00</v>
+      </c>
+      <c r="C38" s="42" t="str">
+        <f t="shared" ref="C38:C69" si="5">IF(A38=96,"24:00",TEXT(TIME(INT(A38*15/60),MOD(A38*15,60),0),"hh:mm"))</f>
+        <v>08:15</v>
+      </c>
+      <c r="D38" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A38-1)/4)+1)</f>
+        <v>5.2</v>
+      </c>
+      <c r="E38" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A38-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A38-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="45">
+        <f t="shared" ref="G38:G69" si="6">E38-F38</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="75">
+        <f>100*(IF(INT((A38-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A38-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A38-1)/4)+1)-IF(INT((A38-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A38-1)/4))))*(MOD(A38-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I38" s="42" t="str">
+        <f t="shared" ref="I38:I69" si="7">IF(E38&gt;0,"CHARGE",IF(F38&gt;0,"DISCHARGE","—"))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="53">
+        <v>34</v>
+      </c>
+      <c r="B39" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>08:15</v>
+      </c>
+      <c r="C39" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>08:30</v>
+      </c>
+      <c r="D39" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A39-1)/4)+1)</f>
+        <v>5.2</v>
+      </c>
+      <c r="E39" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A39-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A39-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="75">
+        <f>100*(IF(INT((A39-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A39-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A39-1)/4)+1)-IF(INT((A39-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A39-1)/4))))*(MOD(A39-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I39" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="53">
+        <v>35</v>
+      </c>
+      <c r="B40" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>08:30</v>
+      </c>
+      <c r="C40" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>08:45</v>
+      </c>
+      <c r="D40" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A40-1)/4)+1)</f>
+        <v>5.2</v>
+      </c>
+      <c r="E40" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A40-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A40-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="75">
+        <f>100*(IF(INT((A40-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A40-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A40-1)/4)+1)-IF(INT((A40-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A40-1)/4))))*(MOD(A40-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I40" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="53">
+        <v>36</v>
+      </c>
+      <c r="B41" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>08:45</v>
+      </c>
+      <c r="C41" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>09:00</v>
+      </c>
+      <c r="D41" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A41-1)/4)+1)</f>
+        <v>5.2</v>
+      </c>
+      <c r="E41" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A41-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A41-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="75">
+        <f>100*(IF(INT((A41-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A41-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A41-1)/4)+1)-IF(INT((A41-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A41-1)/4))))*(MOD(A41-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I41" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="53">
+        <v>37</v>
+      </c>
+      <c r="B42" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>09:00</v>
+      </c>
+      <c r="C42" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>09:15</v>
+      </c>
+      <c r="D42" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A42-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E42" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A42-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A42-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="75">
+        <f>100*(IF(INT((A42-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A42-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A42-1)/4)+1)-IF(INT((A42-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A42-1)/4))))*(MOD(A42-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I42" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="53">
+        <v>38</v>
+      </c>
+      <c r="B43" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>09:15</v>
+      </c>
+      <c r="C43" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>09:30</v>
+      </c>
+      <c r="D43" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A43-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E43" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A43-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A43-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="75">
+        <f>100*(IF(INT((A43-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A43-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A43-1)/4)+1)-IF(INT((A43-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A43-1)/4))))*(MOD(A43-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I43" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="53">
+        <v>39</v>
+      </c>
+      <c r="B44" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>09:30</v>
+      </c>
+      <c r="C44" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>09:45</v>
+      </c>
+      <c r="D44" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A44-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E44" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A44-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A44-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="75">
+        <f>100*(IF(INT((A44-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A44-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A44-1)/4)+1)-IF(INT((A44-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A44-1)/4))))*(MOD(A44-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I44" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="53">
+        <v>40</v>
+      </c>
+      <c r="B45" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>09:45</v>
+      </c>
+      <c r="C45" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>10:00</v>
+      </c>
+      <c r="D45" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A45-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E45" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A45-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A45-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="75">
+        <f>100*(IF(INT((A45-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A45-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A45-1)/4)+1)-IF(INT((A45-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A45-1)/4))))*(MOD(A45-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.784407736637032</v>
+      </c>
+      <c r="I45" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="53">
+        <v>41</v>
+      </c>
+      <c r="B46" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>10:00</v>
+      </c>
+      <c r="C46" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>10:15</v>
+      </c>
+      <c r="D46" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A46-1)/4)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="E46" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A46-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F46" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A46-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H46" s="75">
+        <f>100*(IF(INT((A46-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A46-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A46-1)/4)+1)-IF(INT((A46-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A46-1)/4))))*(MOD(A46-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>25.632458703716658</v>
+      </c>
+      <c r="I46" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="53">
+        <v>42</v>
+      </c>
+      <c r="B47" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>10:15</v>
+      </c>
+      <c r="C47" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>10:30</v>
+      </c>
+      <c r="D47" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A47-1)/4)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="E47" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A47-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F47" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A47-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H47" s="75">
+        <f>100*(IF(INT((A47-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A47-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A47-1)/4)+1)-IF(INT((A47-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A47-1)/4))))*(MOD(A47-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>28.480509670796287</v>
+      </c>
+      <c r="I47" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="53">
+        <v>43</v>
+      </c>
+      <c r="B48" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>10:30</v>
+      </c>
+      <c r="C48" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>10:45</v>
+      </c>
+      <c r="D48" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A48-1)/4)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="E48" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A48-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F48" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A48-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H48" s="75">
+        <f>100*(IF(INT((A48-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A48-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A48-1)/4)+1)-IF(INT((A48-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A48-1)/4))))*(MOD(A48-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>31.328560637875917</v>
+      </c>
+      <c r="I48" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="53">
+        <v>44</v>
+      </c>
+      <c r="B49" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>10:45</v>
+      </c>
+      <c r="C49" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>11:00</v>
+      </c>
+      <c r="D49" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A49-1)/4)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="E49" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A49-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F49" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A49-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H49" s="75">
+        <f>100*(IF(INT((A49-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A49-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A49-1)/4)+1)-IF(INT((A49-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A49-1)/4))))*(MOD(A49-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>34.176611604955546</v>
+      </c>
+      <c r="I49" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="53">
+        <v>45</v>
+      </c>
+      <c r="B50" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>11:00</v>
+      </c>
+      <c r="C50" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>11:15</v>
+      </c>
+      <c r="D50" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A50-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E50" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A50-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F50" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A50-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H50" s="75">
+        <f>100*(IF(INT((A50-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A50-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A50-1)/4)+1)-IF(INT((A50-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A50-1)/4))))*(MOD(A50-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>37.024662572035176</v>
+      </c>
+      <c r="I50" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="53">
+        <v>46</v>
+      </c>
+      <c r="B51" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>11:15</v>
+      </c>
+      <c r="C51" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>11:30</v>
+      </c>
+      <c r="D51" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A51-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E51" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A51-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F51" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A51-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H51" s="75">
+        <f>100*(IF(INT((A51-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A51-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A51-1)/4)+1)-IF(INT((A51-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A51-1)/4))))*(MOD(A51-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>39.872713539114805</v>
+      </c>
+      <c r="I51" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="53">
+        <v>47</v>
+      </c>
+      <c r="B52" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>11:30</v>
+      </c>
+      <c r="C52" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>11:45</v>
+      </c>
+      <c r="D52" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A52-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E52" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A52-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F52" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A52-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H52" s="75">
+        <f>100*(IF(INT((A52-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A52-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A52-1)/4)+1)-IF(INT((A52-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A52-1)/4))))*(MOD(A52-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>42.720764506194435</v>
+      </c>
+      <c r="I52" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="53">
+        <v>48</v>
+      </c>
+      <c r="B53" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>11:45</v>
+      </c>
+      <c r="C53" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>12:00</v>
+      </c>
+      <c r="D53" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A53-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E53" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A53-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F53" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A53-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H53" s="75">
+        <f>100*(IF(INT((A53-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A53-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A53-1)/4)+1)-IF(INT((A53-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A53-1)/4))))*(MOD(A53-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>45.568815473274064</v>
+      </c>
+      <c r="I53" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="53">
+        <v>49</v>
+      </c>
+      <c r="B54" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>12:00</v>
+      </c>
+      <c r="C54" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>12:15</v>
+      </c>
+      <c r="D54" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A54-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E54" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A54-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F54" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A54-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H54" s="75">
+        <f>100*(IF(INT((A54-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A54-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A54-1)/4)+1)-IF(INT((A54-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A54-1)/4))))*(MOD(A54-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>48.416866440353687</v>
+      </c>
+      <c r="I54" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="53">
+        <v>50</v>
+      </c>
+      <c r="B55" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>12:15</v>
+      </c>
+      <c r="C55" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>12:30</v>
+      </c>
+      <c r="D55" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A55-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E55" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A55-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F55" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A55-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H55" s="75">
+        <f>100*(IF(INT((A55-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A55-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A55-1)/4)+1)-IF(INT((A55-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A55-1)/4))))*(MOD(A55-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>51.264917407433316</v>
+      </c>
+      <c r="I55" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="53">
+        <v>51</v>
+      </c>
+      <c r="B56" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>12:30</v>
+      </c>
+      <c r="C56" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>12:45</v>
+      </c>
+      <c r="D56" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A56-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E56" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A56-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F56" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A56-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H56" s="75">
+        <f>100*(IF(INT((A56-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A56-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A56-1)/4)+1)-IF(INT((A56-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A56-1)/4))))*(MOD(A56-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>54.112968374512946</v>
+      </c>
+      <c r="I56" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="53">
+        <v>52</v>
+      </c>
+      <c r="B57" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>12:45</v>
+      </c>
+      <c r="C57" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>13:00</v>
+      </c>
+      <c r="D57" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A57-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E57" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A57-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F57" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A57-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H57" s="75">
+        <f>100*(IF(INT((A57-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A57-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A57-1)/4)+1)-IF(INT((A57-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A57-1)/4))))*(MOD(A57-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>56.961019341592575</v>
+      </c>
+      <c r="I57" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="53">
+        <v>53</v>
+      </c>
+      <c r="B58" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>13:00</v>
+      </c>
+      <c r="C58" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>13:15</v>
+      </c>
+      <c r="D58" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A58-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E58" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A58-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F58" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A58-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H58" s="75">
+        <f>100*(IF(INT((A58-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A58-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A58-1)/4)+1)-IF(INT((A58-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A58-1)/4))))*(MOD(A58-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>59.809070308672204</v>
+      </c>
+      <c r="I58" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="53">
+        <v>54</v>
+      </c>
+      <c r="B59" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>13:15</v>
+      </c>
+      <c r="C59" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>13:30</v>
+      </c>
+      <c r="D59" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A59-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E59" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A59-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F59" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A59-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G59" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H59" s="75">
+        <f>100*(IF(INT((A59-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A59-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A59-1)/4)+1)-IF(INT((A59-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A59-1)/4))))*(MOD(A59-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>62.657121275751834</v>
+      </c>
+      <c r="I59" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="53">
+        <v>55</v>
+      </c>
+      <c r="B60" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>13:30</v>
+      </c>
+      <c r="C60" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>13:45</v>
+      </c>
+      <c r="D60" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A60-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E60" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A60-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F60" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A60-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H60" s="75">
+        <f>100*(IF(INT((A60-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A60-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A60-1)/4)+1)-IF(INT((A60-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A60-1)/4))))*(MOD(A60-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>65.505172242831463</v>
+      </c>
+      <c r="I60" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="53">
+        <v>56</v>
+      </c>
+      <c r="B61" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>13:45</v>
+      </c>
+      <c r="C61" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>14:00</v>
+      </c>
+      <c r="D61" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A61-1)/4)+1)</f>
+        <v>2.4</v>
+      </c>
+      <c r="E61" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A61-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F61" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A61-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H61" s="75">
+        <f>100*(IF(INT((A61-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A61-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A61-1)/4)+1)-IF(INT((A61-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A61-1)/4))))*(MOD(A61-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>68.353223209911093</v>
+      </c>
+      <c r="I61" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="53">
+        <v>57</v>
+      </c>
+      <c r="B62" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>14:00</v>
+      </c>
+      <c r="C62" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>14:15</v>
+      </c>
+      <c r="D62" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A62-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E62" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A62-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F62" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A62-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H62" s="75">
+        <f>100*(IF(INT((A62-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A62-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A62-1)/4)+1)-IF(INT((A62-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A62-1)/4))))*(MOD(A62-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>71.201274176990722</v>
+      </c>
+      <c r="I62" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="53">
+        <v>58</v>
+      </c>
+      <c r="B63" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>14:15</v>
+      </c>
+      <c r="C63" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>14:30</v>
+      </c>
+      <c r="D63" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A63-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E63" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A63-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F63" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A63-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H63" s="75">
+        <f>100*(IF(INT((A63-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A63-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A63-1)/4)+1)-IF(INT((A63-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A63-1)/4))))*(MOD(A63-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>74.049325144070352</v>
+      </c>
+      <c r="I63" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="53">
+        <v>59</v>
+      </c>
+      <c r="B64" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>14:30</v>
+      </c>
+      <c r="C64" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>14:45</v>
+      </c>
+      <c r="D64" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A64-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E64" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A64-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F64" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A64-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H64" s="75">
+        <f>100*(IF(INT((A64-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A64-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A64-1)/4)+1)-IF(INT((A64-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A64-1)/4))))*(MOD(A64-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>76.897376111149981</v>
+      </c>
+      <c r="I64" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="53">
+        <v>60</v>
+      </c>
+      <c r="B65" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>14:45</v>
+      </c>
+      <c r="C65" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>15:00</v>
+      </c>
+      <c r="D65" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A65-1)/4)+1)</f>
+        <v>2.6</v>
+      </c>
+      <c r="E65" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A65-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="F65" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A65-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="45">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="H65" s="75">
+        <f>100*(IF(INT((A65-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A65-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A65-1)/4)+1)-IF(INT((A65-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A65-1)/4))))*(MOD(A65-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>79.745427078229611</v>
+      </c>
+      <c r="I65" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="53">
+        <v>61</v>
+      </c>
+      <c r="B66" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>15:00</v>
+      </c>
+      <c r="C66" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>15:15</v>
+      </c>
+      <c r="D66" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A66-1)/4)+1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="E66" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A66-1)/4)+1)</f>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="F66" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A66-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="45">
+        <f t="shared" si="6"/>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="H66" s="75">
+        <f>100*(IF(INT((A66-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A66-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A66-1)/4)+1)-IF(INT((A66-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A66-1)/4))))*(MOD(A66-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>82.464021183169251</v>
+      </c>
+      <c r="I66" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="53">
+        <v>62</v>
+      </c>
+      <c r="B67" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>15:15</v>
+      </c>
+      <c r="C67" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>15:30</v>
+      </c>
+      <c r="D67" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A67-1)/4)+1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="E67" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A67-1)/4)+1)</f>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="F67" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A67-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="45">
+        <f t="shared" si="6"/>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="H67" s="75">
+        <f>100*(IF(INT((A67-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A67-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A67-1)/4)+1)-IF(INT((A67-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A67-1)/4))))*(MOD(A67-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>85.182615288108892</v>
+      </c>
+      <c r="I67" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="53">
+        <v>63</v>
+      </c>
+      <c r="B68" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>15:30</v>
+      </c>
+      <c r="C68" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>15:45</v>
+      </c>
+      <c r="D68" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A68-1)/4)+1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="E68" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A68-1)/4)+1)</f>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="F68" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A68-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="45">
+        <f t="shared" si="6"/>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="H68" s="75">
+        <f>100*(IF(INT((A68-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A68-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A68-1)/4)+1)-IF(INT((A68-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A68-1)/4))))*(MOD(A68-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>87.901209393048546</v>
+      </c>
+      <c r="I68" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="53">
+        <v>64</v>
+      </c>
+      <c r="B69" s="42" t="str">
+        <f t="shared" si="4"/>
+        <v>15:45</v>
+      </c>
+      <c r="C69" s="42" t="str">
+        <f t="shared" si="5"/>
+        <v>16:00</v>
+      </c>
+      <c r="D69" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A69-1)/4)+1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="E69" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A69-1)/4)+1)</f>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="F69" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A69-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="45">
+        <f t="shared" si="6"/>
+        <v>7.6363636363636331</v>
+      </c>
+      <c r="H69" s="75">
+        <f>100*(IF(INT((A69-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A69-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A69-1)/4)+1)-IF(INT((A69-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A69-1)/4))))*(MOD(A69-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>90.619803497988187</v>
+      </c>
+      <c r="I69" s="42" t="str">
+        <f t="shared" si="7"/>
+        <v>CHARGE</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="53">
+        <v>65</v>
+      </c>
+      <c r="B70" s="42" t="str">
+        <f t="shared" ref="B70:B101" si="8">TEXT(TIME(INT((A70-1)*15/60),MOD((A70-1)*15,60),0),"hh:mm")</f>
+        <v>16:00</v>
+      </c>
+      <c r="C70" s="42" t="str">
+        <f t="shared" ref="C70:C101" si="9">IF(A70=96,"24:00",TEXT(TIME(INT(A70*15/60),MOD(A70*15,60),0),"hh:mm"))</f>
+        <v>16:15</v>
+      </c>
+      <c r="D70" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A70-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E70" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A70-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A70-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G70" s="45">
+        <f t="shared" ref="G70:G101" si="10">E70-F70</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="75">
+        <f>100*(IF(INT((A70-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A70-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A70-1)/4)+1)-IF(INT((A70-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A70-1)/4))))*(MOD(A70-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>90.619803497988187</v>
+      </c>
+      <c r="I70" s="42" t="str">
+        <f t="shared" ref="I70:I101" si="11">IF(E70&gt;0,"CHARGE",IF(F70&gt;0,"DISCHARGE","—"))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="53">
+        <v>66</v>
+      </c>
+      <c r="B71" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>16:15</v>
+      </c>
+      <c r="C71" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>16:30</v>
+      </c>
+      <c r="D71" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A71-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E71" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A71-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A71-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="45">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="75">
+        <f>100*(IF(INT((A71-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A71-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A71-1)/4)+1)-IF(INT((A71-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A71-1)/4))))*(MOD(A71-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>90.619803497988187</v>
+      </c>
+      <c r="I71" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="53">
+        <v>67</v>
+      </c>
+      <c r="B72" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>16:30</v>
+      </c>
+      <c r="C72" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>16:45</v>
+      </c>
+      <c r="D72" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A72-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E72" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A72-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A72-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="45">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="75">
+        <f>100*(IF(INT((A72-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A72-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A72-1)/4)+1)-IF(INT((A72-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A72-1)/4))))*(MOD(A72-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>90.619803497988187</v>
+      </c>
+      <c r="I72" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="53">
+        <v>68</v>
+      </c>
+      <c r="B73" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>16:45</v>
+      </c>
+      <c r="C73" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>17:00</v>
+      </c>
+      <c r="D73" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A73-1)/4)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E73" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A73-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A73-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="45">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="75">
+        <f>100*(IF(INT((A73-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A73-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A73-1)/4)+1)-IF(INT((A73-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A73-1)/4))))*(MOD(A73-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>90.619803497988187</v>
+      </c>
+      <c r="I73" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="53">
+        <v>69</v>
+      </c>
+      <c r="B74" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>17:00</v>
+      </c>
+      <c r="C74" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>17:15</v>
+      </c>
+      <c r="D74" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A74-1)/4)+1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="E74" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A74-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A74-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G74" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H74" s="75">
+        <f>100*(IF(INT((A74-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A74-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A74-1)/4)+1)-IF(INT((A74-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A74-1)/4))))*(MOD(A74-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>87.383381944488605</v>
+      </c>
+      <c r="I74" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="53">
+        <v>70</v>
+      </c>
+      <c r="B75" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>17:15</v>
+      </c>
+      <c r="C75" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>17:30</v>
+      </c>
+      <c r="D75" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A75-1)/4)+1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="E75" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A75-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A75-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G75" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H75" s="75">
+        <f>100*(IF(INT((A75-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A75-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A75-1)/4)+1)-IF(INT((A75-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A75-1)/4))))*(MOD(A75-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>84.146960390989037</v>
+      </c>
+      <c r="I75" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="53">
+        <v>71</v>
+      </c>
+      <c r="B76" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>17:30</v>
+      </c>
+      <c r="C76" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>17:45</v>
+      </c>
+      <c r="D76" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A76-1)/4)+1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="E76" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A76-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A76-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G76" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H76" s="75">
+        <f>100*(IF(INT((A76-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A76-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A76-1)/4)+1)-IF(INT((A76-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A76-1)/4))))*(MOD(A76-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>80.91053883748944</v>
+      </c>
+      <c r="I76" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="53">
+        <v>72</v>
+      </c>
+      <c r="B77" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>17:45</v>
+      </c>
+      <c r="C77" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>18:00</v>
+      </c>
+      <c r="D77" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A77-1)/4)+1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="E77" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A77-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A77-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G77" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H77" s="75">
+        <f>100*(IF(INT((A77-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A77-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A77-1)/4)+1)-IF(INT((A77-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A77-1)/4))))*(MOD(A77-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>77.674117283989872</v>
+      </c>
+      <c r="I77" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="53">
+        <v>73</v>
+      </c>
+      <c r="B78" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>18:00</v>
+      </c>
+      <c r="C78" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>18:15</v>
+      </c>
+      <c r="D78" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A78-1)/4)+1)</f>
+        <v>7.2</v>
+      </c>
+      <c r="E78" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A78-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A78-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G78" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H78" s="75">
+        <f>100*(IF(INT((A78-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A78-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A78-1)/4)+1)-IF(INT((A78-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A78-1)/4))))*(MOD(A78-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>74.43769573049029</v>
+      </c>
+      <c r="I78" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="53">
+        <v>74</v>
+      </c>
+      <c r="B79" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>18:15</v>
+      </c>
+      <c r="C79" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>18:30</v>
+      </c>
+      <c r="D79" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A79-1)/4)+1)</f>
+        <v>7.2</v>
+      </c>
+      <c r="E79" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A79-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A79-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G79" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H79" s="75">
+        <f>100*(IF(INT((A79-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A79-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A79-1)/4)+1)-IF(INT((A79-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A79-1)/4))))*(MOD(A79-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>71.201274176990708</v>
+      </c>
+      <c r="I79" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="53">
+        <v>75</v>
+      </c>
+      <c r="B80" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>18:30</v>
+      </c>
+      <c r="C80" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>18:45</v>
+      </c>
+      <c r="D80" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A80-1)/4)+1)</f>
+        <v>7.2</v>
+      </c>
+      <c r="E80" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A80-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A80-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G80" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H80" s="75">
+        <f>100*(IF(INT((A80-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A80-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A80-1)/4)+1)-IF(INT((A80-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A80-1)/4))))*(MOD(A80-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>67.964852623491126</v>
+      </c>
+      <c r="I80" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" s="53">
+        <v>76</v>
+      </c>
+      <c r="B81" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>18:45</v>
+      </c>
+      <c r="C81" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>19:00</v>
+      </c>
+      <c r="D81" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A81-1)/4)+1)</f>
+        <v>7.2</v>
+      </c>
+      <c r="E81" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A81-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A81-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G81" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H81" s="75">
+        <f>100*(IF(INT((A81-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A81-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A81-1)/4)+1)-IF(INT((A81-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A81-1)/4))))*(MOD(A81-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>64.728431069991558</v>
+      </c>
+      <c r="I81" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="53">
+        <v>77</v>
+      </c>
+      <c r="B82" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>19:00</v>
+      </c>
+      <c r="C82" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>19:15</v>
+      </c>
+      <c r="D82" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A82-1)/4)+1)</f>
+        <v>8.5</v>
+      </c>
+      <c r="E82" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A82-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A82-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G82" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H82" s="75">
+        <f>100*(IF(INT((A82-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A82-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A82-1)/4)+1)-IF(INT((A82-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A82-1)/4))))*(MOD(A82-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>61.492009516491969</v>
+      </c>
+      <c r="I82" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" s="53">
+        <v>78</v>
+      </c>
+      <c r="B83" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>19:15</v>
+      </c>
+      <c r="C83" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>19:30</v>
+      </c>
+      <c r="D83" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A83-1)/4)+1)</f>
+        <v>8.5</v>
+      </c>
+      <c r="E83" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A83-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A83-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G83" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H83" s="75">
+        <f>100*(IF(INT((A83-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A83-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A83-1)/4)+1)-IF(INT((A83-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A83-1)/4))))*(MOD(A83-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>58.255587962992394</v>
+      </c>
+      <c r="I83" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="53">
+        <v>79</v>
+      </c>
+      <c r="B84" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>19:30</v>
+      </c>
+      <c r="C84" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>19:45</v>
+      </c>
+      <c r="D84" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A84-1)/4)+1)</f>
+        <v>8.5</v>
+      </c>
+      <c r="E84" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A84-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A84-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G84" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H84" s="75">
+        <f>100*(IF(INT((A84-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A84-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A84-1)/4)+1)-IF(INT((A84-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A84-1)/4))))*(MOD(A84-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>55.019166409492811</v>
+      </c>
+      <c r="I84" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="53">
+        <v>80</v>
+      </c>
+      <c r="B85" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>19:45</v>
+      </c>
+      <c r="C85" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>20:00</v>
+      </c>
+      <c r="D85" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A85-1)/4)+1)</f>
+        <v>8.5</v>
+      </c>
+      <c r="E85" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A85-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A85-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G85" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H85" s="75">
+        <f>100*(IF(INT((A85-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A85-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A85-1)/4)+1)-IF(INT((A85-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A85-1)/4))))*(MOD(A85-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>51.782744855993236</v>
+      </c>
+      <c r="I85" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="53">
+        <v>81</v>
+      </c>
+      <c r="B86" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>20:00</v>
+      </c>
+      <c r="C86" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>20:15</v>
+      </c>
+      <c r="D86" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A86-1)/4)+1)</f>
+        <v>8.9</v>
+      </c>
+      <c r="E86" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A86-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F86" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A86-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G86" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H86" s="75">
+        <f>100*(IF(INT((A86-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A86-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A86-1)/4)+1)-IF(INT((A86-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A86-1)/4))))*(MOD(A86-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>48.546323302493661</v>
+      </c>
+      <c r="I86" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="53">
+        <v>82</v>
+      </c>
+      <c r="B87" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>20:15</v>
+      </c>
+      <c r="C87" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>20:30</v>
+      </c>
+      <c r="D87" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A87-1)/4)+1)</f>
+        <v>8.9</v>
+      </c>
+      <c r="E87" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A87-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A87-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G87" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H87" s="75">
+        <f>100*(IF(INT((A87-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A87-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A87-1)/4)+1)-IF(INT((A87-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A87-1)/4))))*(MOD(A87-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>45.309901748994079</v>
+      </c>
+      <c r="I87" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" s="53">
+        <v>83</v>
+      </c>
+      <c r="B88" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>20:30</v>
+      </c>
+      <c r="C88" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>20:45</v>
+      </c>
+      <c r="D88" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A88-1)/4)+1)</f>
+        <v>8.9</v>
+      </c>
+      <c r="E88" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A88-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A88-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G88" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H88" s="75">
+        <f>100*(IF(INT((A88-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A88-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A88-1)/4)+1)-IF(INT((A88-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A88-1)/4))))*(MOD(A88-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>42.073480195494497</v>
+      </c>
+      <c r="I88" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" s="53">
+        <v>84</v>
+      </c>
+      <c r="B89" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>20:45</v>
+      </c>
+      <c r="C89" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>21:00</v>
+      </c>
+      <c r="D89" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A89-1)/4)+1)</f>
+        <v>8.9</v>
+      </c>
+      <c r="E89" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A89-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A89-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G89" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H89" s="75">
+        <f>100*(IF(INT((A89-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A89-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A89-1)/4)+1)-IF(INT((A89-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A89-1)/4))))*(MOD(A89-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>38.837058641994922</v>
+      </c>
+      <c r="I89" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" s="53">
+        <v>85</v>
+      </c>
+      <c r="B90" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>21:00</v>
+      </c>
+      <c r="C90" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>21:15</v>
+      </c>
+      <c r="D90" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A90-1)/4)+1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="E90" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A90-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A90-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G90" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H90" s="75">
+        <f>100*(IF(INT((A90-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A90-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A90-1)/4)+1)-IF(INT((A90-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A90-1)/4))))*(MOD(A90-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>35.60063708849534</v>
+      </c>
+      <c r="I90" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" s="53">
+        <v>86</v>
+      </c>
+      <c r="B91" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>21:15</v>
+      </c>
+      <c r="C91" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>21:30</v>
+      </c>
+      <c r="D91" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A91-1)/4)+1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="E91" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A91-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A91-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G91" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H91" s="75">
+        <f>100*(IF(INT((A91-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A91-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A91-1)/4)+1)-IF(INT((A91-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A91-1)/4))))*(MOD(A91-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>32.364215534995758</v>
+      </c>
+      <c r="I91" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" s="53">
+        <v>87</v>
+      </c>
+      <c r="B92" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>21:30</v>
+      </c>
+      <c r="C92" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>21:45</v>
+      </c>
+      <c r="D92" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A92-1)/4)+1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="E92" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A92-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A92-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G92" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H92" s="75">
+        <f>100*(IF(INT((A92-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A92-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A92-1)/4)+1)-IF(INT((A92-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A92-1)/4))))*(MOD(A92-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>29.127793981496183</v>
+      </c>
+      <c r="I92" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" s="53">
+        <v>88</v>
+      </c>
+      <c r="B93" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>21:45</v>
+      </c>
+      <c r="C93" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>22:00</v>
+      </c>
+      <c r="D93" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A93-1)/4)+1)</f>
+        <v>7.8</v>
+      </c>
+      <c r="E93" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A93-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A93-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G93" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H93" s="75">
+        <f>100*(IF(INT((A93-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A93-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A93-1)/4)+1)-IF(INT((A93-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A93-1)/4))))*(MOD(A93-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>25.891372427996604</v>
+      </c>
+      <c r="I93" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" s="53">
+        <v>89</v>
+      </c>
+      <c r="B94" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>22:00</v>
+      </c>
+      <c r="C94" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>22:15</v>
+      </c>
+      <c r="D94" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A94-1)/4)+1)</f>
+        <v>6.2</v>
+      </c>
+      <c r="E94" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A94-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A94-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G94" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H94" s="75">
+        <f>100*(IF(INT((A94-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A94-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A94-1)/4)+1)-IF(INT((A94-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A94-1)/4))))*(MOD(A94-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>22.654950874497022</v>
+      </c>
+      <c r="I94" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" s="53">
+        <v>90</v>
+      </c>
+      <c r="B95" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>22:15</v>
+      </c>
+      <c r="C95" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>22:30</v>
+      </c>
+      <c r="D95" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A95-1)/4)+1)</f>
+        <v>6.2</v>
+      </c>
+      <c r="E95" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A95-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A95-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G95" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H95" s="75">
+        <f>100*(IF(INT((A95-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A95-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A95-1)/4)+1)-IF(INT((A95-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A95-1)/4))))*(MOD(A95-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>19.418529320997443</v>
+      </c>
+      <c r="I95" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" s="53">
+        <v>91</v>
+      </c>
+      <c r="B96" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>22:30</v>
+      </c>
+      <c r="C96" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>22:45</v>
+      </c>
+      <c r="D96" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A96-1)/4)+1)</f>
+        <v>6.2</v>
+      </c>
+      <c r="E96" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A96-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A96-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G96" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H96" s="75">
+        <f>100*(IF(INT((A96-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A96-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A96-1)/4)+1)-IF(INT((A96-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A96-1)/4))))*(MOD(A96-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>16.182107767497868</v>
+      </c>
+      <c r="I96" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" s="53">
+        <v>92</v>
+      </c>
+      <c r="B97" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>22:45</v>
+      </c>
+      <c r="C97" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>23:00</v>
+      </c>
+      <c r="D97" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A97-1)/4)+1)</f>
+        <v>6.2</v>
+      </c>
+      <c r="E97" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A97-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A97-1)/4)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="G97" s="45">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H97" s="75">
+        <f>100*(IF(INT((A97-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A97-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A97-1)/4)+1)-IF(INT((A97-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A97-1)/4))))*(MOD(A97-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>12.94568621399829</v>
+      </c>
+      <c r="I97" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" s="53">
+        <v>93</v>
+      </c>
+      <c r="B98" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>23:00</v>
+      </c>
+      <c r="C98" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>23:15</v>
+      </c>
+      <c r="D98" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A98-1)/4)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="E98" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A98-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A98-1)/4)+1)</f>
+        <v>7.9999999999999849</v>
+      </c>
+      <c r="G98" s="45">
+        <f t="shared" si="10"/>
+        <v>-7.9999999999999849</v>
+      </c>
+      <c r="H98" s="75">
+        <f>100*(IF(INT((A98-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A98-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A98-1)/4)+1)-IF(INT((A98-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A98-1)/4))))*(MOD(A98-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>9.7092646604987181</v>
+      </c>
+      <c r="I98" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" s="53">
+        <v>94</v>
+      </c>
+      <c r="B99" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>23:15</v>
+      </c>
+      <c r="C99" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>23:30</v>
+      </c>
+      <c r="D99" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A99-1)/4)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="E99" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A99-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A99-1)/4)+1)</f>
+        <v>7.9999999999999849</v>
+      </c>
+      <c r="G99" s="45">
+        <f t="shared" si="10"/>
+        <v>-7.9999999999999849</v>
+      </c>
+      <c r="H99" s="75">
+        <f>100*(IF(INT((A99-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A99-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A99-1)/4)+1)-IF(INT((A99-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A99-1)/4))))*(MOD(A99-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>6.4728431069991448</v>
+      </c>
+      <c r="I99" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" s="53">
+        <v>95</v>
+      </c>
+      <c r="B100" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>23:30</v>
+      </c>
+      <c r="C100" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>23:45</v>
+      </c>
+      <c r="D100" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A100-1)/4)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="E100" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A100-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A100-1)/4)+1)</f>
+        <v>7.9999999999999849</v>
+      </c>
+      <c r="G100" s="45">
+        <f t="shared" si="10"/>
+        <v>-7.9999999999999849</v>
+      </c>
+      <c r="H100" s="75">
+        <f>100*(IF(INT((A100-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A100-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A100-1)/4)+1)-IF(INT((A100-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A100-1)/4))))*(MOD(A100-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>3.2364215534995715</v>
+      </c>
+      <c r="I100" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="53">
+        <v>96</v>
+      </c>
+      <c r="B101" s="42" t="str">
+        <f t="shared" si="8"/>
+        <v>23:45</v>
+      </c>
+      <c r="C101" s="42" t="str">
+        <f t="shared" si="9"/>
+        <v>24:00</v>
+      </c>
+      <c r="D101" s="52">
+        <f>INDEX('02_Dispatch'!$C$21:$C$44,INT((A101-1)/4)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="E101" s="45">
+        <f>INDEX('02_Dispatch'!$H$21:$H$44,INT((A101-1)/4)+1)</f>
+        <v>0</v>
+      </c>
+      <c r="F101" s="45">
+        <f>INDEX('02_Dispatch'!$I$21:$I$44,INT((A101-1)/4)+1)</f>
+        <v>7.9999999999999849</v>
+      </c>
+      <c r="G101" s="45">
+        <f t="shared" si="10"/>
+        <v>-7.9999999999999849</v>
+      </c>
+      <c r="H101" s="75">
+        <f>100*(IF(INT((A101-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A101-1)/4)))+(INDEX('02_Dispatch'!$J$21:$J$44,INT((A101-1)/4)+1)-IF(INT((A101-1)/4)=0,0,INDEX('02_Dispatch'!$J$21:$J$44,INT((A101-1)/4))))*(MOD(A101-1,4)+1)/4)/'00_Inputs'!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="I101" s="42" t="str">
+        <f t="shared" si="11"/>
+        <v>DISCHARGE</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -5134,26 +8793,26 @@
         <v>96</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="41">
         <v>0</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="76">
         <v>4.2</v>
       </c>
-      <c r="C2" s="75">
+      <c r="C2" s="76">
         <v>5</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="76">
         <v>3.8</v>
       </c>
     </row>
@@ -5161,13 +8820,13 @@
       <c r="A3" s="41">
         <v>1</v>
       </c>
-      <c r="B3" s="75">
+      <c r="B3" s="76">
         <v>3.9</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="76">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="76">
         <v>3.6</v>
       </c>
     </row>
@@ -5175,13 +8834,13 @@
       <c r="A4" s="41">
         <v>2</v>
       </c>
-      <c r="B4" s="75">
+      <c r="B4" s="76">
         <v>3.7</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="76">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="76">
         <v>3.5</v>
       </c>
     </row>
@@ -5189,13 +8848,13 @@
       <c r="A5" s="41">
         <v>3</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="76">
         <v>3.6</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="76">
         <v>4.3</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="76">
         <v>3.4</v>
       </c>
     </row>
@@ -5203,13 +8862,13 @@
       <c r="A6" s="41">
         <v>4</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="76">
         <v>3.5</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="76">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="76">
         <v>3.4</v>
       </c>
     </row>
@@ -5217,13 +8876,13 @@
       <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="76">
         <v>3.8</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="76">
         <v>4.8</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="76">
         <v>3.6</v>
       </c>
     </row>
@@ -5231,13 +8890,13 @@
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="76">
         <v>4.5999999999999996</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="76">
         <v>5.8</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="76">
         <v>4</v>
       </c>
     </row>
@@ -5245,13 +8904,13 @@
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="75">
+      <c r="B9" s="76">
         <v>5.4</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="76">
         <v>6.8</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="76">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -5259,13 +8918,13 @@
       <c r="A10" s="41">
         <v>8</v>
       </c>
-      <c r="B10" s="75">
+      <c r="B10" s="76">
         <v>5.2</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="76">
         <v>6.2</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="76">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -5273,13 +8932,13 @@
       <c r="A11" s="41">
         <v>9</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="76">
         <v>4</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="76">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="76">
         <v>4</v>
       </c>
     </row>
@@ -5287,13 +8946,13 @@
       <c r="A12" s="41">
         <v>10</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="76">
         <v>3</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="76">
         <v>3.2</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="76">
         <v>3.7</v>
       </c>
     </row>
@@ -5301,13 +8960,13 @@
       <c r="A13" s="41">
         <v>11</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="76">
         <v>2.6</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="76">
         <v>2.6</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="76">
         <v>3.5</v>
       </c>
     </row>
@@ -5315,13 +8974,13 @@
       <c r="A14" s="41">
         <v>12</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="76">
         <v>2.4</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="76">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="76">
         <v>3.4</v>
       </c>
     </row>
@@ -5329,13 +8988,13 @@
       <c r="A15" s="41">
         <v>13</v>
       </c>
-      <c r="B15" s="75">
+      <c r="B15" s="76">
         <v>2.4</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="76">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="76">
         <v>3.4</v>
       </c>
     </row>
@@ -5343,13 +9002,13 @@
       <c r="A16" s="41">
         <v>14</v>
       </c>
-      <c r="B16" s="75">
+      <c r="B16" s="76">
         <v>2.6</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="76">
         <v>2.5</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="76">
         <v>3.5</v>
       </c>
     </row>
@@ -5357,13 +9016,13 @@
       <c r="A17" s="41">
         <v>15</v>
       </c>
-      <c r="B17" s="75">
+      <c r="B17" s="76">
         <v>3.1</v>
       </c>
-      <c r="C17" s="75">
+      <c r="C17" s="76">
         <v>3.4</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="76">
         <v>3.7</v>
       </c>
     </row>
@@ -5371,13 +9030,13 @@
       <c r="A18" s="41">
         <v>16</v>
       </c>
-      <c r="B18" s="75">
+      <c r="B18" s="76">
         <v>4</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="76">
         <v>5.2</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="76">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -5385,13 +9044,13 @@
       <c r="A19" s="41">
         <v>17</v>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="76">
         <v>5.6</v>
       </c>
-      <c r="C19" s="75">
+      <c r="C19" s="76">
         <v>7.4</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="76">
         <v>4.7</v>
       </c>
     </row>
@@ -5399,13 +9058,13 @@
       <c r="A20" s="41">
         <v>18</v>
       </c>
-      <c r="B20" s="75">
+      <c r="B20" s="76">
         <v>7.2</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="76">
         <v>9.6</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="76">
         <v>5.4</v>
       </c>
     </row>
@@ -5413,13 +9072,13 @@
       <c r="A21" s="41">
         <v>19</v>
       </c>
-      <c r="B21" s="75">
+      <c r="B21" s="76">
         <v>8.5</v>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="76">
         <v>10</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="76">
         <v>5.8</v>
       </c>
     </row>
@@ -5427,13 +9086,13 @@
       <c r="A22" s="41">
         <v>20</v>
       </c>
-      <c r="B22" s="75">
+      <c r="B22" s="76">
         <v>8.9</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="76">
         <v>10</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="76">
         <v>5.7</v>
       </c>
     </row>
@@ -5441,13 +9100,13 @@
       <c r="A23" s="41">
         <v>21</v>
       </c>
-      <c r="B23" s="75">
+      <c r="B23" s="76">
         <v>7.8</v>
       </c>
-      <c r="C23" s="75">
+      <c r="C23" s="76">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="76">
         <v>5.2</v>
       </c>
     </row>
@@ -5455,13 +9114,13 @@
       <c r="A24" s="41">
         <v>22</v>
       </c>
-      <c r="B24" s="75">
+      <c r="B24" s="76">
         <v>6.2</v>
       </c>
-      <c r="C24" s="75">
+      <c r="C24" s="76">
         <v>7.4</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="76">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -5469,19 +9128,19 @@
       <c r="A25" s="41">
         <v>23</v>
       </c>
-      <c r="B25" s="75">
+      <c r="B25" s="76">
         <v>5</v>
       </c>
-      <c r="C25" s="75">
+      <c r="C25" s="76">
         <v>6</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D25" s="76">
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
